--- a/python-ai-runtime/evaluation/rag/documents/tenant-10-project-102/spreadsheets/workbook-object-storage-task-cases.xlsx
+++ b/python-ai-runtime/evaluation/rag/documents/tenant-10-project-102/spreadsheets/workbook-object-storage-task-cases.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R9d8f2a657f9644ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务案例" sheetId="2" r:id="Ra32500d5c98a432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败任务明细" sheetId="3" r:id="Rdf024e32d4f5479e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务参数" sheetId="4" r:id="Rb1cc3e8c50db464c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="5" r:id="R7e87bcd6a57f49b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="6" r:id="Rabfe4b127c364beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R8d0ab8a6f05848ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务案例" sheetId="2" r:id="R03cf1c9e6b124489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败任务明细" sheetId="3" r:id="Ra0392cecca954b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务参数" sheetId="4" r:id="R602531d8440344cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="5" r:id="R97723a8664f5480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校验" sheetId="6" r:id="R657e22341c55416e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,7 +467,7 @@
         <x:v>内容摘要</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>收录 MinIO/S3、前缀扫描、清单、Parquet 分区、覆盖保护和断点续传案例。；共 681 条主题记录。</x:v>
+        <x:v>收录 MinIO/S3、前缀扫描、清单、Parquet 分区、覆盖保护和断点续传案例。；共 689 条主题记录。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9511,11 +9511,19 @@
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="36" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="36" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="36" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="36" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="36" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="36" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="36" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="36" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="36" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="26" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="26" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -9541,21 +9549,45 @@
         <x:v>错误码</x:v>
       </x:c>
       <x:c r="H1" s="18" t="str">
-        <x:v>失败原因</x:v>
+        <x:v>用户可见现象</x:v>
       </x:c>
       <x:c r="I1" s="18" t="str">
+        <x:v>用户提示</x:v>
+      </x:c>
+      <x:c r="J1" s="18" t="str">
+        <x:v>日志查看位置</x:v>
+      </x:c>
+      <x:c r="K1" s="18" t="str">
+        <x:v>关键日志摘录</x:v>
+      </x:c>
+      <x:c r="L1" s="18" t="str">
+        <x:v>详细定位过程</x:v>
+      </x:c>
+      <x:c r="M1" s="18" t="str">
+        <x:v>通俗根因</x:v>
+      </x:c>
+      <x:c r="N1" s="18" t="str">
+        <x:v>技术根因</x:v>
+      </x:c>
+      <x:c r="O1" s="18" t="str">
+        <x:v>开发修复说明</x:v>
+      </x:c>
+      <x:c r="P1" s="18" t="str">
+        <x:v>修复步骤</x:v>
+      </x:c>
+      <x:c r="Q1" s="18" t="str">
+        <x:v>配置或代码修改</x:v>
+      </x:c>
+      <x:c r="R1" s="18" t="str">
         <x:v>证据来源</x:v>
       </x:c>
-      <x:c r="J1" s="18" t="str">
+      <x:c r="S1" s="18" t="str">
         <x:v>发生时间</x:v>
       </x:c>
-      <x:c r="K1" s="18" t="str">
+      <x:c r="T1" s="18" t="str">
         <x:v>可信度</x:v>
       </x:c>
-      <x:c r="L1" s="18" t="str">
-        <x:v>处置</x:v>
-      </x:c>
-      <x:c r="M1" s="18" t="str">
+      <x:c r="U1" s="18" t="str">
         <x:v>最终状态</x:v>
       </x:c>
     </x:row>
@@ -9579,25 +9611,49 @@
         <x:v>INC-tenant-10-project-102-0002</x:v>
       </x:c>
       <x:c r="G2" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H2" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I2" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0002 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0002/executions/EXEC-tenant-10-project-102-0002/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K2" s="8" t="str">
+        <x:v>2026-08-10T00:00:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0002 taskId=TASK-tenant-10-project-102-0002 executionId=EXEC-tenant-10-project-102-0002 objectId=object-02 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L2" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0002、taskId=TASK-tenant-10-project-102-0002 和 executionId=EXEC-tenant-10-project-102-0002。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0002/executions/EXEC-tenant-10-project-102-0002/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v100 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N2" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O2" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P2" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R2" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0002</x:v>
       </x:c>
-      <x:c r="J2" s="19" t="str">
+      <x:c r="S2" s="19" t="str">
         <x:v>UTC 2026-08-10 00:00:00.000</x:v>
       </x:c>
-      <x:c r="K2" s="20" t="n">
+      <x:c r="T2" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L2" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M2" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U2" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9620,24 +9676,48 @@
         <x:v>INC-tenant-10-project-102-0003</x:v>
       </x:c>
       <x:c r="G3" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H3" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I3" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J3" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0003 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0003/executions/EXEC-tenant-10-project-102-0003/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K3" s="8" t="str">
+        <x:v>2026-08-10T00:08:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0003 taskId=TASK-tenant-10-project-102-0003 executionId=EXEC-tenant-10-project-102-0003 objectId=object-03 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0003、taskId=TASK-tenant-10-project-102-0003 和 executionId=EXEC-tenant-10-project-102-0003。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0003/executions/EXEC-tenant-10-project-102-0003/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v101 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M3" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N3" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O3" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P3" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q3" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R3" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0003</x:v>
       </x:c>
-      <x:c r="J3" s="19" t="str">
+      <x:c r="S3" s="19" t="str">
         <x:v>UTC 2026-08-10 00:08:00.000</x:v>
       </x:c>
-      <x:c r="K3" s="20" t="n">
+      <x:c r="T3" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L3" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M3" s="8" t="str">
+      <x:c r="U3" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -9661,25 +9741,49 @@
         <x:v>INC-tenant-10-project-102-0005</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I4" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J4" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0005 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0005/executions/EXEC-tenant-10-project-102-0005/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K4" s="8" t="str">
+        <x:v>2026-08-10T00:16:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0005 taskId=TASK-tenant-10-project-102-0005 executionId=EXEC-tenant-10-project-102-0005 objectId=object-05 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L4" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0005、taskId=TASK-tenant-10-project-102-0005 和 executionId=EXEC-tenant-10-project-102-0005。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0005/executions/EXEC-tenant-10-project-102-0005/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v103 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M4" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N4" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O4" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P4" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q4" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R4" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0005</x:v>
       </x:c>
-      <x:c r="J4" s="19" t="str">
+      <x:c r="S4" s="19" t="str">
         <x:v>UTC 2026-08-10 00:16:00.000</x:v>
       </x:c>
-      <x:c r="K4" s="20" t="n">
+      <x:c r="T4" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L4" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M4" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U4" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -9702,24 +9806,48 @@
         <x:v>INC-tenant-10-project-102-0006</x:v>
       </x:c>
       <x:c r="G5" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H5" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J5" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0006 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0006/executions/EXEC-tenant-10-project-102-0006/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K5" s="8" t="str">
+        <x:v>2026-08-10T00:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0006 taskId=TASK-tenant-10-project-102-0006 executionId=EXEC-tenant-10-project-102-0006 objectId=object-06 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L5" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0006、taskId=TASK-tenant-10-project-102-0006 和 executionId=EXEC-tenant-10-project-102-0006。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0006/executions/EXEC-tenant-10-project-102-0006/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v104 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M5" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N5" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O5" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P5" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q5" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R5" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0006</x:v>
       </x:c>
-      <x:c r="J5" s="19" t="str">
+      <x:c r="S5" s="19" t="str">
         <x:v>UTC 2026-08-10 00:24:00.000</x:v>
       </x:c>
-      <x:c r="K5" s="20" t="n">
+      <x:c r="T5" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L5" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M5" s="8" t="str">
+      <x:c r="U5" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9743,24 +9871,48 @@
         <x:v>INC-tenant-10-project-102-0008</x:v>
       </x:c>
       <x:c r="G6" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H6" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J6" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0008 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0008/executions/EXEC-tenant-10-project-102-0008/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K6" s="8" t="str">
+        <x:v>2026-08-10T00:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0008 taskId=TASK-tenant-10-project-102-0008 executionId=EXEC-tenant-10-project-102-0008 objectId=object-08 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0008、taskId=TASK-tenant-10-project-102-0008 和 executionId=EXEC-tenant-10-project-102-0008。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0008/executions/EXEC-tenant-10-project-102-0008/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v106 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N6" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O6" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P6" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R6" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0008</x:v>
       </x:c>
-      <x:c r="J6" s="19" t="str">
+      <x:c r="S6" s="19" t="str">
         <x:v>UTC 2026-08-10 00:32:00.000</x:v>
       </x:c>
-      <x:c r="K6" s="20" t="n">
+      <x:c r="T6" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L6" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M6" s="8" t="str">
+      <x:c r="U6" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9784,24 +9936,48 @@
         <x:v>INC-tenant-10-project-102-0009</x:v>
       </x:c>
       <x:c r="G7" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H7" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J7" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0009 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0009/executions/EXEC-tenant-10-project-102-0009/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K7" s="8" t="str">
+        <x:v>2026-08-10T00:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0009 taskId=TASK-tenant-10-project-102-0009 executionId=EXEC-tenant-10-project-102-0009 objectId=object-09 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L7" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0009、taskId=TASK-tenant-10-project-102-0009 和 executionId=EXEC-tenant-10-project-102-0009。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0009/executions/EXEC-tenant-10-project-102-0009/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v107 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M7" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N7" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O7" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P7" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R7" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0009</x:v>
       </x:c>
-      <x:c r="J7" s="19" t="str">
+      <x:c r="S7" s="19" t="str">
         <x:v>UTC 2026-08-10 00:40:00.000</x:v>
       </x:c>
-      <x:c r="K7" s="20" t="n">
+      <x:c r="T7" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L7" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="str">
+      <x:c r="U7" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9825,24 +10001,48 @@
         <x:v>INC-tenant-10-project-102-0011</x:v>
       </x:c>
       <x:c r="G8" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H8" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0011 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0011/executions/EXEC-tenant-10-project-102-0011/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K8" s="8" t="str">
+        <x:v>2026-08-10T00:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0011 taskId=TASK-tenant-10-project-102-0011 executionId=EXEC-tenant-10-project-102-0011 objectId=object-11 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L8" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0011、taskId=TASK-tenant-10-project-102-0011 和 executionId=EXEC-tenant-10-project-102-0011。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0011/executions/EXEC-tenant-10-project-102-0011/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v109 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N8" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O8" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P8" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q8" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R8" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0011</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="str">
+      <x:c r="S8" s="19" t="str">
         <x:v>UTC 2026-08-10 00:48:00.000</x:v>
       </x:c>
-      <x:c r="K8" s="20" t="n">
+      <x:c r="T8" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L8" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="str">
+      <x:c r="U8" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9866,24 +10066,48 @@
         <x:v>INC-tenant-10-project-102-0012</x:v>
       </x:c>
       <x:c r="G9" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H9" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J9" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0012 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0012/executions/EXEC-tenant-10-project-102-0012/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K9" s="8" t="str">
+        <x:v>2026-08-10T00:56:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0012 taskId=TASK-tenant-10-project-102-0012 executionId=EXEC-tenant-10-project-102-0012 objectId=object-12 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L9" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0012、taskId=TASK-tenant-10-project-102-0012 和 executionId=EXEC-tenant-10-project-102-0012。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0012/executions/EXEC-tenant-10-project-102-0012/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v110 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M9" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N9" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O9" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P9" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q9" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R9" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0012</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="str">
+      <x:c r="S9" s="19" t="str">
         <x:v>UTC 2026-08-10 00:56:00.000</x:v>
       </x:c>
-      <x:c r="K9" s="20" t="n">
+      <x:c r="T9" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L9" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M9" s="8" t="str">
+      <x:c r="U9" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9907,24 +10131,48 @@
         <x:v>INC-tenant-10-project-102-0014</x:v>
       </x:c>
       <x:c r="G10" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H10" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J10" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0014 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0014/executions/EXEC-tenant-10-project-102-0014/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K10" s="8" t="str">
+        <x:v>2026-08-10T01:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0014 taskId=TASK-tenant-10-project-102-0014 executionId=EXEC-tenant-10-project-102-0014 objectId=object-14 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L10" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0014、taskId=TASK-tenant-10-project-102-0014 和 executionId=EXEC-tenant-10-project-102-0014。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0014/executions/EXEC-tenant-10-project-102-0014/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v112 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M10" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N10" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O10" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P10" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q10" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R10" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0014</x:v>
       </x:c>
-      <x:c r="J10" s="19" t="str">
+      <x:c r="S10" s="19" t="str">
         <x:v>UTC 2026-08-10 01:04:00.000</x:v>
       </x:c>
-      <x:c r="K10" s="20" t="n">
+      <x:c r="T10" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L10" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M10" s="8" t="str">
+      <x:c r="U10" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9948,24 +10196,48 @@
         <x:v>INC-tenant-10-project-102-0015</x:v>
       </x:c>
       <x:c r="G11" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H11" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J11" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0015 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0015/executions/EXEC-tenant-10-project-102-0015/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K11" s="8" t="str">
+        <x:v>2026-08-10T01:12:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0015 taskId=TASK-tenant-10-project-102-0015 executionId=EXEC-tenant-10-project-102-0015 objectId=object-15 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L11" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0015、taskId=TASK-tenant-10-project-102-0015 和 executionId=EXEC-tenant-10-project-102-0015。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0015/executions/EXEC-tenant-10-project-102-0015/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v113 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M11" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N11" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O11" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P11" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q11" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R11" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0015</x:v>
       </x:c>
-      <x:c r="J11" s="19" t="str">
+      <x:c r="S11" s="19" t="str">
         <x:v>UTC 2026-08-10 01:12:00.000</x:v>
       </x:c>
-      <x:c r="K11" s="20" t="n">
+      <x:c r="T11" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L11" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M11" s="8" t="str">
+      <x:c r="U11" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -9989,24 +10261,48 @@
         <x:v>INC-tenant-10-project-102-0017</x:v>
       </x:c>
       <x:c r="G12" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H12" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I12" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J12" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0017 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0017/executions/EXEC-tenant-10-project-102-0017/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K12" s="8" t="str">
+        <x:v>2026-08-10T01:20:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0017 taskId=TASK-tenant-10-project-102-0017 executionId=EXEC-tenant-10-project-102-0017 objectId=object-17 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L12" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0017、taskId=TASK-tenant-10-project-102-0017 和 executionId=EXEC-tenant-10-project-102-0017。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0017/executions/EXEC-tenant-10-project-102-0017/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v115 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M12" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N12" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O12" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P12" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q12" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R12" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0017</x:v>
       </x:c>
-      <x:c r="J12" s="19" t="str">
+      <x:c r="S12" s="19" t="str">
         <x:v>UTC 2026-08-10 01:20:00.000</x:v>
       </x:c>
-      <x:c r="K12" s="20" t="n">
+      <x:c r="T12" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L12" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M12" s="8" t="str">
+      <x:c r="U12" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10030,24 +10326,48 @@
         <x:v>INC-tenant-10-project-102-0018</x:v>
       </x:c>
       <x:c r="G13" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H13" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I13" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J13" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0018 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0018/executions/EXEC-tenant-10-project-102-0018/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K13" s="8" t="str">
+        <x:v>2026-08-10T01:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0018 taskId=TASK-tenant-10-project-102-0018 executionId=EXEC-tenant-10-project-102-0018 objectId=object-18 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L13" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0018、taskId=TASK-tenant-10-project-102-0018 和 executionId=EXEC-tenant-10-project-102-0018。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0018/executions/EXEC-tenant-10-project-102-0018/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v116 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M13" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N13" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O13" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P13" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q13" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R13" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0018</x:v>
       </x:c>
-      <x:c r="J13" s="19" t="str">
+      <x:c r="S13" s="19" t="str">
         <x:v>UTC 2026-08-10 01:28:00.000</x:v>
       </x:c>
-      <x:c r="K13" s="20" t="n">
+      <x:c r="T13" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L13" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M13" s="8" t="str">
+      <x:c r="U13" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10071,25 +10391,49 @@
         <x:v>INC-tenant-10-project-102-0020</x:v>
       </x:c>
       <x:c r="G14" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H14" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J14" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0020 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0020/executions/EXEC-tenant-10-project-102-0020/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K14" s="8" t="str">
+        <x:v>2026-08-10T01:36:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0020 taskId=TASK-tenant-10-project-102-0020 executionId=EXEC-tenant-10-project-102-0020 objectId=object-20 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0020、taskId=TASK-tenant-10-project-102-0020 和 executionId=EXEC-tenant-10-project-102-0020。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0020/executions/EXEC-tenant-10-project-102-0020/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v118 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M14" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N14" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O14" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P14" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q14" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R14" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0020</x:v>
       </x:c>
-      <x:c r="J14" s="19" t="str">
+      <x:c r="S14" s="19" t="str">
         <x:v>UTC 2026-08-10 01:36:00.000</x:v>
       </x:c>
-      <x:c r="K14" s="20" t="n">
+      <x:c r="T14" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L14" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M14" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U14" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -10112,24 +10456,48 @@
         <x:v>INC-tenant-10-project-102-0021</x:v>
       </x:c>
       <x:c r="G15" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H15" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I15" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J15" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0021 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0021/executions/EXEC-tenant-10-project-102-0021/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K15" s="8" t="str">
+        <x:v>2026-08-10T01:44:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0021 taskId=TASK-tenant-10-project-102-0021 executionId=EXEC-tenant-10-project-102-0021 objectId=object-21 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0021、taskId=TASK-tenant-10-project-102-0021 和 executionId=EXEC-tenant-10-project-102-0021。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0021/executions/EXEC-tenant-10-project-102-0021/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v119 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M15" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N15" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O15" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P15" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q15" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R15" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0021</x:v>
       </x:c>
-      <x:c r="J15" s="19" t="str">
+      <x:c r="S15" s="19" t="str">
         <x:v>UTC 2026-08-10 01:44:00.000</x:v>
       </x:c>
-      <x:c r="K15" s="20" t="n">
+      <x:c r="T15" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L15" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M15" s="8" t="str">
+      <x:c r="U15" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10153,25 +10521,49 @@
         <x:v>INC-tenant-10-project-102-0023</x:v>
       </x:c>
       <x:c r="G16" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H16" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I16" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J16" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0023 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0023/executions/EXEC-tenant-10-project-102-0023/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K16" s="8" t="str">
+        <x:v>2026-08-10T01:52:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0023 taskId=TASK-tenant-10-project-102-0023 executionId=EXEC-tenant-10-project-102-0023 objectId=object-23 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L16" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0023、taskId=TASK-tenant-10-project-102-0023 和 executionId=EXEC-tenant-10-project-102-0023。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0023/executions/EXEC-tenant-10-project-102-0023/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v121 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M16" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N16" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O16" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P16" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q16" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R16" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0023</x:v>
       </x:c>
-      <x:c r="J16" s="19" t="str">
+      <x:c r="S16" s="19" t="str">
         <x:v>UTC 2026-08-10 01:52:00.000</x:v>
       </x:c>
-      <x:c r="K16" s="20" t="n">
+      <x:c r="T16" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L16" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M16" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U16" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -10194,24 +10586,48 @@
         <x:v>INC-tenant-10-project-102-0024</x:v>
       </x:c>
       <x:c r="G17" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H17" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I17" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J17" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0024 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0024/executions/EXEC-tenant-10-project-102-0024/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K17" s="8" t="str">
+        <x:v>2026-08-10T02:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0024 taskId=TASK-tenant-10-project-102-0024 executionId=EXEC-tenant-10-project-102-0024 objectId=object-24 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L17" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0024、taskId=TASK-tenant-10-project-102-0024 和 executionId=EXEC-tenant-10-project-102-0024。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0024/executions/EXEC-tenant-10-project-102-0024/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v122 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M17" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N17" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O17" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P17" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q17" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R17" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0024</x:v>
       </x:c>
-      <x:c r="J17" s="19" t="str">
+      <x:c r="S17" s="19" t="str">
         <x:v>UTC 2026-08-10 02:00:00.000</x:v>
       </x:c>
-      <x:c r="K17" s="20" t="n">
+      <x:c r="T17" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L17" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M17" s="8" t="str">
+      <x:c r="U17" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10235,24 +10651,48 @@
         <x:v>INC-tenant-10-project-102-0026</x:v>
       </x:c>
       <x:c r="G18" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H18" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I18" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J18" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0026 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0026/executions/EXEC-tenant-10-project-102-0026/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K18" s="8" t="str">
+        <x:v>2026-08-10T02:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0026 taskId=TASK-tenant-10-project-102-0026 executionId=EXEC-tenant-10-project-102-0026 objectId=object-26 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L18" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0026、taskId=TASK-tenant-10-project-102-0026 和 executionId=EXEC-tenant-10-project-102-0026。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0026/executions/EXEC-tenant-10-project-102-0026/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v124 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M18" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N18" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O18" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P18" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q18" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R18" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0026</x:v>
       </x:c>
-      <x:c r="J18" s="19" t="str">
+      <x:c r="S18" s="19" t="str">
         <x:v>UTC 2026-08-10 02:08:00.000</x:v>
       </x:c>
-      <x:c r="K18" s="20" t="n">
+      <x:c r="T18" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L18" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M18" s="8" t="str">
+      <x:c r="U18" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10276,24 +10716,48 @@
         <x:v>INC-tenant-10-project-102-0027</x:v>
       </x:c>
       <x:c r="G19" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H19" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I19" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J19" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0027 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0027/executions/EXEC-tenant-10-project-102-0027/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K19" s="8" t="str">
+        <x:v>2026-08-10T02:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0027 taskId=TASK-tenant-10-project-102-0027 executionId=EXEC-tenant-10-project-102-0027 objectId=object-27 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L19" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0027、taskId=TASK-tenant-10-project-102-0027 和 executionId=EXEC-tenant-10-project-102-0027。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0027/executions/EXEC-tenant-10-project-102-0027/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v125 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M19" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N19" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O19" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P19" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q19" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R19" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0027</x:v>
       </x:c>
-      <x:c r="J19" s="19" t="str">
+      <x:c r="S19" s="19" t="str">
         <x:v>UTC 2026-08-10 02:16:00.000</x:v>
       </x:c>
-      <x:c r="K19" s="20" t="n">
+      <x:c r="T19" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L19" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M19" s="8" t="str">
+      <x:c r="U19" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10317,24 +10781,48 @@
         <x:v>INC-tenant-10-project-102-0029</x:v>
       </x:c>
       <x:c r="G20" s="8" t="str">
-        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H20" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I20" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J20" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0029 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0029/executions/EXEC-tenant-10-project-102-0029/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K20" s="8" t="str">
+        <x:v>2026-08-10T02:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0029 taskId=TASK-tenant-10-project-102-0029 executionId=EXEC-tenant-10-project-102-0029 objectId=object-29 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L20" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0029、taskId=TASK-tenant-10-project-102-0029 和 executionId=EXEC-tenant-10-project-102-0029。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0029/executions/EXEC-tenant-10-project-102-0029/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v127 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M20" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N20" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O20" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P20" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q20" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R20" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0029</x:v>
       </x:c>
-      <x:c r="J20" s="19" t="str">
+      <x:c r="S20" s="19" t="str">
         <x:v>UTC 2026-08-10 02:24:00.000</x:v>
       </x:c>
-      <x:c r="K20" s="20" t="n">
+      <x:c r="T20" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L20" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M20" s="8" t="str">
+      <x:c r="U20" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10358,25 +10846,49 @@
         <x:v>INC-tenant-10-project-102-0030</x:v>
       </x:c>
       <x:c r="G21" s="8" t="str">
-        <x:v>DDL_REQUIRED</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H21" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I21" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J21" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0030 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0030/executions/EXEC-tenant-10-project-102-0030/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K21" s="8" t="str">
+        <x:v>2026-08-10T02:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0030 taskId=TASK-tenant-10-project-102-0030 executionId=EXEC-tenant-10-project-102-0030 objectId=object-30 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L21" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0030、taskId=TASK-tenant-10-project-102-0030 和 executionId=EXEC-tenant-10-project-102-0030。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0030/executions/EXEC-tenant-10-project-102-0030/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v128 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M21" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N21" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O21" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P21" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q21" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R21" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0030</x:v>
       </x:c>
-      <x:c r="J21" s="19" t="str">
+      <x:c r="S21" s="19" t="str">
         <x:v>UTC 2026-08-10 02:32:00.000</x:v>
       </x:c>
-      <x:c r="K21" s="20" t="n">
+      <x:c r="T21" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L21" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M21" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U21" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10399,24 +10911,48 @@
         <x:v>INC-tenant-10-project-102-0032</x:v>
       </x:c>
       <x:c r="G22" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H22" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I22" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J22" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0032 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0032/executions/EXEC-tenant-10-project-102-0032/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K22" s="8" t="str">
+        <x:v>2026-08-10T02:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0032 taskId=TASK-tenant-10-project-102-0032 executionId=EXEC-tenant-10-project-102-0032 objectId=object-32 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L22" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0032、taskId=TASK-tenant-10-project-102-0032 和 executionId=EXEC-tenant-10-project-102-0032。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0032/executions/EXEC-tenant-10-project-102-0032/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v130 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M22" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N22" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O22" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P22" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q22" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R22" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0032</x:v>
       </x:c>
-      <x:c r="J22" s="19" t="str">
+      <x:c r="S22" s="19" t="str">
         <x:v>UTC 2026-08-10 02:40:00.000</x:v>
       </x:c>
-      <x:c r="K22" s="20" t="n">
+      <x:c r="T22" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L22" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M22" s="8" t="str">
+      <x:c r="U22" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10440,25 +10976,49 @@
         <x:v>INC-tenant-10-project-102-0033</x:v>
       </x:c>
       <x:c r="G23" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H23" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I23" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J23" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0033 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0033/executions/EXEC-tenant-10-project-102-0033/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K23" s="8" t="str">
+        <x:v>2026-08-10T02:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0033 taskId=TASK-tenant-10-project-102-0033 executionId=EXEC-tenant-10-project-102-0033 objectId=object-01 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L23" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0033、taskId=TASK-tenant-10-project-102-0033 和 executionId=EXEC-tenant-10-project-102-0033。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0033/executions/EXEC-tenant-10-project-102-0033/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v131 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M23" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N23" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O23" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P23" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q23" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R23" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0033</x:v>
       </x:c>
-      <x:c r="J23" s="19" t="str">
+      <x:c r="S23" s="19" t="str">
         <x:v>UTC 2026-08-10 02:48:00.000</x:v>
       </x:c>
-      <x:c r="K23" s="20" t="n">
+      <x:c r="T23" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L23" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M23" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U23" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -10481,25 +11041,49 @@
         <x:v>INC-tenant-10-project-102-0035</x:v>
       </x:c>
       <x:c r="G24" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H24" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I24" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J24" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0035 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0035/executions/EXEC-tenant-10-project-102-0035/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K24" s="8" t="str">
+        <x:v>2026-08-10T02:56:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0035 taskId=TASK-tenant-10-project-102-0035 executionId=EXEC-tenant-10-project-102-0035 objectId=object-03 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L24" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0035、taskId=TASK-tenant-10-project-102-0035 和 executionId=EXEC-tenant-10-project-102-0035。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0035/executions/EXEC-tenant-10-project-102-0035/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v133 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M24" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N24" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O24" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P24" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q24" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R24" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0035</x:v>
       </x:c>
-      <x:c r="J24" s="19" t="str">
+      <x:c r="S24" s="19" t="str">
         <x:v>UTC 2026-08-10 02:56:00.000</x:v>
       </x:c>
-      <x:c r="K24" s="20" t="n">
+      <x:c r="T24" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L24" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M24" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U24" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -10522,24 +11106,48 @@
         <x:v>INC-tenant-10-project-102-0036</x:v>
       </x:c>
       <x:c r="G25" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H25" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I25" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J25" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0036 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0036/executions/EXEC-tenant-10-project-102-0036/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K25" s="8" t="str">
+        <x:v>2026-08-10T03:04:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0036 taskId=TASK-tenant-10-project-102-0036 executionId=EXEC-tenant-10-project-102-0036 objectId=object-04 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L25" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0036、taskId=TASK-tenant-10-project-102-0036 和 executionId=EXEC-tenant-10-project-102-0036。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0036/executions/EXEC-tenant-10-project-102-0036/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v134 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M25" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N25" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O25" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P25" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q25" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R25" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0036</x:v>
       </x:c>
-      <x:c r="J25" s="19" t="str">
+      <x:c r="S25" s="19" t="str">
         <x:v>UTC 2026-08-10 03:04:00.000</x:v>
       </x:c>
-      <x:c r="K25" s="20" t="n">
+      <x:c r="T25" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L25" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M25" s="8" t="str">
+      <x:c r="U25" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10563,24 +11171,48 @@
         <x:v>INC-tenant-10-project-102-0038</x:v>
       </x:c>
       <x:c r="G26" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H26" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I26" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J26" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0038 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0038/executions/EXEC-tenant-10-project-102-0038/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K26" s="8" t="str">
+        <x:v>2026-08-10T03:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0038 taskId=TASK-tenant-10-project-102-0038 executionId=EXEC-tenant-10-project-102-0038 objectId=object-06 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L26" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0038、taskId=TASK-tenant-10-project-102-0038 和 executionId=EXEC-tenant-10-project-102-0038。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0038/executions/EXEC-tenant-10-project-102-0038/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v136 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M26" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N26" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O26" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P26" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q26" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R26" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0038</x:v>
       </x:c>
-      <x:c r="J26" s="19" t="str">
+      <x:c r="S26" s="19" t="str">
         <x:v>UTC 2026-08-10 03:12:00.000</x:v>
       </x:c>
-      <x:c r="K26" s="20" t="n">
+      <x:c r="T26" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L26" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M26" s="8" t="str">
+      <x:c r="U26" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10604,24 +11236,48 @@
         <x:v>INC-tenant-10-project-102-0039</x:v>
       </x:c>
       <x:c r="G27" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H27" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I27" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J27" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0039 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0039/executions/EXEC-tenant-10-project-102-0039/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K27" s="8" t="str">
+        <x:v>2026-08-10T03:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0039 taskId=TASK-tenant-10-project-102-0039 executionId=EXEC-tenant-10-project-102-0039 objectId=object-07 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L27" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0039、taskId=TASK-tenant-10-project-102-0039 和 executionId=EXEC-tenant-10-project-102-0039。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0039/executions/EXEC-tenant-10-project-102-0039/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v137 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M27" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N27" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O27" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P27" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q27" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R27" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0039</x:v>
       </x:c>
-      <x:c r="J27" s="19" t="str">
+      <x:c r="S27" s="19" t="str">
         <x:v>UTC 2026-08-10 03:20:00.000</x:v>
       </x:c>
-      <x:c r="K27" s="20" t="n">
+      <x:c r="T27" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L27" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M27" s="8" t="str">
+      <x:c r="U27" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10645,24 +11301,48 @@
         <x:v>INC-tenant-10-project-102-0041</x:v>
       </x:c>
       <x:c r="G28" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H28" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I28" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J28" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0041 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0041/executions/EXEC-tenant-10-project-102-0041/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K28" s="8" t="str">
+        <x:v>2026-08-10T03:28:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0041 taskId=TASK-tenant-10-project-102-0041 executionId=EXEC-tenant-10-project-102-0041 objectId=object-09 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L28" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0041、taskId=TASK-tenant-10-project-102-0041 和 executionId=EXEC-tenant-10-project-102-0041。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0041/executions/EXEC-tenant-10-project-102-0041/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v139 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M28" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N28" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O28" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P28" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q28" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R28" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0041</x:v>
       </x:c>
-      <x:c r="J28" s="19" t="str">
+      <x:c r="S28" s="19" t="str">
         <x:v>UTC 2026-08-10 03:28:00.000</x:v>
       </x:c>
-      <x:c r="K28" s="20" t="n">
+      <x:c r="T28" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L28" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M28" s="8" t="str">
+      <x:c r="U28" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10686,25 +11366,49 @@
         <x:v>INC-tenant-10-project-102-0042</x:v>
       </x:c>
       <x:c r="G29" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H29" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I29" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J29" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0042 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0042/executions/EXEC-tenant-10-project-102-0042/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K29" s="8" t="str">
+        <x:v>2026-08-10T03:36:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0042 taskId=TASK-tenant-10-project-102-0042 executionId=EXEC-tenant-10-project-102-0042 objectId=object-10 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L29" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0042、taskId=TASK-tenant-10-project-102-0042 和 executionId=EXEC-tenant-10-project-102-0042。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0042/executions/EXEC-tenant-10-project-102-0042/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v140 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M29" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N29" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O29" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P29" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q29" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R29" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0042</x:v>
       </x:c>
-      <x:c r="J29" s="19" t="str">
+      <x:c r="S29" s="19" t="str">
         <x:v>UTC 2026-08-10 03:36:00.000</x:v>
       </x:c>
-      <x:c r="K29" s="20" t="n">
+      <x:c r="T29" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L29" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M29" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U29" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10727,24 +11431,48 @@
         <x:v>INC-tenant-10-project-102-0044</x:v>
       </x:c>
       <x:c r="G30" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H30" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I30" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J30" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0044 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0044/executions/EXEC-tenant-10-project-102-0044/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K30" s="8" t="str">
+        <x:v>2026-08-10T03:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0044 taskId=TASK-tenant-10-project-102-0044 executionId=EXEC-tenant-10-project-102-0044 objectId=object-12 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L30" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0044、taskId=TASK-tenant-10-project-102-0044 和 executionId=EXEC-tenant-10-project-102-0044。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0044/executions/EXEC-tenant-10-project-102-0044/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v142 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M30" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N30" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O30" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P30" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q30" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R30" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0044</x:v>
       </x:c>
-      <x:c r="J30" s="19" t="str">
+      <x:c r="S30" s="19" t="str">
         <x:v>UTC 2026-08-10 03:44:00.000</x:v>
       </x:c>
-      <x:c r="K30" s="20" t="n">
+      <x:c r="T30" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L30" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M30" s="8" t="str">
+      <x:c r="U30" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10768,24 +11496,48 @@
         <x:v>INC-tenant-10-project-102-0045</x:v>
       </x:c>
       <x:c r="G31" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H31" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I31" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J31" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0045 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0045/executions/EXEC-tenant-10-project-102-0045/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K31" s="8" t="str">
+        <x:v>2026-08-10T03:52:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0045 taskId=TASK-tenant-10-project-102-0045 executionId=EXEC-tenant-10-project-102-0045 objectId=object-13 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L31" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0045、taskId=TASK-tenant-10-project-102-0045 和 executionId=EXEC-tenant-10-project-102-0045。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0045/executions/EXEC-tenant-10-project-102-0045/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v143 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M31" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N31" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O31" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P31" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q31" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R31" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0045</x:v>
       </x:c>
-      <x:c r="J31" s="19" t="str">
+      <x:c r="S31" s="19" t="str">
         <x:v>UTC 2026-08-10 03:52:00.000</x:v>
       </x:c>
-      <x:c r="K31" s="20" t="n">
+      <x:c r="T31" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L31" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M31" s="8" t="str">
+      <x:c r="U31" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10809,24 +11561,48 @@
         <x:v>INC-tenant-10-project-102-0047</x:v>
       </x:c>
       <x:c r="G32" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H32" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I32" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J32" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0047 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0047/executions/EXEC-tenant-10-project-102-0047/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K32" s="8" t="str">
+        <x:v>2026-08-10T04:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0047 taskId=TASK-tenant-10-project-102-0047 executionId=EXEC-tenant-10-project-102-0047 objectId=object-15 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L32" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0047、taskId=TASK-tenant-10-project-102-0047 和 executionId=EXEC-tenant-10-project-102-0047。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0047/executions/EXEC-tenant-10-project-102-0047/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v145 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M32" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N32" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O32" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P32" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q32" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R32" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0047</x:v>
       </x:c>
-      <x:c r="J32" s="19" t="str">
+      <x:c r="S32" s="19" t="str">
         <x:v>UTC 2026-08-10 04:00:00.000</x:v>
       </x:c>
-      <x:c r="K32" s="20" t="n">
+      <x:c r="T32" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L32" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M32" s="8" t="str">
+      <x:c r="U32" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10850,24 +11626,48 @@
         <x:v>INC-tenant-10-project-102-0048</x:v>
       </x:c>
       <x:c r="G33" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H33" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I33" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J33" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0048 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0048/executions/EXEC-tenant-10-project-102-0048/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K33" s="8" t="str">
+        <x:v>2026-08-10T04:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0048 taskId=TASK-tenant-10-project-102-0048 executionId=EXEC-tenant-10-project-102-0048 objectId=object-16 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L33" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0048、taskId=TASK-tenant-10-project-102-0048 和 executionId=EXEC-tenant-10-project-102-0048。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0048/executions/EXEC-tenant-10-project-102-0048/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v146 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M33" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N33" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O33" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P33" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q33" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R33" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0048</x:v>
       </x:c>
-      <x:c r="J33" s="19" t="str">
+      <x:c r="S33" s="19" t="str">
         <x:v>UTC 2026-08-10 04:08:00.000</x:v>
       </x:c>
-      <x:c r="K33" s="20" t="n">
+      <x:c r="T33" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L33" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M33" s="8" t="str">
+      <x:c r="U33" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10891,24 +11691,48 @@
         <x:v>INC-tenant-10-project-102-0050</x:v>
       </x:c>
       <x:c r="G34" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H34" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I34" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J34" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0050 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0050/executions/EXEC-tenant-10-project-102-0050/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K34" s="8" t="str">
+        <x:v>2026-08-10T04:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0050 taskId=TASK-tenant-10-project-102-0050 executionId=EXEC-tenant-10-project-102-0050 objectId=object-18 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L34" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0050、taskId=TASK-tenant-10-project-102-0050 和 executionId=EXEC-tenant-10-project-102-0050。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0050/executions/EXEC-tenant-10-project-102-0050/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v148 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M34" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N34" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O34" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P34" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q34" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R34" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0050</x:v>
       </x:c>
-      <x:c r="J34" s="19" t="str">
+      <x:c r="S34" s="19" t="str">
         <x:v>UTC 2026-08-10 04:16:00.000</x:v>
       </x:c>
-      <x:c r="K34" s="20" t="n">
+      <x:c r="T34" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L34" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M34" s="8" t="str">
+      <x:c r="U34" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10932,24 +11756,48 @@
         <x:v>INC-tenant-10-project-102-0051</x:v>
       </x:c>
       <x:c r="G35" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H35" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I35" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J35" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0051 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0051/executions/EXEC-tenant-10-project-102-0051/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K35" s="8" t="str">
+        <x:v>2026-08-10T04:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0051 taskId=TASK-tenant-10-project-102-0051 executionId=EXEC-tenant-10-project-102-0051 objectId=object-19 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L35" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0051、taskId=TASK-tenant-10-project-102-0051 和 executionId=EXEC-tenant-10-project-102-0051。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0051/executions/EXEC-tenant-10-project-102-0051/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v149 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M35" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N35" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O35" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P35" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q35" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R35" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0051</x:v>
       </x:c>
-      <x:c r="J35" s="19" t="str">
+      <x:c r="S35" s="19" t="str">
         <x:v>UTC 2026-08-10 04:24:00.000</x:v>
       </x:c>
-      <x:c r="K35" s="20" t="n">
+      <x:c r="T35" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L35" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M35" s="8" t="str">
+      <x:c r="U35" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -10973,24 +11821,48 @@
         <x:v>INC-tenant-10-project-102-0053</x:v>
       </x:c>
       <x:c r="G36" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H36" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I36" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J36" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0053 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0053/executions/EXEC-tenant-10-project-102-0053/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K36" s="8" t="str">
+        <x:v>2026-08-10T04:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0053 taskId=TASK-tenant-10-project-102-0053 executionId=EXEC-tenant-10-project-102-0053 objectId=object-21 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L36" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0053、taskId=TASK-tenant-10-project-102-0053 和 executionId=EXEC-tenant-10-project-102-0053。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0053/executions/EXEC-tenant-10-project-102-0053/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v151 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M36" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N36" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O36" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P36" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q36" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R36" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0053</x:v>
       </x:c>
-      <x:c r="J36" s="19" t="str">
+      <x:c r="S36" s="19" t="str">
         <x:v>UTC 2026-08-10 04:32:00.000</x:v>
       </x:c>
-      <x:c r="K36" s="20" t="n">
+      <x:c r="T36" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L36" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M36" s="8" t="str">
+      <x:c r="U36" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11014,24 +11886,48 @@
         <x:v>INC-tenant-10-project-102-0054</x:v>
       </x:c>
       <x:c r="G37" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H37" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I37" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J37" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0054 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0054/executions/EXEC-tenant-10-project-102-0054/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K37" s="8" t="str">
+        <x:v>2026-08-10T04:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0054 taskId=TASK-tenant-10-project-102-0054 executionId=EXEC-tenant-10-project-102-0054 objectId=object-22 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L37" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0054、taskId=TASK-tenant-10-project-102-0054 和 executionId=EXEC-tenant-10-project-102-0054。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0054/executions/EXEC-tenant-10-project-102-0054/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v152 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M37" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N37" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O37" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P37" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q37" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R37" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0054</x:v>
       </x:c>
-      <x:c r="J37" s="19" t="str">
+      <x:c r="S37" s="19" t="str">
         <x:v>UTC 2026-08-10 04:40:00.000</x:v>
       </x:c>
-      <x:c r="K37" s="20" t="n">
+      <x:c r="T37" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L37" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M37" s="8" t="str">
+      <x:c r="U37" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11055,24 +11951,48 @@
         <x:v>INC-tenant-10-project-102-0056</x:v>
       </x:c>
       <x:c r="G38" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H38" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I38" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J38" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0056 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0056/executions/EXEC-tenant-10-project-102-0056/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K38" s="8" t="str">
+        <x:v>2026-08-10T04:48:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0056 taskId=TASK-tenant-10-project-102-0056 executionId=EXEC-tenant-10-project-102-0056 objectId=object-24 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L38" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0056、taskId=TASK-tenant-10-project-102-0056 和 executionId=EXEC-tenant-10-project-102-0056。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0056/executions/EXEC-tenant-10-project-102-0056/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v154 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M38" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N38" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O38" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P38" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q38" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R38" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0056</x:v>
       </x:c>
-      <x:c r="J38" s="19" t="str">
+      <x:c r="S38" s="19" t="str">
         <x:v>UTC 2026-08-10 04:48:00.000</x:v>
       </x:c>
-      <x:c r="K38" s="20" t="n">
+      <x:c r="T38" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L38" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M38" s="8" t="str">
+      <x:c r="U38" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11096,24 +12016,48 @@
         <x:v>INC-tenant-10-project-102-0057</x:v>
       </x:c>
       <x:c r="G39" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H39" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I39" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J39" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0057 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0057/executions/EXEC-tenant-10-project-102-0057/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K39" s="8" t="str">
+        <x:v>2026-08-10T04:56:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0057 taskId=TASK-tenant-10-project-102-0057 executionId=EXEC-tenant-10-project-102-0057 objectId=object-25 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L39" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0057、taskId=TASK-tenant-10-project-102-0057 和 executionId=EXEC-tenant-10-project-102-0057。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0057/executions/EXEC-tenant-10-project-102-0057/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v155 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M39" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N39" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O39" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P39" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q39" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R39" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0057</x:v>
       </x:c>
-      <x:c r="J39" s="19" t="str">
+      <x:c r="S39" s="19" t="str">
         <x:v>UTC 2026-08-10 04:56:00.000</x:v>
       </x:c>
-      <x:c r="K39" s="20" t="n">
+      <x:c r="T39" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L39" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M39" s="8" t="str">
+      <x:c r="U39" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11140,21 +12084,45 @@
         <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H40" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I40" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J40" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0059 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0059/executions/EXEC-tenant-10-project-102-0059/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K40" s="8" t="str">
+        <x:v>2026-08-10T05:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0059 taskId=TASK-tenant-10-project-102-0059 executionId=EXEC-tenant-10-project-102-0059 objectId=object-27 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L40" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0059、taskId=TASK-tenant-10-project-102-0059 和 executionId=EXEC-tenant-10-project-102-0059。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0059/executions/EXEC-tenant-10-project-102-0059/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v157 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M40" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N40" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O40" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P40" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q40" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R40" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0059</x:v>
       </x:c>
-      <x:c r="J40" s="19" t="str">
+      <x:c r="S40" s="19" t="str">
         <x:v>UTC 2026-08-10 05:04:00.000</x:v>
       </x:c>
-      <x:c r="K40" s="20" t="n">
+      <x:c r="T40" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L40" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M40" s="8" t="str">
+      <x:c r="U40" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11181,21 +12149,45 @@
         <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H41" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I41" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J41" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0060 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0060/executions/EXEC-tenant-10-project-102-0060/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K41" s="8" t="str">
+        <x:v>2026-08-10T05:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0060 taskId=TASK-tenant-10-project-102-0060 executionId=EXEC-tenant-10-project-102-0060 objectId=object-28 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L41" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0060、taskId=TASK-tenant-10-project-102-0060 和 executionId=EXEC-tenant-10-project-102-0060。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0060/executions/EXEC-tenant-10-project-102-0060/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v158 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M41" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N41" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O41" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P41" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q41" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R41" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0060</x:v>
       </x:c>
-      <x:c r="J41" s="19" t="str">
+      <x:c r="S41" s="19" t="str">
         <x:v>UTC 2026-08-10 05:12:00.000</x:v>
       </x:c>
-      <x:c r="K41" s="20" t="n">
+      <x:c r="T41" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L41" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M41" s="8" t="str">
+      <x:c r="U41" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -11219,25 +12211,49 @@
         <x:v>INC-tenant-10-project-102-0062</x:v>
       </x:c>
       <x:c r="G42" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H42" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I42" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J42" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0062 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0062/executions/EXEC-tenant-10-project-102-0062/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K42" s="8" t="str">
+        <x:v>2026-08-10T05:20:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0062 taskId=TASK-tenant-10-project-102-0062 executionId=EXEC-tenant-10-project-102-0062 objectId=object-30 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L42" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0062、taskId=TASK-tenant-10-project-102-0062 和 executionId=EXEC-tenant-10-project-102-0062。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0062/executions/EXEC-tenant-10-project-102-0062/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v160 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M42" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N42" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O42" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P42" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q42" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R42" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0062</x:v>
       </x:c>
-      <x:c r="J42" s="19" t="str">
+      <x:c r="S42" s="19" t="str">
         <x:v>UTC 2026-08-10 05:20:00.000</x:v>
       </x:c>
-      <x:c r="K42" s="20" t="n">
+      <x:c r="T42" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L42" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M42" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U42" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11260,24 +12276,48 @@
         <x:v>INC-tenant-10-project-102-0063</x:v>
       </x:c>
       <x:c r="G43" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H43" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I43" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J43" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0063 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0063/executions/EXEC-tenant-10-project-102-0063/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K43" s="8" t="str">
+        <x:v>2026-08-10T05:28:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0063 taskId=TASK-tenant-10-project-102-0063 executionId=EXEC-tenant-10-project-102-0063 objectId=object-31 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L43" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0063、taskId=TASK-tenant-10-project-102-0063 和 executionId=EXEC-tenant-10-project-102-0063。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0063/executions/EXEC-tenant-10-project-102-0063/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v161 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M43" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N43" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O43" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P43" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q43" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R43" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0063</x:v>
       </x:c>
-      <x:c r="J43" s="19" t="str">
+      <x:c r="S43" s="19" t="str">
         <x:v>UTC 2026-08-10 05:28:00.000</x:v>
       </x:c>
-      <x:c r="K43" s="20" t="n">
+      <x:c r="T43" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L43" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M43" s="8" t="str">
+      <x:c r="U43" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -11301,25 +12341,49 @@
         <x:v>INC-tenant-10-project-102-0065</x:v>
       </x:c>
       <x:c r="G44" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H44" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I44" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J44" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0065 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0065/executions/EXEC-tenant-10-project-102-0065/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K44" s="8" t="str">
+        <x:v>2026-08-10T05:36:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0065 taskId=TASK-tenant-10-project-102-0065 executionId=EXEC-tenant-10-project-102-0065 objectId=object-01 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L44" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0065、taskId=TASK-tenant-10-project-102-0065 和 executionId=EXEC-tenant-10-project-102-0065。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0065/executions/EXEC-tenant-10-project-102-0065/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v163 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M44" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N44" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O44" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P44" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q44" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R44" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0065</x:v>
       </x:c>
-      <x:c r="J44" s="19" t="str">
+      <x:c r="S44" s="19" t="str">
         <x:v>UTC 2026-08-10 05:36:00.000</x:v>
       </x:c>
-      <x:c r="K44" s="20" t="n">
+      <x:c r="T44" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L44" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M44" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U44" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -11342,24 +12406,48 @@
         <x:v>INC-tenant-10-project-102-0066</x:v>
       </x:c>
       <x:c r="G45" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H45" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I45" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J45" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0066 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0066/executions/EXEC-tenant-10-project-102-0066/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K45" s="8" t="str">
+        <x:v>2026-08-10T05:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0066 taskId=TASK-tenant-10-project-102-0066 executionId=EXEC-tenant-10-project-102-0066 objectId=object-02 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L45" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0066、taskId=TASK-tenant-10-project-102-0066 和 executionId=EXEC-tenant-10-project-102-0066。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0066/executions/EXEC-tenant-10-project-102-0066/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v164 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M45" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N45" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O45" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P45" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q45" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R45" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0066</x:v>
       </x:c>
-      <x:c r="J45" s="19" t="str">
+      <x:c r="S45" s="19" t="str">
         <x:v>UTC 2026-08-10 05:44:00.000</x:v>
       </x:c>
-      <x:c r="K45" s="20" t="n">
+      <x:c r="T45" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L45" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M45" s="8" t="str">
+      <x:c r="U45" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11383,24 +12471,48 @@
         <x:v>INC-tenant-10-project-102-0068</x:v>
       </x:c>
       <x:c r="G46" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H46" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I46" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J46" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0068 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0068/executions/EXEC-tenant-10-project-102-0068/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K46" s="8" t="str">
+        <x:v>2026-08-10T05:52:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0068 taskId=TASK-tenant-10-project-102-0068 executionId=EXEC-tenant-10-project-102-0068 objectId=object-04 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L46" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0068、taskId=TASK-tenant-10-project-102-0068 和 executionId=EXEC-tenant-10-project-102-0068。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0068/executions/EXEC-tenant-10-project-102-0068/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v166 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M46" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N46" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O46" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P46" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q46" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R46" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0068</x:v>
       </x:c>
-      <x:c r="J46" s="19" t="str">
+      <x:c r="S46" s="19" t="str">
         <x:v>UTC 2026-08-10 05:52:00.000</x:v>
       </x:c>
-      <x:c r="K46" s="20" t="n">
+      <x:c r="T46" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L46" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M46" s="8" t="str">
+      <x:c r="U46" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11424,24 +12536,48 @@
         <x:v>INC-tenant-10-project-102-0069</x:v>
       </x:c>
       <x:c r="G47" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H47" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I47" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J47" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0069 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0069/executions/EXEC-tenant-10-project-102-0069/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K47" s="8" t="str">
+        <x:v>2026-08-10T06:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0069 taskId=TASK-tenant-10-project-102-0069 executionId=EXEC-tenant-10-project-102-0069 objectId=object-05 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L47" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0069、taskId=TASK-tenant-10-project-102-0069 和 executionId=EXEC-tenant-10-project-102-0069。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0069/executions/EXEC-tenant-10-project-102-0069/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v167 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M47" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N47" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O47" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P47" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q47" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R47" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0069</x:v>
       </x:c>
-      <x:c r="J47" s="19" t="str">
+      <x:c r="S47" s="19" t="str">
         <x:v>UTC 2026-08-10 06:00:00.000</x:v>
       </x:c>
-      <x:c r="K47" s="20" t="n">
+      <x:c r="T47" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L47" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M47" s="8" t="str">
+      <x:c r="U47" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11465,24 +12601,48 @@
         <x:v>INC-tenant-10-project-102-0071</x:v>
       </x:c>
       <x:c r="G48" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H48" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I48" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J48" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0071 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0071/executions/EXEC-tenant-10-project-102-0071/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K48" s="8" t="str">
+        <x:v>2026-08-10T06:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0071 taskId=TASK-tenant-10-project-102-0071 executionId=EXEC-tenant-10-project-102-0071 objectId=object-07 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L48" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0071、taskId=TASK-tenant-10-project-102-0071 和 executionId=EXEC-tenant-10-project-102-0071。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0071/executions/EXEC-tenant-10-project-102-0071/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v169 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M48" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N48" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O48" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P48" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q48" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R48" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0071</x:v>
       </x:c>
-      <x:c r="J48" s="19" t="str">
+      <x:c r="S48" s="19" t="str">
         <x:v>UTC 2026-08-10 06:08:00.000</x:v>
       </x:c>
-      <x:c r="K48" s="20" t="n">
+      <x:c r="T48" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L48" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M48" s="8" t="str">
+      <x:c r="U48" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11506,24 +12666,48 @@
         <x:v>INC-tenant-10-project-102-0072</x:v>
       </x:c>
       <x:c r="G49" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H49" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I49" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J49" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0072 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0072/executions/EXEC-tenant-10-project-102-0072/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K49" s="8" t="str">
+        <x:v>2026-08-10T06:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0072 taskId=TASK-tenant-10-project-102-0072 executionId=EXEC-tenant-10-project-102-0072 objectId=object-08 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L49" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0072、taskId=TASK-tenant-10-project-102-0072 和 executionId=EXEC-tenant-10-project-102-0072。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0072/executions/EXEC-tenant-10-project-102-0072/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v170 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M49" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N49" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O49" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P49" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q49" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R49" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0072</x:v>
       </x:c>
-      <x:c r="J49" s="19" t="str">
+      <x:c r="S49" s="19" t="str">
         <x:v>UTC 2026-08-10 06:16:00.000</x:v>
       </x:c>
-      <x:c r="K49" s="20" t="n">
+      <x:c r="T49" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L49" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M49" s="8" t="str">
+      <x:c r="U49" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11547,24 +12731,48 @@
         <x:v>INC-tenant-10-project-102-0074</x:v>
       </x:c>
       <x:c r="G50" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H50" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I50" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J50" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0074 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0074/executions/EXEC-tenant-10-project-102-0074/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K50" s="8" t="str">
+        <x:v>2026-08-10T06:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0074 taskId=TASK-tenant-10-project-102-0074 executionId=EXEC-tenant-10-project-102-0074 objectId=object-10 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L50" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0074、taskId=TASK-tenant-10-project-102-0074 和 executionId=EXEC-tenant-10-project-102-0074。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0074/executions/EXEC-tenant-10-project-102-0074/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v172 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M50" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N50" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O50" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P50" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q50" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R50" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0074</x:v>
       </x:c>
-      <x:c r="J50" s="19" t="str">
+      <x:c r="S50" s="19" t="str">
         <x:v>UTC 2026-08-10 06:24:00.000</x:v>
       </x:c>
-      <x:c r="K50" s="20" t="n">
+      <x:c r="T50" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L50" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M50" s="8" t="str">
+      <x:c r="U50" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11588,24 +12796,48 @@
         <x:v>INC-tenant-10-project-102-0075</x:v>
       </x:c>
       <x:c r="G51" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H51" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I51" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J51" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0075 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0075/executions/EXEC-tenant-10-project-102-0075/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K51" s="8" t="str">
+        <x:v>2026-08-10T06:32:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0075 taskId=TASK-tenant-10-project-102-0075 executionId=EXEC-tenant-10-project-102-0075 objectId=object-11 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L51" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0075、taskId=TASK-tenant-10-project-102-0075 和 executionId=EXEC-tenant-10-project-102-0075。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0075/executions/EXEC-tenant-10-project-102-0075/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v173 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M51" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N51" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O51" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P51" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q51" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R51" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0075</x:v>
       </x:c>
-      <x:c r="J51" s="19" t="str">
+      <x:c r="S51" s="19" t="str">
         <x:v>UTC 2026-08-10 06:32:00.000</x:v>
       </x:c>
-      <x:c r="K51" s="20" t="n">
+      <x:c r="T51" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L51" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M51" s="8" t="str">
+      <x:c r="U51" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11629,24 +12861,48 @@
         <x:v>INC-tenant-10-project-102-0077</x:v>
       </x:c>
       <x:c r="G52" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H52" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I52" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J52" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0077 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0077/executions/EXEC-tenant-10-project-102-0077/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K52" s="8" t="str">
+        <x:v>2026-08-10T06:40:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0077 taskId=TASK-tenant-10-project-102-0077 executionId=EXEC-tenant-10-project-102-0077 objectId=object-13 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L52" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0077、taskId=TASK-tenant-10-project-102-0077 和 executionId=EXEC-tenant-10-project-102-0077。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0077/executions/EXEC-tenant-10-project-102-0077/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v175 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M52" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N52" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O52" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P52" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q52" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R52" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0077</x:v>
       </x:c>
-      <x:c r="J52" s="19" t="str">
+      <x:c r="S52" s="19" t="str">
         <x:v>UTC 2026-08-10 06:40:00.000</x:v>
       </x:c>
-      <x:c r="K52" s="20" t="n">
+      <x:c r="T52" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L52" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M52" s="8" t="str">
+      <x:c r="U52" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11670,24 +12926,48 @@
         <x:v>INC-tenant-10-project-102-0078</x:v>
       </x:c>
       <x:c r="G53" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H53" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I53" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J53" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0078 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0078/executions/EXEC-tenant-10-project-102-0078/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K53" s="8" t="str">
+        <x:v>2026-08-10T06:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0078 taskId=TASK-tenant-10-project-102-0078 executionId=EXEC-tenant-10-project-102-0078 objectId=object-14 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L53" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0078、taskId=TASK-tenant-10-project-102-0078 和 executionId=EXEC-tenant-10-project-102-0078。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0078/executions/EXEC-tenant-10-project-102-0078/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v176 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M53" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N53" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O53" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P53" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q53" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R53" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0078</x:v>
       </x:c>
-      <x:c r="J53" s="19" t="str">
+      <x:c r="S53" s="19" t="str">
         <x:v>UTC 2026-08-10 06:48:00.000</x:v>
       </x:c>
-      <x:c r="K53" s="20" t="n">
+      <x:c r="T53" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L53" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M53" s="8" t="str">
+      <x:c r="U53" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11711,25 +12991,49 @@
         <x:v>INC-tenant-10-project-102-0080</x:v>
       </x:c>
       <x:c r="G54" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H54" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I54" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J54" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0080 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0080/executions/EXEC-tenant-10-project-102-0080/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K54" s="8" t="str">
+        <x:v>2026-08-10T06:56:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0080 taskId=TASK-tenant-10-project-102-0080 executionId=EXEC-tenant-10-project-102-0080 objectId=object-16 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L54" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0080、taskId=TASK-tenant-10-project-102-0080 和 executionId=EXEC-tenant-10-project-102-0080。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0080/executions/EXEC-tenant-10-project-102-0080/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v178 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M54" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N54" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O54" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P54" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q54" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R54" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0080</x:v>
       </x:c>
-      <x:c r="J54" s="19" t="str">
+      <x:c r="S54" s="19" t="str">
         <x:v>UTC 2026-08-10 06:56:00.000</x:v>
       </x:c>
-      <x:c r="K54" s="20" t="n">
+      <x:c r="T54" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L54" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M54" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U54" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -11752,24 +13056,48 @@
         <x:v>INC-tenant-10-project-102-0081</x:v>
       </x:c>
       <x:c r="G55" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H55" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I55" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J55" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0081 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0081/executions/EXEC-tenant-10-project-102-0081/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K55" s="8" t="str">
+        <x:v>2026-08-10T07:04:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0081 taskId=TASK-tenant-10-project-102-0081 executionId=EXEC-tenant-10-project-102-0081 objectId=object-17 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L55" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0081、taskId=TASK-tenant-10-project-102-0081 和 executionId=EXEC-tenant-10-project-102-0081。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0081/executions/EXEC-tenant-10-project-102-0081/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v179 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M55" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N55" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O55" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P55" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q55" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R55" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0081</x:v>
       </x:c>
-      <x:c r="J55" s="19" t="str">
+      <x:c r="S55" s="19" t="str">
         <x:v>UTC 2026-08-10 07:04:00.000</x:v>
       </x:c>
-      <x:c r="K55" s="20" t="n">
+      <x:c r="T55" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L55" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M55" s="8" t="str">
+      <x:c r="U55" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11793,25 +13121,49 @@
         <x:v>INC-tenant-10-project-102-0083</x:v>
       </x:c>
       <x:c r="G56" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H56" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I56" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J56" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0083 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0083/executions/EXEC-tenant-10-project-102-0083/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K56" s="8" t="str">
+        <x:v>2026-08-10T07:12:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0083 taskId=TASK-tenant-10-project-102-0083 executionId=EXEC-tenant-10-project-102-0083 objectId=object-19 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L56" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0083、taskId=TASK-tenant-10-project-102-0083 和 executionId=EXEC-tenant-10-project-102-0083。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0083/executions/EXEC-tenant-10-project-102-0083/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v181 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M56" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N56" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O56" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P56" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q56" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R56" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0083</x:v>
       </x:c>
-      <x:c r="J56" s="19" t="str">
+      <x:c r="S56" s="19" t="str">
         <x:v>UTC 2026-08-10 07:12:00.000</x:v>
       </x:c>
-      <x:c r="K56" s="20" t="n">
+      <x:c r="T56" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L56" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M56" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U56" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -11834,24 +13186,48 @@
         <x:v>INC-tenant-10-project-102-0084</x:v>
       </x:c>
       <x:c r="G57" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H57" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I57" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J57" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0084 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0084/executions/EXEC-tenant-10-project-102-0084/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K57" s="8" t="str">
+        <x:v>2026-08-10T07:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0084 taskId=TASK-tenant-10-project-102-0084 executionId=EXEC-tenant-10-project-102-0084 objectId=object-20 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L57" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0084、taskId=TASK-tenant-10-project-102-0084 和 executionId=EXEC-tenant-10-project-102-0084。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0084/executions/EXEC-tenant-10-project-102-0084/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v182 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M57" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N57" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O57" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P57" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q57" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R57" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0084</x:v>
       </x:c>
-      <x:c r="J57" s="19" t="str">
+      <x:c r="S57" s="19" t="str">
         <x:v>UTC 2026-08-10 07:20:00.000</x:v>
       </x:c>
-      <x:c r="K57" s="20" t="n">
+      <x:c r="T57" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L57" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M57" s="8" t="str">
+      <x:c r="U57" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11875,24 +13251,48 @@
         <x:v>INC-tenant-10-project-102-0086</x:v>
       </x:c>
       <x:c r="G58" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H58" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I58" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J58" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0086 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0086/executions/EXEC-tenant-10-project-102-0086/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K58" s="8" t="str">
+        <x:v>2026-08-10T07:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0086 taskId=TASK-tenant-10-project-102-0086 executionId=EXEC-tenant-10-project-102-0086 objectId=object-22 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L58" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0086、taskId=TASK-tenant-10-project-102-0086 和 executionId=EXEC-tenant-10-project-102-0086。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0086/executions/EXEC-tenant-10-project-102-0086/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v184 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M58" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N58" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O58" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P58" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q58" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R58" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0086</x:v>
       </x:c>
-      <x:c r="J58" s="19" t="str">
+      <x:c r="S58" s="19" t="str">
         <x:v>UTC 2026-08-10 07:28:00.000</x:v>
       </x:c>
-      <x:c r="K58" s="20" t="n">
+      <x:c r="T58" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L58" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M58" s="8" t="str">
+      <x:c r="U58" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11916,24 +13316,48 @@
         <x:v>INC-tenant-10-project-102-0087</x:v>
       </x:c>
       <x:c r="G59" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H59" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I59" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J59" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0087 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0087/executions/EXEC-tenant-10-project-102-0087/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K59" s="8" t="str">
+        <x:v>2026-08-10T07:36:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0087 taskId=TASK-tenant-10-project-102-0087 executionId=EXEC-tenant-10-project-102-0087 objectId=object-23 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L59" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0087、taskId=TASK-tenant-10-project-102-0087 和 executionId=EXEC-tenant-10-project-102-0087。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0087/executions/EXEC-tenant-10-project-102-0087/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v185 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M59" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N59" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O59" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P59" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q59" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R59" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0087</x:v>
       </x:c>
-      <x:c r="J59" s="19" t="str">
+      <x:c r="S59" s="19" t="str">
         <x:v>UTC 2026-08-10 07:36:00.000</x:v>
       </x:c>
-      <x:c r="K59" s="20" t="n">
+      <x:c r="T59" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L59" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M59" s="8" t="str">
+      <x:c r="U59" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11957,24 +13381,48 @@
         <x:v>INC-tenant-10-project-102-0089</x:v>
       </x:c>
       <x:c r="G60" s="8" t="str">
-        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H60" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I60" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J60" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0089 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0089/executions/EXEC-tenant-10-project-102-0089/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K60" s="8" t="str">
+        <x:v>2026-08-10T07:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0089 taskId=TASK-tenant-10-project-102-0089 executionId=EXEC-tenant-10-project-102-0089 objectId=object-25 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L60" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0089、taskId=TASK-tenant-10-project-102-0089 和 executionId=EXEC-tenant-10-project-102-0089。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0089/executions/EXEC-tenant-10-project-102-0089/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v187 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M60" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N60" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O60" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P60" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q60" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R60" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0089</x:v>
       </x:c>
-      <x:c r="J60" s="19" t="str">
+      <x:c r="S60" s="19" t="str">
         <x:v>UTC 2026-08-10 07:44:00.000</x:v>
       </x:c>
-      <x:c r="K60" s="20" t="n">
+      <x:c r="T60" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L60" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M60" s="8" t="str">
+      <x:c r="U60" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -11998,25 +13446,49 @@
         <x:v>INC-tenant-10-project-102-0090</x:v>
       </x:c>
       <x:c r="G61" s="8" t="str">
-        <x:v>DDL_REQUIRED</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H61" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I61" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J61" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0090 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0090/executions/EXEC-tenant-10-project-102-0090/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K61" s="8" t="str">
+        <x:v>2026-08-10T07:52:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0090 taskId=TASK-tenant-10-project-102-0090 executionId=EXEC-tenant-10-project-102-0090 objectId=object-26 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L61" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0090、taskId=TASK-tenant-10-project-102-0090 和 executionId=EXEC-tenant-10-project-102-0090。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0090/executions/EXEC-tenant-10-project-102-0090/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v188 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M61" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N61" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O61" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P61" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q61" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R61" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0090</x:v>
       </x:c>
-      <x:c r="J61" s="19" t="str">
+      <x:c r="S61" s="19" t="str">
         <x:v>UTC 2026-08-10 07:52:00.000</x:v>
       </x:c>
-      <x:c r="K61" s="20" t="n">
+      <x:c r="T61" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L61" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M61" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U61" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -12039,24 +13511,48 @@
         <x:v>INC-tenant-10-project-102-0092</x:v>
       </x:c>
       <x:c r="G62" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H62" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I62" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J62" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0092 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0092/executions/EXEC-tenant-10-project-102-0092/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K62" s="8" t="str">
+        <x:v>2026-08-10T08:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0092 taskId=TASK-tenant-10-project-102-0092 executionId=EXEC-tenant-10-project-102-0092 objectId=object-28 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L62" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0092、taskId=TASK-tenant-10-project-102-0092 和 executionId=EXEC-tenant-10-project-102-0092。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0092/executions/EXEC-tenant-10-project-102-0092/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v190 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M62" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N62" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O62" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P62" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q62" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R62" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0092</x:v>
       </x:c>
-      <x:c r="J62" s="19" t="str">
+      <x:c r="S62" s="19" t="str">
         <x:v>UTC 2026-08-10 08:00:00.000</x:v>
       </x:c>
-      <x:c r="K62" s="20" t="n">
+      <x:c r="T62" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L62" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M62" s="8" t="str">
+      <x:c r="U62" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12080,25 +13576,49 @@
         <x:v>INC-tenant-10-project-102-0093</x:v>
       </x:c>
       <x:c r="G63" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H63" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I63" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J63" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0093 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0093/executions/EXEC-tenant-10-project-102-0093/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K63" s="8" t="str">
+        <x:v>2026-08-10T08:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0093 taskId=TASK-tenant-10-project-102-0093 executionId=EXEC-tenant-10-project-102-0093 objectId=object-29 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L63" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0093、taskId=TASK-tenant-10-project-102-0093 和 executionId=EXEC-tenant-10-project-102-0093。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0093/executions/EXEC-tenant-10-project-102-0093/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v191 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M63" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N63" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O63" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P63" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q63" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R63" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0093</x:v>
       </x:c>
-      <x:c r="J63" s="19" t="str">
+      <x:c r="S63" s="19" t="str">
         <x:v>UTC 2026-08-10 08:08:00.000</x:v>
       </x:c>
-      <x:c r="K63" s="20" t="n">
+      <x:c r="T63" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L63" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M63" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U63" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -12121,25 +13641,49 @@
         <x:v>INC-tenant-10-project-102-0095</x:v>
       </x:c>
       <x:c r="G64" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H64" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I64" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J64" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0095 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0095/executions/EXEC-tenant-10-project-102-0095/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K64" s="8" t="str">
+        <x:v>2026-08-10T08:16:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0095 taskId=TASK-tenant-10-project-102-0095 executionId=EXEC-tenant-10-project-102-0095 objectId=object-31 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L64" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0095、taskId=TASK-tenant-10-project-102-0095 和 executionId=EXEC-tenant-10-project-102-0095。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0095/executions/EXEC-tenant-10-project-102-0095/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v193 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M64" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N64" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O64" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P64" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q64" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R64" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0095</x:v>
       </x:c>
-      <x:c r="J64" s="19" t="str">
+      <x:c r="S64" s="19" t="str">
         <x:v>UTC 2026-08-10 08:16:00.000</x:v>
       </x:c>
-      <x:c r="K64" s="20" t="n">
+      <x:c r="T64" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L64" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M64" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U64" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -12162,24 +13706,48 @@
         <x:v>INC-tenant-10-project-102-0096</x:v>
       </x:c>
       <x:c r="G65" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H65" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I65" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J65" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0096 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0096/executions/EXEC-tenant-10-project-102-0096/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K65" s="8" t="str">
+        <x:v>2026-08-10T08:24:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0096 taskId=TASK-tenant-10-project-102-0096 executionId=EXEC-tenant-10-project-102-0096 objectId=object-32 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L65" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0096、taskId=TASK-tenant-10-project-102-0096 和 executionId=EXEC-tenant-10-project-102-0096。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0096/executions/EXEC-tenant-10-project-102-0096/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v194 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M65" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N65" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O65" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P65" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q65" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R65" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0096</x:v>
       </x:c>
-      <x:c r="J65" s="19" t="str">
+      <x:c r="S65" s="19" t="str">
         <x:v>UTC 2026-08-10 08:24:00.000</x:v>
       </x:c>
-      <x:c r="K65" s="20" t="n">
+      <x:c r="T65" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L65" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M65" s="8" t="str">
+      <x:c r="U65" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12203,24 +13771,48 @@
         <x:v>INC-tenant-10-project-102-0098</x:v>
       </x:c>
       <x:c r="G66" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H66" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I66" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J66" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0098 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0098/executions/EXEC-tenant-10-project-102-0098/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K66" s="8" t="str">
+        <x:v>2026-08-10T08:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0098 taskId=TASK-tenant-10-project-102-0098 executionId=EXEC-tenant-10-project-102-0098 objectId=object-02 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L66" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0098、taskId=TASK-tenant-10-project-102-0098 和 executionId=EXEC-tenant-10-project-102-0098。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0098/executions/EXEC-tenant-10-project-102-0098/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v196 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M66" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N66" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O66" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P66" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q66" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R66" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0098</x:v>
       </x:c>
-      <x:c r="J66" s="19" t="str">
+      <x:c r="S66" s="19" t="str">
         <x:v>UTC 2026-08-10 08:32:00.000</x:v>
       </x:c>
-      <x:c r="K66" s="20" t="n">
+      <x:c r="T66" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L66" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M66" s="8" t="str">
+      <x:c r="U66" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12244,24 +13836,48 @@
         <x:v>INC-tenant-10-project-102-0099</x:v>
       </x:c>
       <x:c r="G67" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H67" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I67" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J67" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0099 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0099/executions/EXEC-tenant-10-project-102-0099/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K67" s="8" t="str">
+        <x:v>2026-08-10T08:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0099 taskId=TASK-tenant-10-project-102-0099 executionId=EXEC-tenant-10-project-102-0099 objectId=object-03 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L67" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0099、taskId=TASK-tenant-10-project-102-0099 和 executionId=EXEC-tenant-10-project-102-0099。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0099/executions/EXEC-tenant-10-project-102-0099/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v197 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M67" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N67" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O67" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P67" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q67" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R67" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0099</x:v>
       </x:c>
-      <x:c r="J67" s="19" t="str">
+      <x:c r="S67" s="19" t="str">
         <x:v>UTC 2026-08-10 08:40:00.000</x:v>
       </x:c>
-      <x:c r="K67" s="20" t="n">
+      <x:c r="T67" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L67" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M67" s="8" t="str">
+      <x:c r="U67" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12285,24 +13901,48 @@
         <x:v>INC-tenant-10-project-102-0101</x:v>
       </x:c>
       <x:c r="G68" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H68" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I68" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J68" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0101 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0101/executions/EXEC-tenant-10-project-102-0101/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K68" s="8" t="str">
+        <x:v>2026-08-10T08:48:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0101 taskId=TASK-tenant-10-project-102-0101 executionId=EXEC-tenant-10-project-102-0101 objectId=object-05 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L68" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0101、taskId=TASK-tenant-10-project-102-0101 和 executionId=EXEC-tenant-10-project-102-0101。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0101/executions/EXEC-tenant-10-project-102-0101/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v199 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M68" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N68" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O68" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P68" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q68" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R68" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0101</x:v>
       </x:c>
-      <x:c r="J68" s="19" t="str">
+      <x:c r="S68" s="19" t="str">
         <x:v>UTC 2026-08-10 08:48:00.000</x:v>
       </x:c>
-      <x:c r="K68" s="20" t="n">
+      <x:c r="T68" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L68" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M68" s="8" t="str">
+      <x:c r="U68" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12326,25 +13966,49 @@
         <x:v>INC-tenant-10-project-102-0102</x:v>
       </x:c>
       <x:c r="G69" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H69" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I69" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J69" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0102 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0102/executions/EXEC-tenant-10-project-102-0102/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K69" s="8" t="str">
+        <x:v>2026-08-10T08:56:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0102 taskId=TASK-tenant-10-project-102-0102 executionId=EXEC-tenant-10-project-102-0102 objectId=object-06 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L69" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0102、taskId=TASK-tenant-10-project-102-0102 和 executionId=EXEC-tenant-10-project-102-0102。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0102/executions/EXEC-tenant-10-project-102-0102/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v200 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M69" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N69" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O69" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P69" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q69" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R69" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0102</x:v>
       </x:c>
-      <x:c r="J69" s="19" t="str">
+      <x:c r="S69" s="19" t="str">
         <x:v>UTC 2026-08-10 08:56:00.000</x:v>
       </x:c>
-      <x:c r="K69" s="20" t="n">
+      <x:c r="T69" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L69" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M69" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U69" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -12367,24 +14031,48 @@
         <x:v>INC-tenant-10-project-102-0104</x:v>
       </x:c>
       <x:c r="G70" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H70" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I70" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J70" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0104 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0104/executions/EXEC-tenant-10-project-102-0104/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K70" s="8" t="str">
+        <x:v>2026-08-10T09:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0104 taskId=TASK-tenant-10-project-102-0104 executionId=EXEC-tenant-10-project-102-0104 objectId=object-08 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L70" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0104、taskId=TASK-tenant-10-project-102-0104 和 executionId=EXEC-tenant-10-project-102-0104。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0104/executions/EXEC-tenant-10-project-102-0104/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v202 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M70" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N70" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O70" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P70" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q70" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R70" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0104</x:v>
       </x:c>
-      <x:c r="J70" s="19" t="str">
+      <x:c r="S70" s="19" t="str">
         <x:v>UTC 2026-08-10 09:04:00.000</x:v>
       </x:c>
-      <x:c r="K70" s="20" t="n">
+      <x:c r="T70" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L70" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M70" s="8" t="str">
+      <x:c r="U70" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12408,24 +14096,48 @@
         <x:v>INC-tenant-10-project-102-0105</x:v>
       </x:c>
       <x:c r="G71" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H71" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I71" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J71" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0105 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0105/executions/EXEC-tenant-10-project-102-0105/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K71" s="8" t="str">
+        <x:v>2026-08-10T09:12:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0105 taskId=TASK-tenant-10-project-102-0105 executionId=EXEC-tenant-10-project-102-0105 objectId=object-09 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L71" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0105、taskId=TASK-tenant-10-project-102-0105 和 executionId=EXEC-tenant-10-project-102-0105。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0105/executions/EXEC-tenant-10-project-102-0105/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v203 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M71" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N71" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O71" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P71" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q71" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R71" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0105</x:v>
       </x:c>
-      <x:c r="J71" s="19" t="str">
+      <x:c r="S71" s="19" t="str">
         <x:v>UTC 2026-08-10 09:12:00.000</x:v>
       </x:c>
-      <x:c r="K71" s="20" t="n">
+      <x:c r="T71" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L71" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M71" s="8" t="str">
+      <x:c r="U71" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12449,24 +14161,48 @@
         <x:v>INC-tenant-10-project-102-0107</x:v>
       </x:c>
       <x:c r="G72" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H72" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I72" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J72" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0107 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0107/executions/EXEC-tenant-10-project-102-0107/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K72" s="8" t="str">
+        <x:v>2026-08-10T09:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0107 taskId=TASK-tenant-10-project-102-0107 executionId=EXEC-tenant-10-project-102-0107 objectId=object-11 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L72" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0107、taskId=TASK-tenant-10-project-102-0107 和 executionId=EXEC-tenant-10-project-102-0107。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0107/executions/EXEC-tenant-10-project-102-0107/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v205 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M72" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N72" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O72" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P72" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q72" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R72" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0107</x:v>
       </x:c>
-      <x:c r="J72" s="19" t="str">
+      <x:c r="S72" s="19" t="str">
         <x:v>UTC 2026-08-10 09:20:00.000</x:v>
       </x:c>
-      <x:c r="K72" s="20" t="n">
+      <x:c r="T72" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L72" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M72" s="8" t="str">
+      <x:c r="U72" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12490,24 +14226,48 @@
         <x:v>INC-tenant-10-project-102-0108</x:v>
       </x:c>
       <x:c r="G73" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H73" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I73" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J73" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0108 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0108/executions/EXEC-tenant-10-project-102-0108/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K73" s="8" t="str">
+        <x:v>2026-08-10T09:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0108 taskId=TASK-tenant-10-project-102-0108 executionId=EXEC-tenant-10-project-102-0108 objectId=object-12 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L73" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0108、taskId=TASK-tenant-10-project-102-0108 和 executionId=EXEC-tenant-10-project-102-0108。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0108/executions/EXEC-tenant-10-project-102-0108/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v206 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M73" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N73" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O73" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P73" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q73" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R73" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0108</x:v>
       </x:c>
-      <x:c r="J73" s="19" t="str">
+      <x:c r="S73" s="19" t="str">
         <x:v>UTC 2026-08-10 09:28:00.000</x:v>
       </x:c>
-      <x:c r="K73" s="20" t="n">
+      <x:c r="T73" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L73" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M73" s="8" t="str">
+      <x:c r="U73" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12531,24 +14291,48 @@
         <x:v>INC-tenant-10-project-102-0110</x:v>
       </x:c>
       <x:c r="G74" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H74" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I74" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J74" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0110 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0110/executions/EXEC-tenant-10-project-102-0110/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K74" s="8" t="str">
+        <x:v>2026-08-10T09:36:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0110 taskId=TASK-tenant-10-project-102-0110 executionId=EXEC-tenant-10-project-102-0110 objectId=object-14 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L74" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0110、taskId=TASK-tenant-10-project-102-0110 和 executionId=EXEC-tenant-10-project-102-0110。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0110/executions/EXEC-tenant-10-project-102-0110/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v208 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M74" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N74" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O74" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P74" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q74" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R74" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0110</x:v>
       </x:c>
-      <x:c r="J74" s="19" t="str">
+      <x:c r="S74" s="19" t="str">
         <x:v>UTC 2026-08-10 09:36:00.000</x:v>
       </x:c>
-      <x:c r="K74" s="20" t="n">
+      <x:c r="T74" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L74" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M74" s="8" t="str">
+      <x:c r="U74" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12572,24 +14356,48 @@
         <x:v>INC-tenant-10-project-102-0111</x:v>
       </x:c>
       <x:c r="G75" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H75" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I75" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J75" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0111 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0111/executions/EXEC-tenant-10-project-102-0111/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K75" s="8" t="str">
+        <x:v>2026-08-10T09:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0111 taskId=TASK-tenant-10-project-102-0111 executionId=EXEC-tenant-10-project-102-0111 objectId=object-15 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L75" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0111、taskId=TASK-tenant-10-project-102-0111 和 executionId=EXEC-tenant-10-project-102-0111。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0111/executions/EXEC-tenant-10-project-102-0111/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v209 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M75" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N75" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O75" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P75" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q75" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R75" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0111</x:v>
       </x:c>
-      <x:c r="J75" s="19" t="str">
+      <x:c r="S75" s="19" t="str">
         <x:v>UTC 2026-08-10 09:44:00.000</x:v>
       </x:c>
-      <x:c r="K75" s="20" t="n">
+      <x:c r="T75" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L75" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M75" s="8" t="str">
+      <x:c r="U75" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12613,24 +14421,48 @@
         <x:v>INC-tenant-10-project-102-0113</x:v>
       </x:c>
       <x:c r="G76" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H76" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I76" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J76" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0113 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0113/executions/EXEC-tenant-10-project-102-0113/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K76" s="8" t="str">
+        <x:v>2026-08-10T09:52:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0113 taskId=TASK-tenant-10-project-102-0113 executionId=EXEC-tenant-10-project-102-0113 objectId=object-17 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L76" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0113、taskId=TASK-tenant-10-project-102-0113 和 executionId=EXEC-tenant-10-project-102-0113。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0113/executions/EXEC-tenant-10-project-102-0113/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v211 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M76" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N76" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O76" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P76" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q76" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R76" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0113</x:v>
       </x:c>
-      <x:c r="J76" s="19" t="str">
+      <x:c r="S76" s="19" t="str">
         <x:v>UTC 2026-08-10 09:52:00.000</x:v>
       </x:c>
-      <x:c r="K76" s="20" t="n">
+      <x:c r="T76" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L76" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M76" s="8" t="str">
+      <x:c r="U76" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12654,24 +14486,48 @@
         <x:v>INC-tenant-10-project-102-0114</x:v>
       </x:c>
       <x:c r="G77" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H77" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I77" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J77" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0114 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0114/executions/EXEC-tenant-10-project-102-0114/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K77" s="8" t="str">
+        <x:v>2026-08-10T10:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0114 taskId=TASK-tenant-10-project-102-0114 executionId=EXEC-tenant-10-project-102-0114 objectId=object-18 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L77" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0114、taskId=TASK-tenant-10-project-102-0114 和 executionId=EXEC-tenant-10-project-102-0114。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0114/executions/EXEC-tenant-10-project-102-0114/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v212 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M77" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N77" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O77" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P77" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q77" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R77" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0114</x:v>
       </x:c>
-      <x:c r="J77" s="19" t="str">
+      <x:c r="S77" s="19" t="str">
         <x:v>UTC 2026-08-10 10:00:00.000</x:v>
       </x:c>
-      <x:c r="K77" s="20" t="n">
+      <x:c r="T77" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L77" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M77" s="8" t="str">
+      <x:c r="U77" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12695,24 +14551,48 @@
         <x:v>INC-tenant-10-project-102-0116</x:v>
       </x:c>
       <x:c r="G78" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H78" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I78" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J78" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0116 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0116/executions/EXEC-tenant-10-project-102-0116/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K78" s="8" t="str">
+        <x:v>2026-08-10T10:08:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0116 taskId=TASK-tenant-10-project-102-0116 executionId=EXEC-tenant-10-project-102-0116 objectId=object-20 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L78" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0116、taskId=TASK-tenant-10-project-102-0116 和 executionId=EXEC-tenant-10-project-102-0116。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0116/executions/EXEC-tenant-10-project-102-0116/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v214 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M78" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N78" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O78" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P78" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q78" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R78" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0116</x:v>
       </x:c>
-      <x:c r="J78" s="19" t="str">
+      <x:c r="S78" s="19" t="str">
         <x:v>UTC 2026-08-10 10:08:00.000</x:v>
       </x:c>
-      <x:c r="K78" s="20" t="n">
+      <x:c r="T78" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L78" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M78" s="8" t="str">
+      <x:c r="U78" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12736,24 +14616,48 @@
         <x:v>INC-tenant-10-project-102-0117</x:v>
       </x:c>
       <x:c r="G79" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H79" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I79" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J79" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0117 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0117/executions/EXEC-tenant-10-project-102-0117/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K79" s="8" t="str">
+        <x:v>2026-08-10T10:16:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0117 taskId=TASK-tenant-10-project-102-0117 executionId=EXEC-tenant-10-project-102-0117 objectId=object-21 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L79" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0117、taskId=TASK-tenant-10-project-102-0117 和 executionId=EXEC-tenant-10-project-102-0117。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0117/executions/EXEC-tenant-10-project-102-0117/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v215 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M79" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N79" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O79" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P79" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q79" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R79" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0117</x:v>
       </x:c>
-      <x:c r="J79" s="19" t="str">
+      <x:c r="S79" s="19" t="str">
         <x:v>UTC 2026-08-10 10:16:00.000</x:v>
       </x:c>
-      <x:c r="K79" s="20" t="n">
+      <x:c r="T79" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L79" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M79" s="8" t="str">
+      <x:c r="U79" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12780,21 +14684,45 @@
         <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H80" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I80" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J80" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0119 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0119/executions/EXEC-tenant-10-project-102-0119/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K80" s="8" t="str">
+        <x:v>2026-08-10T10:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0119 taskId=TASK-tenant-10-project-102-0119 executionId=EXEC-tenant-10-project-102-0119 objectId=object-23 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L80" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0119、taskId=TASK-tenant-10-project-102-0119 和 executionId=EXEC-tenant-10-project-102-0119。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0119/executions/EXEC-tenant-10-project-102-0119/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v217 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M80" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N80" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O80" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P80" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q80" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R80" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0119</x:v>
       </x:c>
-      <x:c r="J80" s="19" t="str">
+      <x:c r="S80" s="19" t="str">
         <x:v>UTC 2026-08-10 10:24:00.000</x:v>
       </x:c>
-      <x:c r="K80" s="20" t="n">
+      <x:c r="T80" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L80" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M80" s="8" t="str">
+      <x:c r="U80" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -12821,21 +14749,45 @@
         <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H81" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I81" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J81" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0120 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0120/executions/EXEC-tenant-10-project-102-0120/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K81" s="8" t="str">
+        <x:v>2026-08-10T10:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0120 taskId=TASK-tenant-10-project-102-0120 executionId=EXEC-tenant-10-project-102-0120 objectId=object-24 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L81" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0120、taskId=TASK-tenant-10-project-102-0120 和 executionId=EXEC-tenant-10-project-102-0120。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0120/executions/EXEC-tenant-10-project-102-0120/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v218 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M81" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N81" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O81" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P81" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q81" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R81" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0120</x:v>
       </x:c>
-      <x:c r="J81" s="19" t="str">
+      <x:c r="S81" s="19" t="str">
         <x:v>UTC 2026-08-10 10:32:00.000</x:v>
       </x:c>
-      <x:c r="K81" s="20" t="n">
+      <x:c r="T81" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L81" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M81" s="8" t="str">
+      <x:c r="U81" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -12859,25 +14811,49 @@
         <x:v>INC-tenant-10-project-102-0122</x:v>
       </x:c>
       <x:c r="G82" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H82" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I82" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J82" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0122 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0122/executions/EXEC-tenant-10-project-102-0122/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K82" s="8" t="str">
+        <x:v>2026-08-10T10:40:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0122 taskId=TASK-tenant-10-project-102-0122 executionId=EXEC-tenant-10-project-102-0122 objectId=object-26 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L82" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0122、taskId=TASK-tenant-10-project-102-0122 和 executionId=EXEC-tenant-10-project-102-0122。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0122/executions/EXEC-tenant-10-project-102-0122/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v220 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M82" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N82" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O82" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P82" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q82" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R82" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0122</x:v>
       </x:c>
-      <x:c r="J82" s="19" t="str">
+      <x:c r="S82" s="19" t="str">
         <x:v>UTC 2026-08-10 10:40:00.000</x:v>
       </x:c>
-      <x:c r="K82" s="20" t="n">
+      <x:c r="T82" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L82" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M82" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U82" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -12900,24 +14876,48 @@
         <x:v>INC-tenant-10-project-102-0123</x:v>
       </x:c>
       <x:c r="G83" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H83" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I83" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J83" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0123 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0123/executions/EXEC-tenant-10-project-102-0123/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K83" s="8" t="str">
+        <x:v>2026-08-10T10:48:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0123 taskId=TASK-tenant-10-project-102-0123 executionId=EXEC-tenant-10-project-102-0123 objectId=object-27 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L83" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0123、taskId=TASK-tenant-10-project-102-0123 和 executionId=EXEC-tenant-10-project-102-0123。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0123/executions/EXEC-tenant-10-project-102-0123/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v221 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M83" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N83" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O83" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P83" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q83" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R83" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0123</x:v>
       </x:c>
-      <x:c r="J83" s="19" t="str">
+      <x:c r="S83" s="19" t="str">
         <x:v>UTC 2026-08-10 10:48:00.000</x:v>
       </x:c>
-      <x:c r="K83" s="20" t="n">
+      <x:c r="T83" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L83" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M83" s="8" t="str">
+      <x:c r="U83" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -12941,25 +14941,49 @@
         <x:v>INC-tenant-10-project-102-0125</x:v>
       </x:c>
       <x:c r="G84" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H84" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I84" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J84" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0125 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0125/executions/EXEC-tenant-10-project-102-0125/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K84" s="8" t="str">
+        <x:v>2026-08-10T10:56:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0125 taskId=TASK-tenant-10-project-102-0125 executionId=EXEC-tenant-10-project-102-0125 objectId=object-29 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L84" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0125、taskId=TASK-tenant-10-project-102-0125 和 executionId=EXEC-tenant-10-project-102-0125。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0125/executions/EXEC-tenant-10-project-102-0125/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v223 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M84" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N84" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O84" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P84" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q84" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R84" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0125</x:v>
       </x:c>
-      <x:c r="J84" s="19" t="str">
+      <x:c r="S84" s="19" t="str">
         <x:v>UTC 2026-08-10 10:56:00.000</x:v>
       </x:c>
-      <x:c r="K84" s="20" t="n">
+      <x:c r="T84" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L84" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M84" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U84" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -12982,24 +15006,48 @@
         <x:v>INC-tenant-10-project-102-0126</x:v>
       </x:c>
       <x:c r="G85" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H85" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I85" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J85" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0126 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0126/executions/EXEC-tenant-10-project-102-0126/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K85" s="8" t="str">
+        <x:v>2026-08-10T11:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0126 taskId=TASK-tenant-10-project-102-0126 executionId=EXEC-tenant-10-project-102-0126 objectId=object-30 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L85" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0126、taskId=TASK-tenant-10-project-102-0126 和 executionId=EXEC-tenant-10-project-102-0126。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0126/executions/EXEC-tenant-10-project-102-0126/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v224 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M85" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N85" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O85" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P85" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q85" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R85" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0126</x:v>
       </x:c>
-      <x:c r="J85" s="19" t="str">
+      <x:c r="S85" s="19" t="str">
         <x:v>UTC 2026-08-10 11:04:00.000</x:v>
       </x:c>
-      <x:c r="K85" s="20" t="n">
+      <x:c r="T85" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L85" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M85" s="8" t="str">
+      <x:c r="U85" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13023,24 +15071,48 @@
         <x:v>INC-tenant-10-project-102-0128</x:v>
       </x:c>
       <x:c r="G86" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H86" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I86" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J86" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0128 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0128/executions/EXEC-tenant-10-project-102-0128/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K86" s="8" t="str">
+        <x:v>2026-08-10T11:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0128 taskId=TASK-tenant-10-project-102-0128 executionId=EXEC-tenant-10-project-102-0128 objectId=object-32 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L86" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0128、taskId=TASK-tenant-10-project-102-0128 和 executionId=EXEC-tenant-10-project-102-0128。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0128/executions/EXEC-tenant-10-project-102-0128/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v226 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M86" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N86" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O86" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P86" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q86" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R86" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0128</x:v>
       </x:c>
-      <x:c r="J86" s="19" t="str">
+      <x:c r="S86" s="19" t="str">
         <x:v>UTC 2026-08-10 11:12:00.000</x:v>
       </x:c>
-      <x:c r="K86" s="20" t="n">
+      <x:c r="T86" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L86" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M86" s="8" t="str">
+      <x:c r="U86" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13064,24 +15136,48 @@
         <x:v>INC-tenant-10-project-102-0129</x:v>
       </x:c>
       <x:c r="G87" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H87" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I87" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J87" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0129 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0129/executions/EXEC-tenant-10-project-102-0129/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K87" s="8" t="str">
+        <x:v>2026-08-10T11:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0129 taskId=TASK-tenant-10-project-102-0129 executionId=EXEC-tenant-10-project-102-0129 objectId=object-01 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L87" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0129、taskId=TASK-tenant-10-project-102-0129 和 executionId=EXEC-tenant-10-project-102-0129。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0129/executions/EXEC-tenant-10-project-102-0129/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v227 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M87" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N87" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O87" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P87" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q87" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R87" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0129</x:v>
       </x:c>
-      <x:c r="J87" s="19" t="str">
+      <x:c r="S87" s="19" t="str">
         <x:v>UTC 2026-08-10 11:20:00.000</x:v>
       </x:c>
-      <x:c r="K87" s="20" t="n">
+      <x:c r="T87" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L87" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M87" s="8" t="str">
+      <x:c r="U87" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13105,24 +15201,48 @@
         <x:v>INC-tenant-10-project-102-0131</x:v>
       </x:c>
       <x:c r="G88" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H88" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I88" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J88" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0131 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0131/executions/EXEC-tenant-10-project-102-0131/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K88" s="8" t="str">
+        <x:v>2026-08-10T11:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0131 taskId=TASK-tenant-10-project-102-0131 executionId=EXEC-tenant-10-project-102-0131 objectId=object-03 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L88" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0131、taskId=TASK-tenant-10-project-102-0131 和 executionId=EXEC-tenant-10-project-102-0131。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0131/executions/EXEC-tenant-10-project-102-0131/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v229 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M88" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N88" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O88" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P88" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q88" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R88" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0131</x:v>
       </x:c>
-      <x:c r="J88" s="19" t="str">
+      <x:c r="S88" s="19" t="str">
         <x:v>UTC 2026-08-10 11:28:00.000</x:v>
       </x:c>
-      <x:c r="K88" s="20" t="n">
+      <x:c r="T88" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L88" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M88" s="8" t="str">
+      <x:c r="U88" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13146,24 +15266,48 @@
         <x:v>INC-tenant-10-project-102-0132</x:v>
       </x:c>
       <x:c r="G89" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H89" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I89" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J89" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0132 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0132/executions/EXEC-tenant-10-project-102-0132/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K89" s="8" t="str">
+        <x:v>2026-08-10T11:36:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0132 taskId=TASK-tenant-10-project-102-0132 executionId=EXEC-tenant-10-project-102-0132 objectId=object-04 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L89" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0132、taskId=TASK-tenant-10-project-102-0132 和 executionId=EXEC-tenant-10-project-102-0132。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0132/executions/EXEC-tenant-10-project-102-0132/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v230 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M89" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N89" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O89" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P89" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q89" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R89" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0132</x:v>
       </x:c>
-      <x:c r="J89" s="19" t="str">
+      <x:c r="S89" s="19" t="str">
         <x:v>UTC 2026-08-10 11:36:00.000</x:v>
       </x:c>
-      <x:c r="K89" s="20" t="n">
+      <x:c r="T89" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L89" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M89" s="8" t="str">
+      <x:c r="U89" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13187,24 +15331,48 @@
         <x:v>INC-tenant-10-project-102-0134</x:v>
       </x:c>
       <x:c r="G90" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H90" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I90" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J90" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0134 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0134/executions/EXEC-tenant-10-project-102-0134/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K90" s="8" t="str">
+        <x:v>2026-08-10T11:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0134 taskId=TASK-tenant-10-project-102-0134 executionId=EXEC-tenant-10-project-102-0134 objectId=object-06 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L90" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0134、taskId=TASK-tenant-10-project-102-0134 和 executionId=EXEC-tenant-10-project-102-0134。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0134/executions/EXEC-tenant-10-project-102-0134/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v232 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M90" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N90" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O90" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P90" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q90" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R90" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0134</x:v>
       </x:c>
-      <x:c r="J90" s="19" t="str">
+      <x:c r="S90" s="19" t="str">
         <x:v>UTC 2026-08-10 11:44:00.000</x:v>
       </x:c>
-      <x:c r="K90" s="20" t="n">
+      <x:c r="T90" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L90" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M90" s="8" t="str">
+      <x:c r="U90" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13228,24 +15396,48 @@
         <x:v>INC-tenant-10-project-102-0135</x:v>
       </x:c>
       <x:c r="G91" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H91" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I91" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J91" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0135 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0135/executions/EXEC-tenant-10-project-102-0135/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K91" s="8" t="str">
+        <x:v>2026-08-10T11:52:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0135 taskId=TASK-tenant-10-project-102-0135 executionId=EXEC-tenant-10-project-102-0135 objectId=object-07 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L91" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0135、taskId=TASK-tenant-10-project-102-0135 和 executionId=EXEC-tenant-10-project-102-0135。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0135/executions/EXEC-tenant-10-project-102-0135/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v233 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M91" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N91" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O91" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P91" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q91" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R91" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0135</x:v>
       </x:c>
-      <x:c r="J91" s="19" t="str">
+      <x:c r="S91" s="19" t="str">
         <x:v>UTC 2026-08-10 11:52:00.000</x:v>
       </x:c>
-      <x:c r="K91" s="20" t="n">
+      <x:c r="T91" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L91" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M91" s="8" t="str">
+      <x:c r="U91" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13269,24 +15461,48 @@
         <x:v>INC-tenant-10-project-102-0137</x:v>
       </x:c>
       <x:c r="G92" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H92" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I92" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J92" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0137 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0137/executions/EXEC-tenant-10-project-102-0137/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K92" s="8" t="str">
+        <x:v>2026-08-10T12:00:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0137 taskId=TASK-tenant-10-project-102-0137 executionId=EXEC-tenant-10-project-102-0137 objectId=object-09 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L92" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0137、taskId=TASK-tenant-10-project-102-0137 和 executionId=EXEC-tenant-10-project-102-0137。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0137/executions/EXEC-tenant-10-project-102-0137/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v235 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M92" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N92" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O92" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P92" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q92" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R92" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0137</x:v>
       </x:c>
-      <x:c r="J92" s="19" t="str">
+      <x:c r="S92" s="19" t="str">
         <x:v>UTC 2026-08-10 12:00:00.000</x:v>
       </x:c>
-      <x:c r="K92" s="20" t="n">
+      <x:c r="T92" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L92" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M92" s="8" t="str">
+      <x:c r="U92" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13310,24 +15526,48 @@
         <x:v>INC-tenant-10-project-102-0138</x:v>
       </x:c>
       <x:c r="G93" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H93" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I93" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J93" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0138 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0138/executions/EXEC-tenant-10-project-102-0138/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K93" s="8" t="str">
+        <x:v>2026-08-10T12:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0138 taskId=TASK-tenant-10-project-102-0138 executionId=EXEC-tenant-10-project-102-0138 objectId=object-10 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L93" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0138、taskId=TASK-tenant-10-project-102-0138 和 executionId=EXEC-tenant-10-project-102-0138。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0138/executions/EXEC-tenant-10-project-102-0138/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v236 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M93" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N93" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O93" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P93" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q93" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R93" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0138</x:v>
       </x:c>
-      <x:c r="J93" s="19" t="str">
+      <x:c r="S93" s="19" t="str">
         <x:v>UTC 2026-08-10 12:08:00.000</x:v>
       </x:c>
-      <x:c r="K93" s="20" t="n">
+      <x:c r="T93" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L93" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M93" s="8" t="str">
+      <x:c r="U93" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13351,25 +15591,49 @@
         <x:v>INC-tenant-10-project-102-0140</x:v>
       </x:c>
       <x:c r="G94" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H94" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I94" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J94" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0140 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0140/executions/EXEC-tenant-10-project-102-0140/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K94" s="8" t="str">
+        <x:v>2026-08-10T12:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0140 taskId=TASK-tenant-10-project-102-0140 executionId=EXEC-tenant-10-project-102-0140 objectId=object-12 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L94" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0140、taskId=TASK-tenant-10-project-102-0140 和 executionId=EXEC-tenant-10-project-102-0140。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0140/executions/EXEC-tenant-10-project-102-0140/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v238 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M94" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N94" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O94" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P94" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q94" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R94" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0140</x:v>
       </x:c>
-      <x:c r="J94" s="19" t="str">
+      <x:c r="S94" s="19" t="str">
         <x:v>UTC 2026-08-10 12:16:00.000</x:v>
       </x:c>
-      <x:c r="K94" s="20" t="n">
+      <x:c r="T94" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L94" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M94" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U94" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -13392,24 +15656,48 @@
         <x:v>INC-tenant-10-project-102-0141</x:v>
       </x:c>
       <x:c r="G95" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H95" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I95" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J95" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0141 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0141/executions/EXEC-tenant-10-project-102-0141/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K95" s="8" t="str">
+        <x:v>2026-08-10T12:24:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0141 taskId=TASK-tenant-10-project-102-0141 executionId=EXEC-tenant-10-project-102-0141 objectId=object-13 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L95" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0141、taskId=TASK-tenant-10-project-102-0141 和 executionId=EXEC-tenant-10-project-102-0141。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0141/executions/EXEC-tenant-10-project-102-0141/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v239 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M95" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N95" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O95" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P95" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q95" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R95" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0141</x:v>
       </x:c>
-      <x:c r="J95" s="19" t="str">
+      <x:c r="S95" s="19" t="str">
         <x:v>UTC 2026-08-10 12:24:00.000</x:v>
       </x:c>
-      <x:c r="K95" s="20" t="n">
+      <x:c r="T95" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L95" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M95" s="8" t="str">
+      <x:c r="U95" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13433,25 +15721,49 @@
         <x:v>INC-tenant-10-project-102-0143</x:v>
       </x:c>
       <x:c r="G96" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H96" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I96" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J96" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0143 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0143/executions/EXEC-tenant-10-project-102-0143/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K96" s="8" t="str">
+        <x:v>2026-08-10T12:32:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0143 taskId=TASK-tenant-10-project-102-0143 executionId=EXEC-tenant-10-project-102-0143 objectId=object-15 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L96" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0143、taskId=TASK-tenant-10-project-102-0143 和 executionId=EXEC-tenant-10-project-102-0143。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0143/executions/EXEC-tenant-10-project-102-0143/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v241 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M96" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N96" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O96" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P96" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q96" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R96" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0143</x:v>
       </x:c>
-      <x:c r="J96" s="19" t="str">
+      <x:c r="S96" s="19" t="str">
         <x:v>UTC 2026-08-10 12:32:00.000</x:v>
       </x:c>
-      <x:c r="K96" s="20" t="n">
+      <x:c r="T96" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L96" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M96" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U96" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -13474,24 +15786,48 @@
         <x:v>INC-tenant-10-project-102-0144</x:v>
       </x:c>
       <x:c r="G97" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H97" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I97" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J97" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0144 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0144/executions/EXEC-tenant-10-project-102-0144/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K97" s="8" t="str">
+        <x:v>2026-08-10T12:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0144 taskId=TASK-tenant-10-project-102-0144 executionId=EXEC-tenant-10-project-102-0144 objectId=object-16 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L97" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0144、taskId=TASK-tenant-10-project-102-0144 和 executionId=EXEC-tenant-10-project-102-0144。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0144/executions/EXEC-tenant-10-project-102-0144/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v242 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M97" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N97" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O97" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P97" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q97" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R97" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0144</x:v>
       </x:c>
-      <x:c r="J97" s="19" t="str">
+      <x:c r="S97" s="19" t="str">
         <x:v>UTC 2026-08-10 12:40:00.000</x:v>
       </x:c>
-      <x:c r="K97" s="20" t="n">
+      <x:c r="T97" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L97" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M97" s="8" t="str">
+      <x:c r="U97" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13515,24 +15851,48 @@
         <x:v>INC-tenant-10-project-102-0146</x:v>
       </x:c>
       <x:c r="G98" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H98" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I98" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J98" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0146 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0146/executions/EXEC-tenant-10-project-102-0146/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K98" s="8" t="str">
+        <x:v>2026-08-10T12:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0146 taskId=TASK-tenant-10-project-102-0146 executionId=EXEC-tenant-10-project-102-0146 objectId=object-18 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L98" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0146、taskId=TASK-tenant-10-project-102-0146 和 executionId=EXEC-tenant-10-project-102-0146。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0146/executions/EXEC-tenant-10-project-102-0146/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v244 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M98" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N98" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O98" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P98" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q98" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R98" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0146</x:v>
       </x:c>
-      <x:c r="J98" s="19" t="str">
+      <x:c r="S98" s="19" t="str">
         <x:v>UTC 2026-08-10 12:48:00.000</x:v>
       </x:c>
-      <x:c r="K98" s="20" t="n">
+      <x:c r="T98" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L98" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M98" s="8" t="str">
+      <x:c r="U98" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13556,24 +15916,48 @@
         <x:v>INC-tenant-10-project-102-0147</x:v>
       </x:c>
       <x:c r="G99" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H99" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I99" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J99" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0147 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0147/executions/EXEC-tenant-10-project-102-0147/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K99" s="8" t="str">
+        <x:v>2026-08-10T12:56:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0147 taskId=TASK-tenant-10-project-102-0147 executionId=EXEC-tenant-10-project-102-0147 objectId=object-19 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L99" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0147、taskId=TASK-tenant-10-project-102-0147 和 executionId=EXEC-tenant-10-project-102-0147。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0147/executions/EXEC-tenant-10-project-102-0147/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v245 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M99" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N99" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O99" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P99" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q99" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R99" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0147</x:v>
       </x:c>
-      <x:c r="J99" s="19" t="str">
+      <x:c r="S99" s="19" t="str">
         <x:v>UTC 2026-08-10 12:56:00.000</x:v>
       </x:c>
-      <x:c r="K99" s="20" t="n">
+      <x:c r="T99" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L99" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M99" s="8" t="str">
+      <x:c r="U99" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13597,24 +15981,48 @@
         <x:v>INC-tenant-10-project-102-0149</x:v>
       </x:c>
       <x:c r="G100" s="8" t="str">
-        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H100" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I100" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J100" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0149 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0149/executions/EXEC-tenant-10-project-102-0149/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K100" s="8" t="str">
+        <x:v>2026-08-10T13:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0149 taskId=TASK-tenant-10-project-102-0149 executionId=EXEC-tenant-10-project-102-0149 objectId=object-21 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L100" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0149、taskId=TASK-tenant-10-project-102-0149 和 executionId=EXEC-tenant-10-project-102-0149。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0149/executions/EXEC-tenant-10-project-102-0149/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v247 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M100" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N100" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O100" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P100" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q100" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R100" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0149</x:v>
       </x:c>
-      <x:c r="J100" s="19" t="str">
+      <x:c r="S100" s="19" t="str">
         <x:v>UTC 2026-08-10 13:04:00.000</x:v>
       </x:c>
-      <x:c r="K100" s="20" t="n">
+      <x:c r="T100" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L100" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M100" s="8" t="str">
+      <x:c r="U100" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13638,25 +16046,49 @@
         <x:v>INC-tenant-10-project-102-0150</x:v>
       </x:c>
       <x:c r="G101" s="8" t="str">
-        <x:v>DDL_REQUIRED</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H101" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I101" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J101" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0150 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0150/executions/EXEC-tenant-10-project-102-0150/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K101" s="8" t="str">
+        <x:v>2026-08-10T13:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0150 taskId=TASK-tenant-10-project-102-0150 executionId=EXEC-tenant-10-project-102-0150 objectId=object-22 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L101" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0150、taskId=TASK-tenant-10-project-102-0150 和 executionId=EXEC-tenant-10-project-102-0150。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0150/executions/EXEC-tenant-10-project-102-0150/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v248 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M101" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N101" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O101" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P101" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q101" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R101" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0150</x:v>
       </x:c>
-      <x:c r="J101" s="19" t="str">
+      <x:c r="S101" s="19" t="str">
         <x:v>UTC 2026-08-10 13:12:00.000</x:v>
       </x:c>
-      <x:c r="K101" s="20" t="n">
+      <x:c r="T101" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L101" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M101" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U101" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -13679,24 +16111,48 @@
         <x:v>INC-tenant-10-project-102-0152</x:v>
       </x:c>
       <x:c r="G102" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H102" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I102" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J102" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0152 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0152/executions/EXEC-tenant-10-project-102-0152/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K102" s="8" t="str">
+        <x:v>2026-08-10T13:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0152 taskId=TASK-tenant-10-project-102-0152 executionId=EXEC-tenant-10-project-102-0152 objectId=object-24 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L102" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0152、taskId=TASK-tenant-10-project-102-0152 和 executionId=EXEC-tenant-10-project-102-0152。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0152/executions/EXEC-tenant-10-project-102-0152/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v250 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M102" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N102" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O102" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P102" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q102" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R102" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0152</x:v>
       </x:c>
-      <x:c r="J102" s="19" t="str">
+      <x:c r="S102" s="19" t="str">
         <x:v>UTC 2026-08-10 13:20:00.000</x:v>
       </x:c>
-      <x:c r="K102" s="20" t="n">
+      <x:c r="T102" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L102" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M102" s="8" t="str">
+      <x:c r="U102" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13720,25 +16176,49 @@
         <x:v>INC-tenant-10-project-102-0153</x:v>
       </x:c>
       <x:c r="G103" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H103" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I103" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J103" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0153 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0153/executions/EXEC-tenant-10-project-102-0153/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K103" s="8" t="str">
+        <x:v>2026-08-10T13:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0153 taskId=TASK-tenant-10-project-102-0153 executionId=EXEC-tenant-10-project-102-0153 objectId=object-25 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L103" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0153、taskId=TASK-tenant-10-project-102-0153 和 executionId=EXEC-tenant-10-project-102-0153。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0153/executions/EXEC-tenant-10-project-102-0153/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v251 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M103" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N103" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O103" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P103" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q103" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R103" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0153</x:v>
       </x:c>
-      <x:c r="J103" s="19" t="str">
+      <x:c r="S103" s="19" t="str">
         <x:v>UTC 2026-08-10 13:28:00.000</x:v>
       </x:c>
-      <x:c r="K103" s="20" t="n">
+      <x:c r="T103" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L103" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M103" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U103" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -13761,25 +16241,49 @@
         <x:v>INC-tenant-10-project-102-0155</x:v>
       </x:c>
       <x:c r="G104" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H104" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I104" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J104" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0155 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0155/executions/EXEC-tenant-10-project-102-0155/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K104" s="8" t="str">
+        <x:v>2026-08-10T13:36:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0155 taskId=TASK-tenant-10-project-102-0155 executionId=EXEC-tenant-10-project-102-0155 objectId=object-27 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L104" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0155、taskId=TASK-tenant-10-project-102-0155 和 executionId=EXEC-tenant-10-project-102-0155。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0155/executions/EXEC-tenant-10-project-102-0155/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v253 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M104" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N104" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O104" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P104" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q104" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R104" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0155</x:v>
       </x:c>
-      <x:c r="J104" s="19" t="str">
+      <x:c r="S104" s="19" t="str">
         <x:v>UTC 2026-08-10 13:36:00.000</x:v>
       </x:c>
-      <x:c r="K104" s="20" t="n">
+      <x:c r="T104" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L104" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M104" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U104" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -13802,24 +16306,48 @@
         <x:v>INC-tenant-10-project-102-0156</x:v>
       </x:c>
       <x:c r="G105" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H105" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I105" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J105" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0156 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0156/executions/EXEC-tenant-10-project-102-0156/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K105" s="8" t="str">
+        <x:v>2026-08-10T13:44:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0156 taskId=TASK-tenant-10-project-102-0156 executionId=EXEC-tenant-10-project-102-0156 objectId=object-28 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L105" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0156、taskId=TASK-tenant-10-project-102-0156 和 executionId=EXEC-tenant-10-project-102-0156。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0156/executions/EXEC-tenant-10-project-102-0156/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v254 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M105" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N105" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O105" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P105" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q105" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R105" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0156</x:v>
       </x:c>
-      <x:c r="J105" s="19" t="str">
+      <x:c r="S105" s="19" t="str">
         <x:v>UTC 2026-08-10 13:44:00.000</x:v>
       </x:c>
-      <x:c r="K105" s="20" t="n">
+      <x:c r="T105" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L105" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M105" s="8" t="str">
+      <x:c r="U105" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13843,24 +16371,48 @@
         <x:v>INC-tenant-10-project-102-0158</x:v>
       </x:c>
       <x:c r="G106" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H106" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I106" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J106" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0158 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0158/executions/EXEC-tenant-10-project-102-0158/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K106" s="8" t="str">
+        <x:v>2026-08-10T13:52:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0158 taskId=TASK-tenant-10-project-102-0158 executionId=EXEC-tenant-10-project-102-0158 objectId=object-30 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L106" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0158、taskId=TASK-tenant-10-project-102-0158 和 executionId=EXEC-tenant-10-project-102-0158。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0158/executions/EXEC-tenant-10-project-102-0158/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v256 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M106" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N106" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O106" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P106" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q106" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R106" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0158</x:v>
       </x:c>
-      <x:c r="J106" s="19" t="str">
+      <x:c r="S106" s="19" t="str">
         <x:v>UTC 2026-08-10 13:52:00.000</x:v>
       </x:c>
-      <x:c r="K106" s="20" t="n">
+      <x:c r="T106" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L106" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M106" s="8" t="str">
+      <x:c r="U106" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13884,24 +16436,48 @@
         <x:v>INC-tenant-10-project-102-0159</x:v>
       </x:c>
       <x:c r="G107" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H107" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I107" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J107" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0159 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0159/executions/EXEC-tenant-10-project-102-0159/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K107" s="8" t="str">
+        <x:v>2026-08-10T14:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0159 taskId=TASK-tenant-10-project-102-0159 executionId=EXEC-tenant-10-project-102-0159 objectId=object-31 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L107" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0159、taskId=TASK-tenant-10-project-102-0159 和 executionId=EXEC-tenant-10-project-102-0159。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0159/executions/EXEC-tenant-10-project-102-0159/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v257 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M107" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N107" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O107" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P107" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q107" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R107" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0159</x:v>
       </x:c>
-      <x:c r="J107" s="19" t="str">
+      <x:c r="S107" s="19" t="str">
         <x:v>UTC 2026-08-10 14:00:00.000</x:v>
       </x:c>
-      <x:c r="K107" s="20" t="n">
+      <x:c r="T107" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L107" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M107" s="8" t="str">
+      <x:c r="U107" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13925,24 +16501,48 @@
         <x:v>INC-tenant-10-project-102-0161</x:v>
       </x:c>
       <x:c r="G108" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H108" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I108" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J108" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0161 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0161/executions/EXEC-tenant-10-project-102-0161/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K108" s="8" t="str">
+        <x:v>2026-08-10T14:08:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0161 taskId=TASK-tenant-10-project-102-0161 executionId=EXEC-tenant-10-project-102-0161 objectId=object-01 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L108" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0161、taskId=TASK-tenant-10-project-102-0161 和 executionId=EXEC-tenant-10-project-102-0161。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0161/executions/EXEC-tenant-10-project-102-0161/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v259 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M108" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N108" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O108" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P108" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q108" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R108" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0161</x:v>
       </x:c>
-      <x:c r="J108" s="19" t="str">
+      <x:c r="S108" s="19" t="str">
         <x:v>UTC 2026-08-10 14:08:00.000</x:v>
       </x:c>
-      <x:c r="K108" s="20" t="n">
+      <x:c r="T108" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L108" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M108" s="8" t="str">
+      <x:c r="U108" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -13966,25 +16566,49 @@
         <x:v>INC-tenant-10-project-102-0162</x:v>
       </x:c>
       <x:c r="G109" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H109" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I109" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J109" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0162 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0162/executions/EXEC-tenant-10-project-102-0162/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K109" s="8" t="str">
+        <x:v>2026-08-10T14:16:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0162 taskId=TASK-tenant-10-project-102-0162 executionId=EXEC-tenant-10-project-102-0162 objectId=object-02 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L109" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0162、taskId=TASK-tenant-10-project-102-0162 和 executionId=EXEC-tenant-10-project-102-0162。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0162/executions/EXEC-tenant-10-project-102-0162/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v260 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M109" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N109" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O109" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P109" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q109" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R109" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0162</x:v>
       </x:c>
-      <x:c r="J109" s="19" t="str">
+      <x:c r="S109" s="19" t="str">
         <x:v>UTC 2026-08-10 14:16:00.000</x:v>
       </x:c>
-      <x:c r="K109" s="20" t="n">
+      <x:c r="T109" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L109" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M109" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U109" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -14007,24 +16631,48 @@
         <x:v>INC-tenant-10-project-102-0164</x:v>
       </x:c>
       <x:c r="G110" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H110" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I110" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J110" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0164 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0164/executions/EXEC-tenant-10-project-102-0164/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K110" s="8" t="str">
+        <x:v>2026-08-10T14:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0164 taskId=TASK-tenant-10-project-102-0164 executionId=EXEC-tenant-10-project-102-0164 objectId=object-04 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L110" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0164、taskId=TASK-tenant-10-project-102-0164 和 executionId=EXEC-tenant-10-project-102-0164。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0164/executions/EXEC-tenant-10-project-102-0164/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v262 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M110" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N110" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O110" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P110" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q110" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R110" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0164</x:v>
       </x:c>
-      <x:c r="J110" s="19" t="str">
+      <x:c r="S110" s="19" t="str">
         <x:v>UTC 2026-08-10 14:24:00.000</x:v>
       </x:c>
-      <x:c r="K110" s="20" t="n">
+      <x:c r="T110" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L110" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M110" s="8" t="str">
+      <x:c r="U110" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14048,24 +16696,48 @@
         <x:v>INC-tenant-10-project-102-0165</x:v>
       </x:c>
       <x:c r="G111" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H111" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I111" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J111" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0165 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0165/executions/EXEC-tenant-10-project-102-0165/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K111" s="8" t="str">
+        <x:v>2026-08-10T14:32:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0165 taskId=TASK-tenant-10-project-102-0165 executionId=EXEC-tenant-10-project-102-0165 objectId=object-05 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L111" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0165、taskId=TASK-tenant-10-project-102-0165 和 executionId=EXEC-tenant-10-project-102-0165。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0165/executions/EXEC-tenant-10-project-102-0165/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v263 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M111" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N111" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O111" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P111" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q111" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R111" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0165</x:v>
       </x:c>
-      <x:c r="J111" s="19" t="str">
+      <x:c r="S111" s="19" t="str">
         <x:v>UTC 2026-08-10 14:32:00.000</x:v>
       </x:c>
-      <x:c r="K111" s="20" t="n">
+      <x:c r="T111" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L111" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M111" s="8" t="str">
+      <x:c r="U111" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14089,24 +16761,48 @@
         <x:v>INC-tenant-10-project-102-0167</x:v>
       </x:c>
       <x:c r="G112" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H112" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I112" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J112" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0167 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0167/executions/EXEC-tenant-10-project-102-0167/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K112" s="8" t="str">
+        <x:v>2026-08-10T14:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0167 taskId=TASK-tenant-10-project-102-0167 executionId=EXEC-tenant-10-project-102-0167 objectId=object-07 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L112" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0167、taskId=TASK-tenant-10-project-102-0167 和 executionId=EXEC-tenant-10-project-102-0167。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0167/executions/EXEC-tenant-10-project-102-0167/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v265 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M112" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N112" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O112" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P112" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q112" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R112" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0167</x:v>
       </x:c>
-      <x:c r="J112" s="19" t="str">
+      <x:c r="S112" s="19" t="str">
         <x:v>UTC 2026-08-10 14:40:00.000</x:v>
       </x:c>
-      <x:c r="K112" s="20" t="n">
+      <x:c r="T112" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L112" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M112" s="8" t="str">
+      <x:c r="U112" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14130,24 +16826,48 @@
         <x:v>INC-tenant-10-project-102-0168</x:v>
       </x:c>
       <x:c r="G113" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H113" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I113" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J113" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0168 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0168/executions/EXEC-tenant-10-project-102-0168/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K113" s="8" t="str">
+        <x:v>2026-08-10T14:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0168 taskId=TASK-tenant-10-project-102-0168 executionId=EXEC-tenant-10-project-102-0168 objectId=object-08 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L113" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0168、taskId=TASK-tenant-10-project-102-0168 和 executionId=EXEC-tenant-10-project-102-0168。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0168/executions/EXEC-tenant-10-project-102-0168/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v266 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M113" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N113" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O113" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P113" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q113" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R113" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0168</x:v>
       </x:c>
-      <x:c r="J113" s="19" t="str">
+      <x:c r="S113" s="19" t="str">
         <x:v>UTC 2026-08-10 14:48:00.000</x:v>
       </x:c>
-      <x:c r="K113" s="20" t="n">
+      <x:c r="T113" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L113" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M113" s="8" t="str">
+      <x:c r="U113" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14171,24 +16891,48 @@
         <x:v>INC-tenant-10-project-102-0170</x:v>
       </x:c>
       <x:c r="G114" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H114" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I114" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J114" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0170 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0170/executions/EXEC-tenant-10-project-102-0170/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K114" s="8" t="str">
+        <x:v>2026-08-10T14:56:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0170 taskId=TASK-tenant-10-project-102-0170 executionId=EXEC-tenant-10-project-102-0170 objectId=object-10 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L114" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0170、taskId=TASK-tenant-10-project-102-0170 和 executionId=EXEC-tenant-10-project-102-0170。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0170/executions/EXEC-tenant-10-project-102-0170/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v268 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M114" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N114" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O114" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P114" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q114" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R114" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0170</x:v>
       </x:c>
-      <x:c r="J114" s="19" t="str">
+      <x:c r="S114" s="19" t="str">
         <x:v>UTC 2026-08-10 14:56:00.000</x:v>
       </x:c>
-      <x:c r="K114" s="20" t="n">
+      <x:c r="T114" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L114" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M114" s="8" t="str">
+      <x:c r="U114" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14212,24 +16956,48 @@
         <x:v>INC-tenant-10-project-102-0171</x:v>
       </x:c>
       <x:c r="G115" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H115" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I115" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J115" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0171 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0171/executions/EXEC-tenant-10-project-102-0171/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K115" s="8" t="str">
+        <x:v>2026-08-10T15:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0171 taskId=TASK-tenant-10-project-102-0171 executionId=EXEC-tenant-10-project-102-0171 objectId=object-11 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L115" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0171、taskId=TASK-tenant-10-project-102-0171 和 executionId=EXEC-tenant-10-project-102-0171。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0171/executions/EXEC-tenant-10-project-102-0171/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v269 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M115" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N115" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O115" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P115" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q115" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R115" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0171</x:v>
       </x:c>
-      <x:c r="J115" s="19" t="str">
+      <x:c r="S115" s="19" t="str">
         <x:v>UTC 2026-08-10 15:04:00.000</x:v>
       </x:c>
-      <x:c r="K115" s="20" t="n">
+      <x:c r="T115" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L115" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M115" s="8" t="str">
+      <x:c r="U115" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14253,24 +17021,48 @@
         <x:v>INC-tenant-10-project-102-0173</x:v>
       </x:c>
       <x:c r="G116" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H116" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I116" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J116" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0173 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0173/executions/EXEC-tenant-10-project-102-0173/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K116" s="8" t="str">
+        <x:v>2026-08-10T15:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0173 taskId=TASK-tenant-10-project-102-0173 executionId=EXEC-tenant-10-project-102-0173 objectId=object-13 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L116" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0173、taskId=TASK-tenant-10-project-102-0173 和 executionId=EXEC-tenant-10-project-102-0173。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0173/executions/EXEC-tenant-10-project-102-0173/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v271 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M116" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N116" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O116" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P116" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q116" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R116" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0173</x:v>
       </x:c>
-      <x:c r="J116" s="19" t="str">
+      <x:c r="S116" s="19" t="str">
         <x:v>UTC 2026-08-10 15:12:00.000</x:v>
       </x:c>
-      <x:c r="K116" s="20" t="n">
+      <x:c r="T116" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L116" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M116" s="8" t="str">
+      <x:c r="U116" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14294,24 +17086,48 @@
         <x:v>INC-tenant-10-project-102-0174</x:v>
       </x:c>
       <x:c r="G117" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H117" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I117" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J117" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0174 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0174/executions/EXEC-tenant-10-project-102-0174/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K117" s="8" t="str">
+        <x:v>2026-08-10T15:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0174 taskId=TASK-tenant-10-project-102-0174 executionId=EXEC-tenant-10-project-102-0174 objectId=object-14 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L117" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0174、taskId=TASK-tenant-10-project-102-0174 和 executionId=EXEC-tenant-10-project-102-0174。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0174/executions/EXEC-tenant-10-project-102-0174/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v272 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M117" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N117" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O117" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P117" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q117" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R117" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0174</x:v>
       </x:c>
-      <x:c r="J117" s="19" t="str">
+      <x:c r="S117" s="19" t="str">
         <x:v>UTC 2026-08-10 15:20:00.000</x:v>
       </x:c>
-      <x:c r="K117" s="20" t="n">
+      <x:c r="T117" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L117" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M117" s="8" t="str">
+      <x:c r="U117" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14335,24 +17151,48 @@
         <x:v>INC-tenant-10-project-102-0176</x:v>
       </x:c>
       <x:c r="G118" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H118" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I118" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J118" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0176 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0176/executions/EXEC-tenant-10-project-102-0176/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K118" s="8" t="str">
+        <x:v>2026-08-10T15:28:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0176 taskId=TASK-tenant-10-project-102-0176 executionId=EXEC-tenant-10-project-102-0176 objectId=object-16 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L118" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0176、taskId=TASK-tenant-10-project-102-0176 和 executionId=EXEC-tenant-10-project-102-0176。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0176/executions/EXEC-tenant-10-project-102-0176/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v274 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M118" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N118" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O118" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P118" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q118" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R118" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0176</x:v>
       </x:c>
-      <x:c r="J118" s="19" t="str">
+      <x:c r="S118" s="19" t="str">
         <x:v>UTC 2026-08-10 15:28:00.000</x:v>
       </x:c>
-      <x:c r="K118" s="20" t="n">
+      <x:c r="T118" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L118" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M118" s="8" t="str">
+      <x:c r="U118" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14376,24 +17216,48 @@
         <x:v>INC-tenant-10-project-102-0177</x:v>
       </x:c>
       <x:c r="G119" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H119" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I119" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J119" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0177 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0177/executions/EXEC-tenant-10-project-102-0177/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K119" s="8" t="str">
+        <x:v>2026-08-10T15:36:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0177 taskId=TASK-tenant-10-project-102-0177 executionId=EXEC-tenant-10-project-102-0177 objectId=object-17 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L119" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0177、taskId=TASK-tenant-10-project-102-0177 和 executionId=EXEC-tenant-10-project-102-0177。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0177/executions/EXEC-tenant-10-project-102-0177/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v275 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M119" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N119" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O119" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P119" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q119" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R119" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0177</x:v>
       </x:c>
-      <x:c r="J119" s="19" t="str">
+      <x:c r="S119" s="19" t="str">
         <x:v>UTC 2026-08-10 15:36:00.000</x:v>
       </x:c>
-      <x:c r="K119" s="20" t="n">
+      <x:c r="T119" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L119" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M119" s="8" t="str">
+      <x:c r="U119" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14420,21 +17284,45 @@
         <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H120" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I120" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J120" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0179 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0179/executions/EXEC-tenant-10-project-102-0179/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K120" s="8" t="str">
+        <x:v>2026-08-10T15:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0179 taskId=TASK-tenant-10-project-102-0179 executionId=EXEC-tenant-10-project-102-0179 objectId=object-19 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L120" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0179、taskId=TASK-tenant-10-project-102-0179 和 executionId=EXEC-tenant-10-project-102-0179。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0179/executions/EXEC-tenant-10-project-102-0179/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v277 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M120" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N120" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O120" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P120" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q120" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R120" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0179</x:v>
       </x:c>
-      <x:c r="J120" s="19" t="str">
+      <x:c r="S120" s="19" t="str">
         <x:v>UTC 2026-08-10 15:44:00.000</x:v>
       </x:c>
-      <x:c r="K120" s="20" t="n">
+      <x:c r="T120" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L120" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M120" s="8" t="str">
+      <x:c r="U120" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14461,21 +17349,45 @@
         <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H121" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I121" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J121" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0180 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0180/executions/EXEC-tenant-10-project-102-0180/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K121" s="8" t="str">
+        <x:v>2026-08-10T15:52:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0180 taskId=TASK-tenant-10-project-102-0180 executionId=EXEC-tenant-10-project-102-0180 objectId=object-20 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L121" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0180、taskId=TASK-tenant-10-project-102-0180 和 executionId=EXEC-tenant-10-project-102-0180。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0180/executions/EXEC-tenant-10-project-102-0180/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v278 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M121" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N121" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O121" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P121" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q121" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R121" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0180</x:v>
       </x:c>
-      <x:c r="J121" s="19" t="str">
+      <x:c r="S121" s="19" t="str">
         <x:v>UTC 2026-08-10 15:52:00.000</x:v>
       </x:c>
-      <x:c r="K121" s="20" t="n">
+      <x:c r="T121" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L121" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M121" s="8" t="str">
+      <x:c r="U121" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -14499,25 +17411,49 @@
         <x:v>INC-tenant-10-project-102-0182</x:v>
       </x:c>
       <x:c r="G122" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H122" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I122" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J122" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0182 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0182/executions/EXEC-tenant-10-project-102-0182/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K122" s="8" t="str">
+        <x:v>2026-08-10T16:00:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0182 taskId=TASK-tenant-10-project-102-0182 executionId=EXEC-tenant-10-project-102-0182 objectId=object-22 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L122" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0182、taskId=TASK-tenant-10-project-102-0182 和 executionId=EXEC-tenant-10-project-102-0182。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0182/executions/EXEC-tenant-10-project-102-0182/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v280 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M122" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N122" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O122" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P122" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q122" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R122" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0182</x:v>
       </x:c>
-      <x:c r="J122" s="19" t="str">
+      <x:c r="S122" s="19" t="str">
         <x:v>UTC 2026-08-10 16:00:00.000</x:v>
       </x:c>
-      <x:c r="K122" s="20" t="n">
+      <x:c r="T122" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L122" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M122" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U122" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -14540,24 +17476,48 @@
         <x:v>INC-tenant-10-project-102-0183</x:v>
       </x:c>
       <x:c r="G123" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H123" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I123" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J123" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0183 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0183/executions/EXEC-tenant-10-project-102-0183/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K123" s="8" t="str">
+        <x:v>2026-08-10T16:08:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0183 taskId=TASK-tenant-10-project-102-0183 executionId=EXEC-tenant-10-project-102-0183 objectId=object-23 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L123" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0183、taskId=TASK-tenant-10-project-102-0183 和 executionId=EXEC-tenant-10-project-102-0183。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0183/executions/EXEC-tenant-10-project-102-0183/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v281 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M123" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N123" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O123" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P123" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q123" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R123" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0183</x:v>
       </x:c>
-      <x:c r="J123" s="19" t="str">
+      <x:c r="S123" s="19" t="str">
         <x:v>UTC 2026-08-10 16:08:00.000</x:v>
       </x:c>
-      <x:c r="K123" s="20" t="n">
+      <x:c r="T123" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L123" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M123" s="8" t="str">
+      <x:c r="U123" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -14581,25 +17541,49 @@
         <x:v>INC-tenant-10-project-102-0185</x:v>
       </x:c>
       <x:c r="G124" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H124" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I124" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J124" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0185 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0185/executions/EXEC-tenant-10-project-102-0185/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K124" s="8" t="str">
+        <x:v>2026-08-10T16:16:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0185 taskId=TASK-tenant-10-project-102-0185 executionId=EXEC-tenant-10-project-102-0185 objectId=object-25 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L124" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0185、taskId=TASK-tenant-10-project-102-0185 和 executionId=EXEC-tenant-10-project-102-0185。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0185/executions/EXEC-tenant-10-project-102-0185/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v283 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M124" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N124" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O124" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P124" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q124" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R124" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0185</x:v>
       </x:c>
-      <x:c r="J124" s="19" t="str">
+      <x:c r="S124" s="19" t="str">
         <x:v>UTC 2026-08-10 16:16:00.000</x:v>
       </x:c>
-      <x:c r="K124" s="20" t="n">
+      <x:c r="T124" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L124" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M124" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U124" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -14622,24 +17606,48 @@
         <x:v>INC-tenant-10-project-102-0186</x:v>
       </x:c>
       <x:c r="G125" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H125" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I125" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J125" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0186 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0186/executions/EXEC-tenant-10-project-102-0186/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K125" s="8" t="str">
+        <x:v>2026-08-10T16:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0186 taskId=TASK-tenant-10-project-102-0186 executionId=EXEC-tenant-10-project-102-0186 objectId=object-26 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L125" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0186、taskId=TASK-tenant-10-project-102-0186 和 executionId=EXEC-tenant-10-project-102-0186。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0186/executions/EXEC-tenant-10-project-102-0186/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v284 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M125" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N125" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O125" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P125" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q125" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R125" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0186</x:v>
       </x:c>
-      <x:c r="J125" s="19" t="str">
+      <x:c r="S125" s="19" t="str">
         <x:v>UTC 2026-08-10 16:24:00.000</x:v>
       </x:c>
-      <x:c r="K125" s="20" t="n">
+      <x:c r="T125" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L125" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M125" s="8" t="str">
+      <x:c r="U125" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14663,24 +17671,48 @@
         <x:v>INC-tenant-10-project-102-0188</x:v>
       </x:c>
       <x:c r="G126" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H126" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I126" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J126" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0188 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0188/executions/EXEC-tenant-10-project-102-0188/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K126" s="8" t="str">
+        <x:v>2026-08-10T16:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0188 taskId=TASK-tenant-10-project-102-0188 executionId=EXEC-tenant-10-project-102-0188 objectId=object-28 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L126" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0188、taskId=TASK-tenant-10-project-102-0188 和 executionId=EXEC-tenant-10-project-102-0188。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0188/executions/EXEC-tenant-10-project-102-0188/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v286 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M126" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N126" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O126" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P126" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q126" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R126" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0188</x:v>
       </x:c>
-      <x:c r="J126" s="19" t="str">
+      <x:c r="S126" s="19" t="str">
         <x:v>UTC 2026-08-10 16:32:00.000</x:v>
       </x:c>
-      <x:c r="K126" s="20" t="n">
+      <x:c r="T126" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L126" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M126" s="8" t="str">
+      <x:c r="U126" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14704,24 +17736,48 @@
         <x:v>INC-tenant-10-project-102-0189</x:v>
       </x:c>
       <x:c r="G127" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H127" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I127" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J127" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0189 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0189/executions/EXEC-tenant-10-project-102-0189/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K127" s="8" t="str">
+        <x:v>2026-08-10T16:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0189 taskId=TASK-tenant-10-project-102-0189 executionId=EXEC-tenant-10-project-102-0189 objectId=object-29 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L127" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0189、taskId=TASK-tenant-10-project-102-0189 和 executionId=EXEC-tenant-10-project-102-0189。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0189/executions/EXEC-tenant-10-project-102-0189/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v287 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M127" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N127" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O127" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P127" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q127" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R127" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0189</x:v>
       </x:c>
-      <x:c r="J127" s="19" t="str">
+      <x:c r="S127" s="19" t="str">
         <x:v>UTC 2026-08-10 16:40:00.000</x:v>
       </x:c>
-      <x:c r="K127" s="20" t="n">
+      <x:c r="T127" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L127" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M127" s="8" t="str">
+      <x:c r="U127" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14745,24 +17801,48 @@
         <x:v>INC-tenant-10-project-102-0191</x:v>
       </x:c>
       <x:c r="G128" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H128" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I128" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J128" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0191 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0191/executions/EXEC-tenant-10-project-102-0191/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K128" s="8" t="str">
+        <x:v>2026-08-10T16:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0191 taskId=TASK-tenant-10-project-102-0191 executionId=EXEC-tenant-10-project-102-0191 objectId=object-31 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L128" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0191、taskId=TASK-tenant-10-project-102-0191 和 executionId=EXEC-tenant-10-project-102-0191。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0191/executions/EXEC-tenant-10-project-102-0191/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v289 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M128" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N128" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O128" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P128" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q128" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R128" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0191</x:v>
       </x:c>
-      <x:c r="J128" s="19" t="str">
+      <x:c r="S128" s="19" t="str">
         <x:v>UTC 2026-08-10 16:48:00.000</x:v>
       </x:c>
-      <x:c r="K128" s="20" t="n">
+      <x:c r="T128" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L128" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M128" s="8" t="str">
+      <x:c r="U128" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14786,24 +17866,48 @@
         <x:v>INC-tenant-10-project-102-0192</x:v>
       </x:c>
       <x:c r="G129" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H129" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I129" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J129" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0192 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0192/executions/EXEC-tenant-10-project-102-0192/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K129" s="8" t="str">
+        <x:v>2026-08-10T16:56:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0192 taskId=TASK-tenant-10-project-102-0192 executionId=EXEC-tenant-10-project-102-0192 objectId=object-32 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L129" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0192、taskId=TASK-tenant-10-project-102-0192 和 executionId=EXEC-tenant-10-project-102-0192。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0192/executions/EXEC-tenant-10-project-102-0192/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v290 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M129" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N129" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O129" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P129" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q129" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R129" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0192</x:v>
       </x:c>
-      <x:c r="J129" s="19" t="str">
+      <x:c r="S129" s="19" t="str">
         <x:v>UTC 2026-08-10 16:56:00.000</x:v>
       </x:c>
-      <x:c r="K129" s="20" t="n">
+      <x:c r="T129" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L129" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M129" s="8" t="str">
+      <x:c r="U129" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14827,24 +17931,48 @@
         <x:v>INC-tenant-10-project-102-0194</x:v>
       </x:c>
       <x:c r="G130" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H130" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I130" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J130" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0194 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0194/executions/EXEC-tenant-10-project-102-0194/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K130" s="8" t="str">
+        <x:v>2026-08-10T17:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0194 taskId=TASK-tenant-10-project-102-0194 executionId=EXEC-tenant-10-project-102-0194 objectId=object-02 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L130" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0194、taskId=TASK-tenant-10-project-102-0194 和 executionId=EXEC-tenant-10-project-102-0194。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0194/executions/EXEC-tenant-10-project-102-0194/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v292 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M130" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N130" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O130" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P130" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q130" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R130" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0194</x:v>
       </x:c>
-      <x:c r="J130" s="19" t="str">
+      <x:c r="S130" s="19" t="str">
         <x:v>UTC 2026-08-10 17:04:00.000</x:v>
       </x:c>
-      <x:c r="K130" s="20" t="n">
+      <x:c r="T130" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L130" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M130" s="8" t="str">
+      <x:c r="U130" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14868,24 +17996,48 @@
         <x:v>INC-tenant-10-project-102-0195</x:v>
       </x:c>
       <x:c r="G131" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H131" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I131" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J131" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0195 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0195/executions/EXEC-tenant-10-project-102-0195/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K131" s="8" t="str">
+        <x:v>2026-08-10T17:12:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0195 taskId=TASK-tenant-10-project-102-0195 executionId=EXEC-tenant-10-project-102-0195 objectId=object-03 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L131" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0195、taskId=TASK-tenant-10-project-102-0195 和 executionId=EXEC-tenant-10-project-102-0195。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0195/executions/EXEC-tenant-10-project-102-0195/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v293 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M131" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N131" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O131" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P131" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q131" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R131" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0195</x:v>
       </x:c>
-      <x:c r="J131" s="19" t="str">
+      <x:c r="S131" s="19" t="str">
         <x:v>UTC 2026-08-10 17:12:00.000</x:v>
       </x:c>
-      <x:c r="K131" s="20" t="n">
+      <x:c r="T131" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L131" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M131" s="8" t="str">
+      <x:c r="U131" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14909,24 +18061,48 @@
         <x:v>INC-tenant-10-project-102-0197</x:v>
       </x:c>
       <x:c r="G132" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H132" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I132" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J132" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0197 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0197/executions/EXEC-tenant-10-project-102-0197/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K132" s="8" t="str">
+        <x:v>2026-08-10T17:20:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0197 taskId=TASK-tenant-10-project-102-0197 executionId=EXEC-tenant-10-project-102-0197 objectId=object-05 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L132" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0197、taskId=TASK-tenant-10-project-102-0197 和 executionId=EXEC-tenant-10-project-102-0197。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0197/executions/EXEC-tenant-10-project-102-0197/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v295 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M132" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N132" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O132" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P132" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q132" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R132" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0197</x:v>
       </x:c>
-      <x:c r="J132" s="19" t="str">
+      <x:c r="S132" s="19" t="str">
         <x:v>UTC 2026-08-10 17:20:00.000</x:v>
       </x:c>
-      <x:c r="K132" s="20" t="n">
+      <x:c r="T132" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L132" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M132" s="8" t="str">
+      <x:c r="U132" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14950,24 +18126,48 @@
         <x:v>INC-tenant-10-project-102-0198</x:v>
       </x:c>
       <x:c r="G133" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H133" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I133" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J133" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0198 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0198/executions/EXEC-tenant-10-project-102-0198/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K133" s="8" t="str">
+        <x:v>2026-08-10T17:28:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0198 taskId=TASK-tenant-10-project-102-0198 executionId=EXEC-tenant-10-project-102-0198 objectId=object-06 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L133" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0198、taskId=TASK-tenant-10-project-102-0198 和 executionId=EXEC-tenant-10-project-102-0198。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0198/executions/EXEC-tenant-10-project-102-0198/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v296 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M133" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N133" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O133" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P133" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q133" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R133" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0198</x:v>
       </x:c>
-      <x:c r="J133" s="19" t="str">
+      <x:c r="S133" s="19" t="str">
         <x:v>UTC 2026-08-10 17:28:00.000</x:v>
       </x:c>
-      <x:c r="K133" s="20" t="n">
+      <x:c r="T133" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L133" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M133" s="8" t="str">
+      <x:c r="U133" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -14991,25 +18191,49 @@
         <x:v>INC-tenant-10-project-102-0200</x:v>
       </x:c>
       <x:c r="G134" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H134" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I134" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J134" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0200 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0200/executions/EXEC-tenant-10-project-102-0200/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K134" s="8" t="str">
+        <x:v>2026-08-10T17:36:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0200 taskId=TASK-tenant-10-project-102-0200 executionId=EXEC-tenant-10-project-102-0200 objectId=object-08 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L134" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0200、taskId=TASK-tenant-10-project-102-0200 和 executionId=EXEC-tenant-10-project-102-0200。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0200/executions/EXEC-tenant-10-project-102-0200/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v298 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M134" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N134" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O134" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P134" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q134" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R134" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0200</x:v>
       </x:c>
-      <x:c r="J134" s="19" t="str">
+      <x:c r="S134" s="19" t="str">
         <x:v>UTC 2026-08-10 17:36:00.000</x:v>
       </x:c>
-      <x:c r="K134" s="20" t="n">
+      <x:c r="T134" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L134" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M134" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U134" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -15032,24 +18256,48 @@
         <x:v>INC-tenant-10-project-102-0201</x:v>
       </x:c>
       <x:c r="G135" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H135" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I135" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J135" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0201 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0201/executions/EXEC-tenant-10-project-102-0201/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K135" s="8" t="str">
+        <x:v>2026-08-10T17:44:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0201 taskId=TASK-tenant-10-project-102-0201 executionId=EXEC-tenant-10-project-102-0201 objectId=object-09 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L135" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0201、taskId=TASK-tenant-10-project-102-0201 和 executionId=EXEC-tenant-10-project-102-0201。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0201/executions/EXEC-tenant-10-project-102-0201/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v299 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M135" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N135" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O135" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P135" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q135" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R135" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0201</x:v>
       </x:c>
-      <x:c r="J135" s="19" t="str">
+      <x:c r="S135" s="19" t="str">
         <x:v>UTC 2026-08-10 17:44:00.000</x:v>
       </x:c>
-      <x:c r="K135" s="20" t="n">
+      <x:c r="T135" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L135" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M135" s="8" t="str">
+      <x:c r="U135" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15073,25 +18321,49 @@
         <x:v>INC-tenant-10-project-102-0203</x:v>
       </x:c>
       <x:c r="G136" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>PERMISSION_DENIED</x:v>
       </x:c>
       <x:c r="H136" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>按钮可能不可用，或提交后收到 403；已有任务状态不会因为拒绝而改变</x:v>
       </x:c>
       <x:c r="I136" s="8" t="str">
+        <x:v>当前账号没有执行该操作的权限，或批准范围与目标资源不匹配</x:v>
+      </x:c>
+      <x:c r="J136" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0203 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0203/executions/EXEC-tenant-10-project-102-0203/logs；服务日志：docker compose logs permission-admin，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K136" s="8" t="str">
+        <x:v>2026-08-10T17:52:00.000Z level=ERROR service=permission-admin traceId=trace-tenant-10-project-102-0203 taskId=TASK-tenant-10-project-102-0203 executionId=EXEC-tenant-10-project-102-0203 objectId=object-11 errorCode=PERMISSION_DENIED message="authorization decision DENY; resourceAction or dataScope not satisfied; sideEffectStarted=false" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L136" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0203、taskId=TASK-tenant-10-project-102-0203 和 executionId=EXEC-tenant-10-project-102-0203。 2. 调用执行日志接口，找到最早出现的 errorCode=PERMISSION_DENIED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0203/executions/EXEC-tenant-10-project-102-0203/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 permission-admin 日志，按 traceId 检索关键行；同时核对关联服务 Gateway、data-sync、agent-runtime。 5. 围绕“核对 actor、role、resourceType、action、tenant/project 范围、审批主体、有效期和批准是否已消费”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v301 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed。</x:v>
+      </x:c>
+      <x:c r="M136" s="8" t="str">
+        <x:v>当前账号的角色或审批只允许查看，不能执行这次修改；也可能是用户切到了错误项目或批准已经过期</x:v>
+      </x:c>
+      <x:c r="N136" s="8" t="str">
+        <x:v>permission-admin 返回 DENY，资源动作、数据范围或双主体审批事实至少一项不满足，控制面在副作用前 fail-closed</x:v>
+      </x:c>
+      <x:c r="O136" s="8" t="str">
+        <x:v>确认 Gateway 的路由动作映射与业务服务二次对象校验一致，排除缓存未失效或把 GET/POST 映射到错误动作的代码问题</x:v>
+      </x:c>
+      <x:c r="P136" s="8" t="str">
+        <x:v>确认当前租户和项目；查看所需资源动作；由不同的有权限批准人补充最小范围审批；策略变更后刷新授权缓存；重新提交原操作</x:v>
+      </x:c>
+      <x:c r="Q136" s="8" t="str">
+        <x:v>配置正确角色、路由策略、数据范围或审批，不通过改代码绕过授权；若动作映射错误，修复 Gateway 规则并补权限回归测试</x:v>
+      </x:c>
+      <x:c r="R136" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0203</x:v>
       </x:c>
-      <x:c r="J136" s="19" t="str">
+      <x:c r="S136" s="19" t="str">
         <x:v>UTC 2026-08-10 17:52:00.000</x:v>
       </x:c>
-      <x:c r="K136" s="20" t="n">
+      <x:c r="T136" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L136" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M136" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U136" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -15114,24 +18386,48 @@
         <x:v>INC-tenant-10-project-102-0204</x:v>
       </x:c>
       <x:c r="G137" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H137" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I137" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J137" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0204 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0204/executions/EXEC-tenant-10-project-102-0204/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K137" s="8" t="str">
+        <x:v>2026-08-10T18:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0204 taskId=TASK-tenant-10-project-102-0204 executionId=EXEC-tenant-10-project-102-0204 objectId=object-12 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L137" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0204、taskId=TASK-tenant-10-project-102-0204 和 executionId=EXEC-tenant-10-project-102-0204。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0204/executions/EXEC-tenant-10-project-102-0204/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v302 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M137" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N137" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O137" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P137" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q137" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R137" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0204</x:v>
       </x:c>
-      <x:c r="J137" s="19" t="str">
+      <x:c r="S137" s="19" t="str">
         <x:v>UTC 2026-08-10 18:00:00.000</x:v>
       </x:c>
-      <x:c r="K137" s="20" t="n">
+      <x:c r="T137" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L137" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M137" s="8" t="str">
+      <x:c r="U137" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15155,24 +18451,48 @@
         <x:v>INC-tenant-10-project-102-0206</x:v>
       </x:c>
       <x:c r="G138" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>FIELD_MAPPING_MISSING</x:v>
       </x:c>
       <x:c r="H138" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>字段映射页突出显示未映射字段，运行时则可能出现目标列缺失或写入失败</x:v>
       </x:c>
       <x:c r="I138" s="8" t="str">
+        <x:v>目标字段缺少来源映射，请选择唯一兼容字段或补充转换规则</x:v>
+      </x:c>
+      <x:c r="J138" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0206 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0206/executions/EXEC-tenant-10-project-102-0206/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K138" s="8" t="str">
+        <x:v>2026-08-10T18:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0206 taskId=TASK-tenant-10-project-102-0206 executionId=EXEC-tenant-10-project-102-0206 objectId=object-14 errorCode=FIELD_MAPPING_MISSING message="required target field has no active source mapping; candidateCount evaluated from metadata" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L138" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0206、taskId=TASK-tenant-10-project-102-0206 和 executionId=EXEC-tenant-10-project-102-0206。 2. 调用执行日志接口，找到最早出现的 errorCode=FIELD_MAPPING_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0206/executions/EXEC-tenant-10-project-102-0206/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“检查目标字段是否必填、是否有默认值、当前映射是否引用已删除字段、候选源字段数量和类型兼容性”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v304 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认。</x:v>
+      </x:c>
+      <x:c r="M138" s="8" t="str">
+        <x:v>任务不知道应该把哪个源字段写入目标字段，继续运行可能把数据写错列，所以系统停止</x:v>
+      </x:c>
+      <x:c r="N138" s="8" t="str">
+        <x:v>发布映射无法解析到当前元数据中的源字段，且目标字段需要显式值或唯一兼容候选尚未确认</x:v>
+      </x:c>
+      <x:c r="O138" s="8" t="str">
+        <x:v>确认映射修复器只在候选唯一、目标未占用、类型和主键属性一致时自动改名，不能把歧义候选静默取第一项</x:v>
+      </x:c>
+      <x:c r="P138" s="8" t="str">
+        <x:v>刷新两端元数据；核对字段含义；唯一兼容候选可自动改映射；存在多个候选时由用户选择；保存新版本并重新预检</x:v>
+      </x:c>
+      <x:c r="Q138" s="8" t="str">
+        <x:v>更新字段映射配置；若候选算法漏掉合法字段，修复类型/序号/主键兼容判断并增加歧义测试</x:v>
+      </x:c>
+      <x:c r="R138" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0206</x:v>
       </x:c>
-      <x:c r="J138" s="19" t="str">
+      <x:c r="S138" s="19" t="str">
         <x:v>UTC 2026-08-10 18:08:00.000</x:v>
       </x:c>
-      <x:c r="K138" s="20" t="n">
+      <x:c r="T138" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L138" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M138" s="8" t="str">
+      <x:c r="U138" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15196,24 +18516,48 @@
         <x:v>INC-tenant-10-project-102-0207</x:v>
       </x:c>
       <x:c r="G139" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H139" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I139" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J139" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0207 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0207/executions/EXEC-tenant-10-project-102-0207/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K139" s="8" t="str">
+        <x:v>2026-08-10T18:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0207 taskId=TASK-tenant-10-project-102-0207 executionId=EXEC-tenant-10-project-102-0207 objectId=object-15 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L139" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0207、taskId=TASK-tenant-10-project-102-0207 和 executionId=EXEC-tenant-10-project-102-0207。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0207/executions/EXEC-tenant-10-project-102-0207/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v305 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M139" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N139" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O139" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P139" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q139" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R139" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0207</x:v>
       </x:c>
-      <x:c r="J139" s="19" t="str">
+      <x:c r="S139" s="19" t="str">
         <x:v>UTC 2026-08-10 18:16:00.000</x:v>
       </x:c>
-      <x:c r="K139" s="20" t="n">
+      <x:c r="T139" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L139" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M139" s="8" t="str">
+      <x:c r="U139" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15237,24 +18581,48 @@
         <x:v>INC-tenant-10-project-102-0209</x:v>
       </x:c>
       <x:c r="G140" s="8" t="str">
-        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
+        <x:v>NUMERIC_OVERFLOW</x:v>
       </x:c>
       <x:c r="H140" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>少数大额记录写入失败，普通记录可能已经成功</x:v>
       </x:c>
       <x:c r="I140" s="8" t="str">
+        <x:v>数值超出目标字段可保存范围，系统未进行静默截断</x:v>
+      </x:c>
+      <x:c r="J140" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0209 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0209/executions/EXEC-tenant-10-project-102-0209/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K140" s="8" t="str">
+        <x:v>2026-08-10T18:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0209 taskId=TASK-tenant-10-project-102-0209 executionId=EXEC-tenant-10-project-102-0209 objectId=object-17 errorCode=NUMERIC_OVERFLOW message="SQLState=22003 numeric value out of range; target precision or scale exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L140" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0209、taskId=TASK-tenant-10-project-102-0209 和 executionId=EXEC-tenant-10-project-102-0209。 2. 调用执行日志接口，找到最早出现的 errorCode=NUMERIC_OVERFLOW，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0209/executions/EXEC-tenant-10-project-102-0209/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“检查失败字段的最值摘要、目标 precision/scale、超限记录数量和最近成功数据分布”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v307 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 numeric precision/scale 无法表示源值，数据库返回 22003。</x:v>
+      </x:c>
+      <x:c r="M140" s="8" t="str">
+        <x:v>目标列的数字格子太小，当前数值放不下</x:v>
+      </x:c>
+      <x:c r="N140" s="8" t="str">
+        <x:v>目标 numeric precision/scale 无法表示源值，数据库返回 22003</x:v>
+      </x:c>
+      <x:c r="O140" s="8" t="str">
+        <x:v>确认 Decimal 转换没有先经过浮点数导致精度膨胀，并检查 JDBC scale 绑定</x:v>
+      </x:c>
+      <x:c r="P140" s="8" t="str">
+        <x:v>禁止截断；评估调整字段映射、单位换算或目标列精度；DDL 变更必须审批；修复后仅重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q140" s="8" t="str">
+        <x:v>修改转换规则或经审批扩大目标字段精度；若代码使用浮点中转，改用 Decimal/BigDecimal 并增加极值测试</x:v>
+      </x:c>
+      <x:c r="R140" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0209</x:v>
       </x:c>
-      <x:c r="J140" s="19" t="str">
+      <x:c r="S140" s="19" t="str">
         <x:v>UTC 2026-08-10 18:24:00.000</x:v>
       </x:c>
-      <x:c r="K140" s="20" t="n">
+      <x:c r="T140" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L140" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M140" s="8" t="str">
+      <x:c r="U140" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15278,25 +18646,49 @@
         <x:v>INC-tenant-10-project-102-0210</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
-        <x:v>DDL_REQUIRED</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H141" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I141" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J141" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0210 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0210/executions/EXEC-tenant-10-project-102-0210/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K141" s="8" t="str">
+        <x:v>2026-08-10T18:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0210 taskId=TASK-tenant-10-project-102-0210 executionId=EXEC-tenant-10-project-102-0210 objectId=object-18 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L141" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0210、taskId=TASK-tenant-10-project-102-0210 和 executionId=EXEC-tenant-10-project-102-0210。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0210/executions/EXEC-tenant-10-project-102-0210/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v308 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M141" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N141" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O141" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P141" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q141" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R141" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0210</x:v>
       </x:c>
-      <x:c r="J141" s="19" t="str">
+      <x:c r="S141" s="19" t="str">
         <x:v>UTC 2026-08-10 18:32:00.000</x:v>
       </x:c>
-      <x:c r="K141" s="20" t="n">
+      <x:c r="T141" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L141" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M141" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U141" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -15319,24 +18711,48 @@
         <x:v>INC-tenant-10-project-102-0212</x:v>
       </x:c>
       <x:c r="G142" s="8" t="str">
-        <x:v>CONNECTION_TIMEOUT</x:v>
+        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
       </x:c>
       <x:c r="H142" s="8" t="str">
-        <x:v>网络或端点超时；核对 连接耗时、DNS、目标健康</x:v>
+        <x:v>任务重试后出现重复键错误，已成功数据不会被系统直接覆盖</x:v>
       </x:c>
       <x:c r="I142" s="8" t="str">
+        <x:v>目标中已存在相同唯一键，请确认这是幂等重放还是业务数据冲突</x:v>
+      </x:c>
+      <x:c r="J142" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0212 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0212/executions/EXEC-tenant-10-project-102-0212/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K142" s="8" t="str">
+        <x:v>2026-08-10T18:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0212 taskId=TASK-tenant-10-project-102-0212 executionId=EXEC-tenant-10-project-102-0212 objectId=object-20 errorCode=UNIQUE_CONSTRAINT_VIOLATION message="SQLState=23505 unique constraint violation; existingReceipt lookup required" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L142" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0212、taskId=TASK-tenant-10-project-102-0212 和 executionId=EXEC-tenant-10-project-102-0212。 2. 调用执行日志接口，找到最早出现的 errorCode=UNIQUE_CONSTRAINT_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0212/executions/EXEC-tenant-10-project-102-0212/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、checkpoint/幂等账本。 5. 围绕“检查约束名、键摘要、上次提交回执、checkpoint、attempt 和目标现有记录来源”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v310 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：业务键重复或幂等回执丢失，INSERT 触发 23505。</x:v>
+      </x:c>
+      <x:c r="M142" s="8" t="str">
+        <x:v>目标表里已经有相同编号的记录，系统不能确定应该忽略、更新还是报错</x:v>
+      </x:c>
+      <x:c r="N142" s="8" t="str">
+        <x:v>业务键重复或幂等回执丢失，INSERT 触发 23505</x:v>
+      </x:c>
+      <x:c r="O142" s="8" t="str">
+        <x:v>确认提交成功与 checkpoint 更新之间是否存在崩溃窗口，并检查 upsert/insert 策略是否符合任务模式</x:v>
+      </x:c>
+      <x:c r="P142" s="8" t="str">
+        <x:v>先判断是否为同一次执行的已提交记录；幂等重放可确认成功并前移位点；真实业务冲突转人工决定，不自动覆盖</x:v>
+      </x:c>
+      <x:c r="Q142" s="8" t="str">
+        <x:v>修复 checkpoint 与提交回执顺序或调整经审核的 upsert 策略；增加提交后崩溃重放测试</x:v>
+      </x:c>
+      <x:c r="R142" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0212</x:v>
       </x:c>
-      <x:c r="J142" s="19" t="str">
+      <x:c r="S142" s="19" t="str">
         <x:v>UTC 2026-08-10 18:40:00.000</x:v>
       </x:c>
-      <x:c r="K142" s="20" t="n">
+      <x:c r="T142" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L142" s="8" t="str">
-        <x:v>有界增加超时或等待端点恢复</x:v>
-      </x:c>
-      <x:c r="M142" s="8" t="str">
+      <x:c r="U142" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15360,25 +18776,49 @@
         <x:v>INC-tenant-10-project-102-0213</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
-        <x:v>AUTHENTICATION_FAILED</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H143" s="8" t="str">
-        <x:v>凭据失效或引用错误；核对 认证响应与凭据引用版本</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I143" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J143" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0213 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0213/executions/EXEC-tenant-10-project-102-0213/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K143" s="8" t="str">
+        <x:v>2026-08-10T18:48:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0213 taskId=TASK-tenant-10-project-102-0213 executionId=EXEC-tenant-10-project-102-0213 objectId=object-21 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L143" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0213、taskId=TASK-tenant-10-project-102-0213 和 executionId=EXEC-tenant-10-project-102-0213。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0213/executions/EXEC-tenant-10-project-102-0213/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v311 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M143" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N143" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O143" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P143" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q143" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R143" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0213</x:v>
       </x:c>
-      <x:c r="J143" s="19" t="str">
+      <x:c r="S143" s="19" t="str">
         <x:v>UTC 2026-08-10 18:48:00.000</x:v>
       </x:c>
-      <x:c r="K143" s="20" t="n">
+      <x:c r="T143" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L143" s="8" t="str">
-        <x:v>退出自治并要求有权限主体轮换凭据</x:v>
-      </x:c>
-      <x:c r="M143" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U143" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -15401,25 +18841,49 @@
         <x:v>INC-tenant-10-project-102-0215</x:v>
       </x:c>
       <x:c r="G144" s="8" t="str">
-        <x:v>PERMISSION_DENIED</x:v>
+        <x:v>KAFKA_BACKLOG_HIGH</x:v>
       </x:c>
       <x:c r="H144" s="8" t="str">
-        <x:v>资源动作未授权；核对 actor、resource、action、审批事实</x:v>
+        <x:v>用户提交任务后长时间停在排队中，状态更新明显延迟</x:v>
       </x:c>
       <x:c r="I144" s="8" t="str">
+        <x:v>任务已受理但队列处理延迟较高，系统正在排队</x:v>
+      </x:c>
+      <x:c r="J144" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0215 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0215/executions/EXEC-tenant-10-project-102-0215/logs；服务日志：docker compose logs kafka，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K144" s="8" t="str">
+        <x:v>2026-08-10T18:56:00.000Z level=ERROR service=Kafka traceId=trace-tenant-10-project-102-0215 taskId=TASK-tenant-10-project-102-0215 executionId=EXEC-tenant-10-project-102-0215 objectId=object-23 errorCode=KAFKA_BACKLOG_HIGH message="consumer group lag exceeds budget; oldestMessageAgeSeconds growing; retryTopic hot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L144" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0215、taskId=TASK-tenant-10-project-102-0215 和 executionId=EXEC-tenant-10-project-102-0215。 2. 调用执行日志接口，找到最早出现的 errorCode=KAFKA_BACKLOG_HIGH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0215/executions/EXEC-tenant-10-project-102-0215/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 Kafka 日志，按 traceId 检索关键行；同时核对关联服务 agent-runtime、python-ai-runtime、data-sync。 5. 围绕“按 consumer group 查看 partition lag、最老消息、消费速率、实例数、重试/DLT 和处理时延”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v313 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长。</x:v>
+      </x:c>
+      <x:c r="M144" s="8" t="str">
+        <x:v>进入队列的任务比系统处理得快，或者某条坏消息一直重试占住队列</x:v>
+      </x:c>
+      <x:c r="N144" s="8" t="str">
+        <x:v>消费者吞吐低于生产吞吐或 retry 循环造成 group lag 持续增长</x:v>
+      </x:c>
+      <x:c r="O144" s="8" t="str">
+        <x:v>检查单条消息是否长时间阻塞消费线程、是否缺少幂等导致反复失败，以及分区键是否形成热点</x:v>
+      </x:c>
+      <x:c r="P144" s="8" t="str">
+        <x:v>隔离坏消息；确认消费者健康；在容量许可下扩容；优化慢处理；保持 retry 次数有界；不通过删除消息掩盖问题</x:v>
+      </x:c>
+      <x:c r="Q144" s="8" t="str">
+        <x:v>调整消费者容量/分区或修复阻塞处理代码；增加积压、热点分区和 DLT 回归</x:v>
+      </x:c>
+      <x:c r="R144" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0215</x:v>
       </x:c>
-      <x:c r="J144" s="19" t="str">
+      <x:c r="S144" s="19" t="str">
         <x:v>UTC 2026-08-10 18:56:00.000</x:v>
       </x:c>
-      <x:c r="K144" s="20" t="n">
+      <x:c r="T144" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L144" s="8" t="str">
-        <x:v>退出自治并说明所需权限</x:v>
-      </x:c>
-      <x:c r="M144" s="8" t="str">
-        <x:v>ATTENTION_REQUIRED</x:v>
+      <x:c r="U144" s="8" t="str">
+        <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -15442,24 +18906,48 @@
         <x:v>INC-tenant-10-project-102-0216</x:v>
       </x:c>
       <x:c r="G145" s="8" t="str">
-        <x:v>RATE_LIMIT_EXCEEDED</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H145" s="8" t="str">
-        <x:v>来源或目标端限流；核对 429、限流头、连接器容量</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I145" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J145" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0216 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0216/executions/EXEC-tenant-10-project-102-0216/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K145" s="8" t="str">
+        <x:v>2026-08-10T19:04:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0216 taskId=TASK-tenant-10-project-102-0216 executionId=EXEC-tenant-10-project-102-0216 objectId=object-24 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L145" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0216、taskId=TASK-tenant-10-project-102-0216 和 executionId=EXEC-tenant-10-project-102-0216。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0216/executions/EXEC-tenant-10-project-102-0216/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v314 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M145" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N145" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O145" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P145" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q145" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R145" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0216</x:v>
       </x:c>
-      <x:c r="J145" s="19" t="str">
+      <x:c r="S145" s="19" t="str">
         <x:v>UTC 2026-08-10 19:04:00.000</x:v>
       </x:c>
-      <x:c r="K145" s="20" t="n">
+      <x:c r="T145" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L145" s="8" t="str">
-        <x:v>降低并发和批量后有界退避</x:v>
-      </x:c>
-      <x:c r="M145" s="8" t="str">
+      <x:c r="U145" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15483,24 +18971,48 @@
         <x:v>INC-tenant-10-project-102-0218</x:v>
       </x:c>
       <x:c r="G146" s="8" t="str">
-        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
+        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
       </x:c>
       <x:c r="H146" s="8" t="str">
-        <x:v>来源结构发生变化；核对 schema 指纹与元数据差异</x:v>
+        <x:v>多个任务同时变慢或写入暂停，目标端可能返回连接过多或磁盘不足</x:v>
       </x:c>
       <x:c r="I146" s="8" t="str">
+        <x:v>目标系统容量不足，系统已暂停放大负载并等待恢复</x:v>
+      </x:c>
+      <x:c r="J146" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0218 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0218/executions/EXEC-tenant-10-project-102-0218/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K146" s="8" t="str">
+        <x:v>2026-08-10T19:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0218 taskId=TASK-tenant-10-project-102-0218 executionId=EXEC-tenant-10-project-102-0218 objectId=object-26 errorCode=TARGET_CAPACITY_EXCEEDED message="target capacity guard rejected write; connectionPool or storage threshold exceeded" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L146" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0218、taskId=TASK-tenant-10-project-102-0218 和 executionId=EXEC-tenant-10-project-102-0218。 2. 调用执行日志接口，找到最早出现的 errorCode=TARGET_CAPACITY_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0218/executions/EXEC-tenant-10-project-102-0218/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、监控系统。 5. 围绕“检查目标连接数、等待事件、磁盘、WAL、I/O、任务并发和配额，不只看单个任务日志”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v316 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入。</x:v>
+      </x:c>
+      <x:c r="M146" s="8" t="str">
+        <x:v>目标数据库当前太忙或空间不足，继续写入会让更多任务失败</x:v>
+      </x:c>
+      <x:c r="N146" s="8" t="str">
+        <x:v>目标资源指标超过治理阈值，容量门禁或数据库拒绝新写入</x:v>
+      </x:c>
+      <x:c r="O146" s="8" t="str">
+        <x:v>确认连接池归还、批次提交和背压生效，排除连接泄漏或无界队列</x:v>
+      </x:c>
+      <x:c r="P146" s="8" t="str">
+        <x:v>降低 channel/batch；暂停非关键任务；释放异常连接；扩容需审批；容量恢复后重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q146" s="8" t="str">
+        <x:v>调整受治理运行参数或基础设施容量；若连接泄漏，修复资源关闭逻辑并增加压力测试</x:v>
+      </x:c>
+      <x:c r="R146" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0218</x:v>
       </x:c>
-      <x:c r="J146" s="19" t="str">
+      <x:c r="S146" s="19" t="str">
         <x:v>UTC 2026-08-10 19:12:00.000</x:v>
       </x:c>
-      <x:c r="K146" s="20" t="n">
+      <x:c r="T146" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L146" s="8" t="str">
-        <x:v>刷新元数据；唯一兼容映射才修复</x:v>
-      </x:c>
-      <x:c r="M146" s="8" t="str">
+      <x:c r="U146" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15524,24 +19036,48 @@
         <x:v>INC-tenant-10-project-102-0219</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
-        <x:v>FIELD_MAPPING_MISSING</x:v>
+        <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H147" s="8" t="str">
-        <x:v>目标字段缺少映射；核对 源目标字段与历史成功映射</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I147" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J147" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0219 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0219/executions/EXEC-tenant-10-project-102-0219/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K147" s="8" t="str">
+        <x:v>2026-08-10T19:20:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0219 taskId=TASK-tenant-10-project-102-0219 executionId=EXEC-tenant-10-project-102-0219 objectId=object-27 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L147" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0219、taskId=TASK-tenant-10-project-102-0219 和 executionId=EXEC-tenant-10-project-102-0219。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0219/executions/EXEC-tenant-10-project-102-0219/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v317 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M147" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N147" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O147" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P147" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q147" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R147" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0219</x:v>
       </x:c>
-      <x:c r="J147" s="19" t="str">
+      <x:c r="S147" s="19" t="str">
         <x:v>UTC 2026-08-10 19:20:00.000</x:v>
       </x:c>
-      <x:c r="K147" s="20" t="n">
+      <x:c r="T147" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L147" s="8" t="str">
-        <x:v>唯一映射可修复，歧义时退出</x:v>
-      </x:c>
-      <x:c r="M147" s="8" t="str">
+      <x:c r="U147" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15565,24 +19101,48 @@
         <x:v>INC-tenant-10-project-102-0221</x:v>
       </x:c>
       <x:c r="G148" s="8" t="str">
-        <x:v>NOT_NULL_VIOLATION</x:v>
+        <x:v>CONNECTION_TIMEOUT</x:v>
       </x:c>
       <x:c r="H148" s="8" t="str">
-        <x:v>目标非空字段收到空值；核对 错误字段、字段画像、已批准默认值</x:v>
+        <x:v>数据源能够在下拉框中看到，但连接校验持续转圈，随后任务停在预检或读取阶段</x:v>
       </x:c>
       <x:c r="I148" s="8" t="str">
+        <x:v>连接源数据源超时，请稍后重试；若持续出现，请联系运维并提供 traceId</x:v>
+      </x:c>
+      <x:c r="J148" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0221 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0221/executions/EXEC-tenant-10-project-102-0221/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K148" s="8" t="str">
+        <x:v>2026-08-10T19:28:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0221 taskId=TASK-tenant-10-project-102-0221 executionId=EXEC-tenant-10-project-102-0221 objectId=object-29 errorCode=CONNECTION_TIMEOUT message="connect timeout after 30000ms while probing datasource endpoint; transportFailure=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L148" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0221、taskId=TASK-tenant-10-project-102-0221 和 executionId=EXEC-tenant-10-project-102-0221。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTION_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0221/executions/EXEC-tenant-10-project-102-0221/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Gateway、DNS/网络和源数据库。 5. 围绕“先区分 DNS 解析失败、端口不通、目标实例未启动、Nacos 旧实例地址和客户端 timeout 过小”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v319 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前。</x:v>
+      </x:c>
+      <x:c r="M148" s="8" t="str">
+        <x:v>系统在规定时间内没有连上所选数据源，常见原因是地址或端口填错、数据库没启动、网络不通，或者连接等待时间配置得太短</x:v>
+      </x:c>
+      <x:c r="N148" s="8" t="str">
+        <x:v>数据源探测或 run-once HTTP 调用抛出 transport timeout，未在客户端截止时间内取得成功 envelope；错误发生在业务 SQL 执行之前</x:v>
+      </x:c>
+      <x:c r="O148" s="8" t="str">
+        <x:v>如果目标健康且同机网络可达，但请求仍固定访问旧地址，应检查服务发现缓存和 HTTP 客户端地址刷新；如果只有大表首批读取超时，应检查 run-once 超时投影而不是误判为凭据失败</x:v>
+      </x:c>
+      <x:c r="P148" s="8" t="str">
+        <x:v>核对数据源主机和端口；从运行节点测试 DNS 与 TCP；确认目标数据库健康；清理失效服务实例；仅在连接确实较慢且授权允许时有界增加 timeout；重新执行连接测试和预检</x:v>
+      </x:c>
+      <x:c r="Q148" s="8" t="str">
+        <x:v>配置问题修改数据源地址、服务发现实例或 timeout 上限；若代码错误缓存了旧地址，则修复客户端实例刷新逻辑并增加连接拒绝、DNS 失败和读取超时回归测试</x:v>
+      </x:c>
+      <x:c r="R148" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0221</x:v>
       </x:c>
-      <x:c r="J148" s="19" t="str">
+      <x:c r="S148" s="19" t="str">
         <x:v>UTC 2026-08-10 19:28:00.000</x:v>
       </x:c>
-      <x:c r="K148" s="20" t="n">
+      <x:c r="T148" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L148" s="8" t="str">
-        <x:v>使用已批准默认值，不放宽约束</x:v>
-      </x:c>
-      <x:c r="M148" s="8" t="str">
+      <x:c r="U148" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15606,25 +19166,49 @@
         <x:v>INC-tenant-10-project-102-0222</x:v>
       </x:c>
       <x:c r="G149" s="8" t="str">
-        <x:v>DATA_TYPE_MISMATCH</x:v>
+        <x:v>AUTHENTICATION_FAILED</x:v>
       </x:c>
       <x:c r="H149" s="8" t="str">
-        <x:v>源目标类型不兼容；核对 类型、精度、长度与样本统计</x:v>
+        <x:v>连接测试立即失败，任务详情提示认证失败，但页面不会展示用户名、密码或 Token 原文</x:v>
       </x:c>
       <x:c r="I149" s="8" t="str">
+        <x:v>数据源认证失败，请由有权限的管理员检查凭据引用是否有效</x:v>
+      </x:c>
+      <x:c r="J149" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0222 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0222/executions/EXEC-tenant-10-project-102-0222/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K149" s="8" t="str">
+        <x:v>2026-08-10T19:36:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0222 taskId=TASK-tenant-10-project-102-0222 executionId=EXEC-tenant-10-project-102-0222 objectId=object-30 errorCode=AUTHENTICATION_FAILED message="authentication rejected by datasource; credentialRefVersion mismatch; secretValueRedacted=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L149" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0222、taskId=TASK-tenant-10-project-102-0222 和 executionId=EXEC-tenant-10-project-102-0222。 2. 调用执行日志接口，找到最早出现的 errorCode=AUTHENTICATION_FAILED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0222/executions/EXEC-tenant-10-project-102-0222/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 Secret 管理、源数据库、data-sync。 5. 围绕“查看数据库返回的认证状态、当前 credentialRef 版本和最近一次成功执行使用的引用版本，禁止在日志中打印密码”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v320 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致。</x:v>
+      </x:c>
+      <x:c r="M149" s="8" t="str">
+        <x:v>系统保存的是凭据引用而不是明文密码；当前引用已经失效、版本选错，或数据库端账号被锁定，因此连接器被拒绝</x:v>
+      </x:c>
+      <x:c r="N149" s="8" t="str">
+        <x:v>连接器建立会话时收到认证拒绝，credential reference 与 Secret 当前版本或数据库账号状态不一致</x:v>
+      </x:c>
+      <x:c r="O149" s="8" t="str">
+        <x:v>确认连接器是否把凭据引用解析成了最新 Secret，以及轮换后连接池是否仍持有旧连接；401/28P01 等认证错误不能被错误标记为自动重试</x:v>
+      </x:c>
+      <x:c r="P149" s="8" t="str">
+        <x:v>由有权限主体核对账号状态；在 Secret 管理系统轮换或修正凭据；更新数据源的凭据引用；关闭旧连接池；重新连接测试。自治 Loop 不得猜测或修改凭据</x:v>
+      </x:c>
+      <x:c r="Q149" s="8" t="str">
+        <x:v>通常修改 Secret 或凭据引用；若轮换后连接池未刷新，则修复连接池失效逻辑并增加凭据版本切换测试</x:v>
+      </x:c>
+      <x:c r="R149" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0222</x:v>
       </x:c>
-      <x:c r="J149" s="19" t="str">
+      <x:c r="S149" s="19" t="str">
         <x:v>UTC 2026-08-10 19:36:00.000</x:v>
       </x:c>
-      <x:c r="K149" s="20" t="n">
+      <x:c r="T149" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L149" s="8" t="str">
-        <x:v>无损转换可修复，有损转换退出</x:v>
-      </x:c>
-      <x:c r="M149" s="8" t="str">
-        <x:v>RECOVERED</x:v>
+      <x:c r="U149" s="8" t="str">
+        <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -15647,24 +19231,48 @@
         <x:v>INC-tenant-10-project-102-0224</x:v>
       </x:c>
       <x:c r="G150" s="8" t="str">
-        <x:v>NUMERIC_OVERFLOW</x:v>
+        <x:v>RATE_LIMIT_EXCEEDED</x:v>
       </x:c>
       <x:c r="H150" s="8" t="str">
-        <x:v>数值超过目标精度；核对 最值、precision 与 scale</x:v>
+        <x:v>任务速度突然下降并进入有界重试，执行详情显示限流而不是普通网络失败</x:v>
       </x:c>
       <x:c r="I150" s="8" t="str">
+        <x:v>对端请求过于频繁，系统已降低速率并等待重试</x:v>
+      </x:c>
+      <x:c r="J150" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0224 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0224/executions/EXEC-tenant-10-project-102-0224/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K150" s="8" t="str">
+        <x:v>2026-08-10T19:44:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0224 taskId=TASK-tenant-10-project-102-0224 executionId=EXEC-tenant-10-project-102-0224 objectId=object-32 errorCode=RATE_LIMIT_EXCEEDED message="remote endpoint returned 429; retryAfterSeconds=30; currentChannel exceeds governed capacity" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L150" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0224、taskId=TASK-tenant-10-project-102-0224 和 executionId=EXEC-tenant-10-project-102-0224。 2. 调用执行日志接口，找到最早出现的 errorCode=RATE_LIMIT_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0224/executions/EXEC-tenant-10-project-102-0224/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、外部 API、目标数据库。 5. 围绕“查看 429、Retry-After、当前 channel/batch、连接器能力快照和最近成功配置，确认是不是突然放大并发”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v322 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额。</x:v>
+      </x:c>
+      <x:c r="M150" s="8" t="str">
+        <x:v>任务一次发出的请求太多，对方系统主动限速；不是数据内容错误</x:v>
+      </x:c>
+      <x:c r="N150" s="8" t="str">
+        <x:v>来源或目标端限流策略拒绝当前吞吐，运行参数超过能力快照或租户配额</x:v>
+      </x:c>
+      <x:c r="O150" s="8" t="str">
+        <x:v>核对连接器是否正确解析 Retry-After 并使用有界退避，防止多个 worker 同时立即重试形成重试风暴</x:v>
+      </x:c>
+      <x:c r="P150" s="8" t="str">
+        <x:v>读取对端限流头；将 channel 和 batch 降到上次成功值或连接器上限以内；按 Retry-After 退避；只重放失败对象</x:v>
+      </x:c>
+      <x:c r="Q150" s="8" t="str">
+        <x:v>调整受治理运行参数；如果代码忽略 Retry-After，则修复退避调度和抖动算法并增加并发重试测试</x:v>
+      </x:c>
+      <x:c r="R150" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0224</x:v>
       </x:c>
-      <x:c r="J150" s="19" t="str">
+      <x:c r="S150" s="19" t="str">
         <x:v>UTC 2026-08-10 19:44:00.000</x:v>
       </x:c>
-      <x:c r="K150" s="20" t="n">
+      <x:c r="T150" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L150" s="8" t="str">
-        <x:v>禁止截断，转人工扩容或修改映射</x:v>
-      </x:c>
-      <x:c r="M150" s="8" t="str">
+      <x:c r="U150" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15688,24 +19296,48 @@
         <x:v>INC-tenant-10-project-102-0225</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
-        <x:v>STRING_TRUNCATION_RISK</x:v>
+        <x:v>SCHEMA_DRIFT_DETECTED</x:v>
       </x:c>
       <x:c r="H151" s="8" t="str">
-        <x:v>字符串超过目标长度；核对 最大长度与超限行数</x:v>
+        <x:v>任务在正式写入前被预检阻断，字段映射页面提示来源结构已变化</x:v>
       </x:c>
       <x:c r="I151" s="8" t="str">
+        <x:v>检测到数据结构变化，请刷新元数据并确认字段映射</x:v>
+      </x:c>
+      <x:c r="J151" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0225 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0225/executions/EXEC-tenant-10-project-102-0225/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K151" s="8" t="str">
+        <x:v>2026-08-10T19:52:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0225 taskId=TASK-tenant-10-project-102-0225 executionId=EXEC-tenant-10-project-102-0225 objectId=object-01 errorCode=SCHEMA_DRIFT_DETECTED message="schema fingerprint changed; publishedSchemaHash does not match currentMetadataHash" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L151" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0225、taskId=TASK-tenant-10-project-102-0225 和 executionId=EXEC-tenant-10-project-102-0225。 2. 调用执行日志接口，找到最早出现的 errorCode=SCHEMA_DRIFT_DETECTED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0225/executions/EXEC-tenant-10-project-102-0225/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、源数据库元数据接口。 5. 围绕“比较当前元数据、发布版本 schema 指纹、最近成功版本和字段增删改清单”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v323 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异。</x:v>
+      </x:c>
+      <x:c r="M151" s="8" t="str">
+        <x:v>源表结构在任务发布后被改过，旧任务仍按原来的字段清单运行，因此系统先停下来避免写错列</x:v>
+      </x:c>
+      <x:c r="N151" s="8" t="str">
+        <x:v>当前 metadata fingerprint 与不可变发布版本不一致，预检检测到字段集合、顺序或类型差异</x:v>
+      </x:c>
+      <x:c r="O151" s="8" t="str">
+        <x:v>确认元数据规范化顺序稳定，避免字段排序变化造成假漂移；真实改名应进入唯一候选映射而不是直接覆盖发布版本</x:v>
+      </x:c>
+      <x:c r="P151" s="8" t="str">
+        <x:v>刷新元数据；查看差异；唯一且类型兼容的改名可以受治理修复；新增可空字段可忽略；删除必需字段或歧义映射转人工确认；重新预检并发布新版本</x:v>
+      </x:c>
+      <x:c r="Q151" s="8" t="str">
+        <x:v>修改任务字段映射或发布配置；若是假漂移，修复元数据规范化/哈希算法并增加顺序无关测试</x:v>
+      </x:c>
+      <x:c r="R151" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0225</x:v>
       </x:c>
-      <x:c r="J151" s="19" t="str">
+      <x:c r="S151" s="19" t="str">
         <x:v>UTC 2026-08-10 19:52:00.000</x:v>
       </x:c>
-      <x:c r="K151" s="20" t="n">
+      <x:c r="T151" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L151" s="8" t="str">
-        <x:v>禁止静默截断，转人工确认影响</x:v>
-      </x:c>
-      <x:c r="M151" s="8" t="str">
+      <x:c r="U151" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15729,24 +19361,48 @@
         <x:v>INC-tenant-10-project-102-0227</x:v>
       </x:c>
       <x:c r="G152" s="8" t="str">
-        <x:v>FOREIGN_KEY_MISSING</x:v>
+        <x:v>NOT_NULL_VIOLATION</x:v>
       </x:c>
       <x:c r="H152" s="8" t="str">
-        <x:v>父记录尚未存在；核对 约束名、父子对象与执行 DAG</x:v>
+        <x:v>任务读取成功但写入失败，脏数据数量增加，错误详情显示具体目标字段不能为空</x:v>
       </x:c>
       <x:c r="I152" s="8" t="str">
+        <x:v>目标字段不允许为空，请修正字段映射、数据清洗规则或目标默认值</x:v>
+      </x:c>
+      <x:c r="J152" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0227 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0227/executions/EXEC-tenant-10-project-102-0227/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K152" s="8" t="str">
+        <x:v>2026-08-10T20:00:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0227 taskId=TASK-tenant-10-project-102-0227 executionId=EXEC-tenant-10-project-102-0227 objectId=object-03 errorCode=NOT_NULL_VIOLATION message="SQLState=23502 not-null constraint violation; targetColumn required and resolvedValue is null" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L152" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0227、taskId=TASK-tenant-10-project-102-0227 和 executionId=EXEC-tenant-10-project-102-0227。 2. 调用执行日志接口，找到最早出现的 errorCode=NOT_NULL_VIOLATION，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0227/executions/EXEC-tenant-10-project-102-0227/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“按 SQLState 23502 定位目标列，检查源字段空值率、映射、转换规则、目标默认值和最近成功配置”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v325 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行。</x:v>
+      </x:c>
+      <x:c r="M152" s="8" t="str">
+        <x:v>源数据这一列没有值，但目标表要求每一行都必须有值</x:v>
+      </x:c>
+      <x:c r="N152" s="8" t="str">
+        <x:v>写入 SQL 为 NOT NULL 目标列提供了 null，数据库约束在提交时拒绝该行</x:v>
+      </x:c>
+      <x:c r="O152" s="8" t="str">
+        <x:v>确认 writer 没有把空字符串错误转成 null，也没有漏应用已批准默认值；禁止在代码里用固定假值掩盖约束</x:v>
+      </x:c>
+      <x:c r="P152" s="8" t="str">
+        <x:v>定位空值来源；修正映射或清洗规则；仅使用业务已经批准的默认值；若确需放宽目标约束则转 DDL 人工审批；重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q152" s="8" t="str">
+        <x:v>修改映射/转换配置或经审批修改 DDL；若转换器丢值，修复字段转换代码并增加 null/空串边界测试</x:v>
+      </x:c>
+      <x:c r="R152" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0227</x:v>
       </x:c>
-      <x:c r="J152" s="19" t="str">
+      <x:c r="S152" s="19" t="str">
         <x:v>UTC 2026-08-10 20:00:00.000</x:v>
       </x:c>
-      <x:c r="K152" s="20" t="n">
+      <x:c r="T152" s="20" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="L152" s="8" t="str">
-        <x:v>调整依赖顺序并重放父子对象</x:v>
-      </x:c>
-      <x:c r="M152" s="8" t="str">
+      <x:c r="U152" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15770,24 +19426,48 @@
         <x:v>INC-tenant-10-project-102-0228</x:v>
       </x:c>
       <x:c r="G153" s="8" t="str">
-        <x:v>UNIQUE_CONSTRAINT_VIOLATION</x:v>
+        <x:v>DATA_TYPE_MISMATCH</x:v>
       </x:c>
       <x:c r="H153" s="8" t="str">
-        <x:v>业务键或幂等键重复；核对 约束名、键摘要与历史回执</x:v>
+        <x:v>预检提示类型不兼容，或任务写入阶段返回类型转换失败</x:v>
       </x:c>
       <x:c r="I153" s="8" t="str">
+        <x:v>字段类型不兼容，请调整映射或配置明确的转换规则</x:v>
+      </x:c>
+      <x:c r="J153" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0228 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0228/executions/EXEC-tenant-10-project-102-0228/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K153" s="8" t="str">
+        <x:v>2026-08-10T20:08:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0228 taskId=TASK-tenant-10-project-102-0228 executionId=EXEC-tenant-10-project-102-0228 objectId=object-04 errorCode=DATA_TYPE_MISMATCH message="SQLState=22P02 invalid input syntax or incompatible sourceTargetType conversion" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L153" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0228、taskId=TASK-tenant-10-project-102-0228 和 executionId=EXEC-tenant-10-project-102-0228。 2. 调用执行日志接口，找到最早出现的 errorCode=DATA_TYPE_MISMATCH，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0228/executions/EXEC-tenant-10-project-102-0228/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标数据库。 5. 围绕“查看源/目标类型、样本统计、失败值类型摘要、精度长度和已配置转换器，不记录原始敏感值”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v326 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误。</x:v>
+      </x:c>
+      <x:c r="M153" s="8" t="str">
+        <x:v>源字段的数据格式和目标列要求不一致，系统无法确定怎样安全转换</x:v>
+      </x:c>
+      <x:c r="N153" s="8" t="str">
+        <x:v>字段转换或 JDBC 参数绑定无法满足目标类型合同，数据库返回类型/语法错误</x:v>
+      </x:c>
+      <x:c r="O153" s="8" t="str">
+        <x:v>确认转换器注册表选择了正确 sourceType-&gt;targetType 处理器，并区分解析失败和数据库驱动绑定类型错误</x:v>
+      </x:c>
+      <x:c r="P153" s="8" t="str">
+        <x:v>配置无损转换；修正日期格式或枚举映射；有损截断、精度下降或语义不明确时转人工；重新预检和样本执行</x:v>
+      </x:c>
+      <x:c r="Q153" s="8" t="str">
+        <x:v>修改字段转换配置；若合法类型组合未注册，增加转换器并覆盖正常、非法、边界值测试</x:v>
+      </x:c>
+      <x:c r="R153" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0228</x:v>
       </x:c>
-      <x:c r="J153" s="19" t="str">
+      <x:c r="S153" s="19" t="str">
         <x:v>UTC 2026-08-10 20:08:00.000</x:v>
       </x:c>
-      <x:c r="K153" s="20" t="n">
+      <x:c r="T153" s="20" t="n">
         <x:v>0.91</x:v>
       </x:c>
-      <x:c r="L153" s="8" t="str">
-        <x:v>仅确认幂等重放，业务冲突退出</x:v>
-      </x:c>
-      <x:c r="M153" s="8" t="str">
+      <x:c r="U153" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15811,24 +19491,48 @@
         <x:v>INC-tenant-10-project-102-0230</x:v>
       </x:c>
       <x:c r="G154" s="8" t="str">
-        <x:v>CHECKPOINT_NOT_FOUND</x:v>
+        <x:v>STRING_TRUNCATION_RISK</x:v>
       </x:c>
       <x:c r="H154" s="8" t="str">
-        <x:v>没有可恢复位点；核对 对象台账与 checkpoint 表</x:v>
+        <x:v>任务在预检阶段阻断，或超长记录被标为脏数据但不会被静默裁剪</x:v>
       </x:c>
       <x:c r="I154" s="8" t="str">
+        <x:v>文本长度超过目标字段限制，请调整映射、清洗规则或目标长度</x:v>
+      </x:c>
+      <x:c r="J154" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0230 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0230/executions/EXEC-tenant-10-project-102-0230/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K154" s="8" t="str">
+        <x:v>2026-08-10T20:16:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0230 taskId=TASK-tenant-10-project-102-0230 executionId=EXEC-tenant-10-project-102-0230 objectId=object-06 errorCode=STRING_TRUNCATION_RISK message="SQLState=22001 value too long for target column; silentTruncationPrevented=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L154" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0230、taskId=TASK-tenant-10-project-102-0230 和 executionId=EXEC-tenant-10-project-102-0230。 2. 调用执行日志接口，找到最早出现的 errorCode=STRING_TRUNCATION_RISK，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0230/executions/EXEC-tenant-10-project-102-0230/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、data-quality。 5. 围绕“查看字段画像 maxLength、目标长度、超限行数和是否存在批准的可逆清洗规则”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v328 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断。</x:v>
+      </x:c>
+      <x:c r="M154" s="8" t="str">
+        <x:v>源文本比目标字段允许的长度更长</x:v>
+      </x:c>
+      <x:c r="N154" s="8" t="str">
+        <x:v>目标 varchar 长度合同不足，数据库返回 22001 或预检提前阻断</x:v>
+      </x:c>
+      <x:c r="O154" s="8" t="str">
+        <x:v>确认 writer 在数据库报错前执行长度预检，并且没有 substring 静默截断</x:v>
+      </x:c>
+      <x:c r="P154" s="8" t="str">
+        <x:v>评估扩大目标字段、改写目标字段、业务确认后清洗或拆分；不允许自动截断；修改后重放失败记录</x:v>
+      </x:c>
+      <x:c r="Q154" s="8" t="str">
+        <x:v>修改映射/清洗配置或经审批修改 DDL；若代码截断，删除隐式 substring 并增加超长测试</x:v>
+      </x:c>
+      <x:c r="R154" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0230</x:v>
       </x:c>
-      <x:c r="J154" s="19" t="str">
+      <x:c r="S154" s="19" t="str">
         <x:v>UTC 2026-08-10 20:16:00.000</x:v>
       </x:c>
-      <x:c r="K154" s="20" t="n">
+      <x:c r="T154" s="20" t="n">
         <x:v>0.92</x:v>
       </x:c>
-      <x:c r="L154" s="8" t="str">
-        <x:v>仅在授权允许时从安全起点重跑</x:v>
-      </x:c>
-      <x:c r="M154" s="8" t="str">
+      <x:c r="U154" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15852,24 +19556,48 @@
         <x:v>INC-tenant-10-project-102-0231</x:v>
       </x:c>
       <x:c r="G155" s="8" t="str">
-        <x:v>CHECKPOINT_STALE</x:v>
+        <x:v>FOREIGN_KEY_MISSING</x:v>
       </x:c>
       <x:c r="H155" s="8" t="str">
-        <x:v>位点与已提交结果不一致；核对 worker 回执、目标提交与位点时间</x:v>
+        <x:v>父表可能成功，子表部分记录失败，任务详情显示外键约束错误</x:v>
       </x:c>
       <x:c r="I155" s="8" t="str">
+        <x:v>关联的父记录尚未写入，请检查对象依赖顺序和同步范围</x:v>
+      </x:c>
+      <x:c r="J155" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0231 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0231/executions/EXEC-tenant-10-project-102-0231/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K155" s="8" t="str">
+        <x:v>2026-08-10T20:24:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0231 taskId=TASK-tenant-10-project-102-0231 executionId=EXEC-tenant-10-project-102-0231 objectId=object-07 errorCode=FOREIGN_KEY_MISSING message="SQLState=23503 foreign key violation; parent key not found before child write" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L155" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0231、taskId=TASK-tenant-10-project-102-0231 和 executionId=EXEC-tenant-10-project-102-0231。 2. 调用执行日志接口，找到最早出现的 errorCode=FOREIGN_KEY_MISSING，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0231/executions/EXEC-tenant-10-project-102-0231/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标 PostgreSQL、任务 DAG。 5. 围绕“读取约束名、父子对象、任务 DAG、父对象状态、过滤范围和失败键摘要”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v329 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503。</x:v>
+      </x:c>
+      <x:c r="M155" s="8" t="str">
+        <x:v>系统先写了子记录，但它依赖的父记录还不存在</x:v>
+      </x:c>
+      <x:c r="N155" s="8" t="str">
+        <x:v>对象执行顺序或范围导致目标外键查不到父键，数据库返回 23503</x:v>
+      </x:c>
+      <x:c r="O155" s="8" t="str">
+        <x:v>确认拓扑排序没有遗漏元数据外键边，并检查并发 worker 是否绕过父对象完成屏障</x:v>
+      </x:c>
+      <x:c r="P155" s="8" t="str">
+        <x:v>补齐外键元数据；确保父对象先完成；确认父记录在授权范围内；再按父后子的顺序重放失败分片。禁用外键属于高风险人工操作</x:v>
+      </x:c>
+      <x:c r="Q155" s="8" t="str">
+        <x:v>修改任务 DAG 或范围配置；若拓扑排序代码漏边，修复依赖图构建并增加并发父子表测试</x:v>
+      </x:c>
+      <x:c r="R155" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0231</x:v>
       </x:c>
-      <x:c r="J155" s="19" t="str">
+      <x:c r="S155" s="19" t="str">
         <x:v>UTC 2026-08-10 20:24:00.000</x:v>
       </x:c>
-      <x:c r="K155" s="20" t="n">
+      <x:c r="T155" s="20" t="n">
         <x:v>0.93</x:v>
       </x:c>
-      <x:c r="L155" s="8" t="str">
-        <x:v>选择最近已确认位点并验证去重</x:v>
-      </x:c>
-      <x:c r="M155" s="8" t="str">
+      <x:c r="U155" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15893,24 +19621,48 @@
         <x:v>INC-tenant-10-project-102-0233</x:v>
       </x:c>
       <x:c r="G156" s="8" t="str">
-        <x:v>KAFKA_BACKLOG_HIGH</x:v>
+        <x:v>CHECKPOINT_NOT_FOUND</x:v>
       </x:c>
       <x:c r="H156" s="8" t="str">
-        <x:v>消费者处理速度低于生产速度；核对 group、partition、lag 与处理时延</x:v>
+        <x:v>恢复按钮提交后任务没有继续，页面提示找不到安全恢复位置</x:v>
       </x:c>
       <x:c r="I156" s="8" t="str">
+        <x:v>没有可用的恢复位点，需要从安全起点重新执行或由运维确认</x:v>
+      </x:c>
+      <x:c r="J156" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0233 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0233/executions/EXEC-tenant-10-project-102-0233/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K156" s="8" t="str">
+        <x:v>2026-08-10T20:32:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0233 taskId=TASK-tenant-10-project-102-0233 executionId=EXEC-tenant-10-project-102-0233 objectId=object-09 errorCode=CHECKPOINT_NOT_FOUND message="checkpoint lookup returned empty for execution object; fallbackRequiresAuthorization=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L156" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0233、taskId=TASK-tenant-10-project-102-0233 和 executionId=EXEC-tenant-10-project-102-0233。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_NOT_FOUND，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0233/executions/EXEC-tenant-10-project-102-0233/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 PostgreSQL checkpoint 表、对象台账。 5. 围绕“查询对象台账、checkpoint 表、任务模式、首次执行时间和清理记录，确认是否本来就不应有位点”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v331 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor。</x:v>
+      </x:c>
+      <x:c r="M156" s="8" t="str">
+        <x:v>系统没有找到上次安全停下的位置，所以不能直接从中间继续</x:v>
+      </x:c>
+      <x:c r="N156" s="8" t="str">
+        <x:v>对象缺少持久 checkpoint 或引用已经失效，恢复状态机无法计算 resume cursor</x:v>
+      </x:c>
+      <x:c r="O156" s="8" t="str">
+        <x:v>检查 checkpoint 写入事务是否与批次回执一致，以及保留任务是否误删仍被执行引用的位点</x:v>
+      </x:c>
+      <x:c r="P156" s="8" t="str">
+        <x:v>确认允许的安全起点；全量任务可在授权范围内重跑失败对象；增量任务需人工确认游标；修复位点保留策略后重试</x:v>
+      </x:c>
+      <x:c r="Q156" s="8" t="str">
+        <x:v>修改 checkpoint 数据或保留配置；若事务漏写，修复回执/位点原子性并增加崩溃恢复测试</x:v>
+      </x:c>
+      <x:c r="R156" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0233</x:v>
       </x:c>
-      <x:c r="J156" s="19" t="str">
+      <x:c r="S156" s="19" t="str">
         <x:v>UTC 2026-08-10 20:32:00.000</x:v>
       </x:c>
-      <x:c r="K156" s="20" t="n">
+      <x:c r="T156" s="20" t="n">
         <x:v>0.94</x:v>
       </x:c>
-      <x:c r="L156" s="8" t="str">
-        <x:v>隔离坏消息并按容量策略处理</x:v>
-      </x:c>
-      <x:c r="M156" s="8" t="str">
+      <x:c r="U156" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15934,24 +19686,48 @@
         <x:v>INC-tenant-10-project-102-0234</x:v>
       </x:c>
       <x:c r="G157" s="8" t="str">
-        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
+        <x:v>CHECKPOINT_STALE</x:v>
       </x:c>
       <x:c r="H157" s="8" t="str">
-        <x:v>事务事实未及时投递；核对 outbox 状态、attempt 与 broker 回执</x:v>
+        <x:v>恢复预检提示位点不一致，系统停止以避免重复写入</x:v>
       </x:c>
       <x:c r="I157" s="8" t="str">
+        <x:v>恢复位点与已提交结果不一致，请先完成位点对账</x:v>
+      </x:c>
+      <x:c r="J157" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0234 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0234/executions/EXEC-tenant-10-project-102-0234/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K157" s="8" t="str">
+        <x:v>2026-08-10T20:40:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0234 taskId=TASK-tenant-10-project-102-0234 executionId=EXEC-tenant-10-project-102-0234 objectId=object-10 errorCode=CHECKPOINT_STALE message="checkpoint timestamp precedes committed worker receipt; replay duplication risk detected" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L157" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0234、taskId=TASK-tenant-10-project-102-0234 和 executionId=EXEC-tenant-10-project-102-0234。 2. 调用执行日志接口，找到最早出现的 errorCode=CHECKPOINT_STALE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0234/executions/EXEC-tenant-10-project-102-0234/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 目标数据库、checkpoint/worker receipt。 5. 围绕“比较 checkpoint 时间、worker 回执、目标提交时间、配置版本和对象 attempt”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v332 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：checkpoint 与 authoritative commit receipt 不一致，恢复游标过期。</x:v>
+      </x:c>
+      <x:c r="M157" s="8" t="str">
+        <x:v>系统记录的进度比目标数据库实际完成的位置更旧，直接继续可能重复写数据</x:v>
+      </x:c>
+      <x:c r="N157" s="8" t="str">
+        <x:v>checkpoint 与 authoritative commit receipt 不一致，恢复游标过期</x:v>
+      </x:c>
+      <x:c r="O157" s="8" t="str">
+        <x:v>检查提交事务、回执和 checkpoint 的先后顺序，定位是否存在写目标成功但位点更新失败的窗口</x:v>
+      </x:c>
+      <x:c r="P157" s="8" t="str">
+        <x:v>选择最近已确认提交的位点；对唯一键和目标统计做去重验证；更新位点后只重放未确认批次</x:v>
+      </x:c>
+      <x:c r="Q157" s="8" t="str">
+        <x:v>修正 checkpoint；若代码顺序错误，将目标提交、回执和位点更新纳入可靠事务/补偿流程</x:v>
+      </x:c>
+      <x:c r="R157" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0234</x:v>
       </x:c>
-      <x:c r="J157" s="19" t="str">
+      <x:c r="S157" s="19" t="str">
         <x:v>UTC 2026-08-10 20:40:00.000</x:v>
       </x:c>
-      <x:c r="K157" s="20" t="n">
+      <x:c r="T157" s="20" t="n">
         <x:v>0.95</x:v>
       </x:c>
-      <x:c r="L157" s="8" t="str">
-        <x:v>重投未交付 outbox，不重复业务事务</x:v>
-      </x:c>
-      <x:c r="M157" s="8" t="str">
+      <x:c r="U157" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -15975,24 +19751,48 @@
         <x:v>INC-tenant-10-project-102-0236</x:v>
       </x:c>
       <x:c r="G158" s="8" t="str">
-        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
+        <x:v>OUTBOX_DELIVERY_TIMEOUT</x:v>
       </x:c>
       <x:c r="H158" s="8" t="str">
-        <x:v>连接器版本不支持配置；核对 版本、能力快照与配置字段</x:v>
+        <x:v>页面显示请求已保存，但下游执行迟迟没有开始</x:v>
       </x:c>
       <x:c r="I158" s="8" t="str">
+        <x:v>任务已保存，异步投递暂时延迟，请勿重复创建任务</x:v>
+      </x:c>
+      <x:c r="J158" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0236 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0236/executions/EXEC-tenant-10-project-102-0236/logs；服务日志：docker compose logs agent-runtime，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K158" s="8" t="str">
+        <x:v>2026-08-10T20:48:00.000Z level=ERROR service=agent-runtime traceId=trace-tenant-10-project-102-0236 taskId=TASK-tenant-10-project-102-0236 executionId=EXEC-tenant-10-project-102-0236 objectId=object-12 errorCode=OUTBOX_DELIVERY_TIMEOUT message="outbox state remains PENDING after delivery deadline; broker acknowledgement missing" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L158" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0236、taskId=TASK-tenant-10-project-102-0236 和 executionId=EXEC-tenant-10-project-102-0236。 2. 调用执行日志接口，找到最早出现的 errorCode=OUTBOX_DELIVERY_TIMEOUT，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0236/executions/EXEC-tenant-10-project-102-0236/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 agent-runtime 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、Kafka、PostgreSQL outbox。 5. 围绕“查询 outbox 状态、attempt、nextAttemptAt、broker 健康、producer 错误和 consumer result”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v334 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失。</x:v>
+      </x:c>
+      <x:c r="M158" s="8" t="str">
+        <x:v>系统已经把任务保存下来，但负责送到消息队列的投递步骤暂时没有成功</x:v>
+      </x:c>
+      <x:c r="N158" s="8" t="str">
+        <x:v>事务 outbox 持久化成功，Kafka publish acknowledgement 在截止时间内缺失</x:v>
+      </x:c>
+      <x:c r="O158" s="8" t="str">
+        <x:v>确认 dispatcher 只重投未确认 outbox，并且消息键稳定；禁止重新执行已经提交的业务事务</x:v>
+      </x:c>
+      <x:c r="P158" s="8" t="str">
+        <x:v>恢复 broker/网络；重投同一 outbox；检查 producer 权限和 topic；等待 consumer result；不要重新创建业务对象</x:v>
+      </x:c>
+      <x:c r="Q158" s="8" t="str">
+        <x:v>修复 Kafka 配置或 dispatcher；若状态判断错误，修复 outbox CAS/幂等逻辑并增加确认丢失测试</x:v>
+      </x:c>
+      <x:c r="R158" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0236</x:v>
       </x:c>
-      <x:c r="J158" s="19" t="str">
+      <x:c r="S158" s="19" t="str">
         <x:v>UTC 2026-08-10 20:48:00.000</x:v>
       </x:c>
-      <x:c r="K158" s="20" t="n">
+      <x:c r="T158" s="20" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="L158" s="8" t="str">
-        <x:v>回滚兼容配置或人工升级连接器</x:v>
-      </x:c>
-      <x:c r="M158" s="8" t="str">
+      <x:c r="U158" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -16016,24 +19816,48 @@
         <x:v>INC-tenant-10-project-102-0237</x:v>
       </x:c>
       <x:c r="G159" s="8" t="str">
-        <x:v>TARGET_CAPACITY_EXCEEDED</x:v>
+        <x:v>CONNECTOR_VERSION_INCOMPATIBLE</x:v>
       </x:c>
       <x:c r="H159" s="8" t="str">
-        <x:v>目标连接或磁盘达到阈值；核对 容量指标、等待事件与配额</x:v>
+        <x:v>配置可以保存草稿，但预检提示连接器版本不支持该能力</x:v>
       </x:c>
       <x:c r="I159" s="8" t="str">
+        <x:v>当前连接器版本不支持所选模式或参数，请使用兼容配置或升级连接器</x:v>
+      </x:c>
+      <x:c r="J159" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0237 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0237/executions/EXEC-tenant-10-project-102-0237/logs；服务日志：docker compose logs datasource-management，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K159" s="8" t="str">
+        <x:v>2026-08-10T20:56:00.000Z level=ERROR service=datasource-management traceId=trace-tenant-10-project-102-0237 taskId=TASK-tenant-10-project-102-0237 executionId=EXEC-tenant-10-project-102-0237 objectId=object-13 errorCode=CONNECTOR_VERSION_INCOMPATIBLE message="connector capability mismatch; requested option absent from runtime version capability snapshot" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L159" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0237、taskId=TASK-tenant-10-project-102-0237 和 executionId=EXEC-tenant-10-project-102-0237。 2. 调用执行日志接口，找到最早出现的 errorCode=CONNECTOR_VERSION_INCOMPATIBLE，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0237/executions/EXEC-tenant-10-project-102-0237/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 datasource-management 日志，按 traceId 检索关键行；同时核对关联服务 data-sync、连接器运行时。 5. 围绕“比较连接器运行时版本、能力快照、任务配置字段和最近成功版本”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v335 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：任务所需 capability 不在当前 connector runtime manifest 中。</x:v>
+      </x:c>
+      <x:c r="M159" s="8" t="str">
+        <x:v>当前安装的连接器版本太旧或能力不同，无法理解任务中的某个配置项</x:v>
+      </x:c>
+      <x:c r="N159" s="8" t="str">
+        <x:v>任务所需 capability 不在当前 connector runtime manifest 中</x:v>
+      </x:c>
+      <x:c r="O159" s="8" t="str">
+        <x:v>检查能力探测是否来自真实运行时而不是静态枚举，以及升级后缓存是否刷新</x:v>
+      </x:c>
+      <x:c r="P159" s="8" t="str">
+        <x:v>回滚到上次兼容配置，或在变更窗口升级连接器；刷新能力快照；重新预检</x:v>
+      </x:c>
+      <x:c r="Q159" s="8" t="str">
+        <x:v>修改任务参数或升级连接器；若能力缓存过期，修复刷新逻辑并增加版本切换测试</x:v>
+      </x:c>
+      <x:c r="R159" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0237</x:v>
       </x:c>
-      <x:c r="J159" s="19" t="str">
+      <x:c r="S159" s="19" t="str">
         <x:v>UTC 2026-08-10 20:56:00.000</x:v>
       </x:c>
-      <x:c r="K159" s="20" t="n">
+      <x:c r="T159" s="20" t="n">
         <x:v>0.97</x:v>
       </x:c>
-      <x:c r="L159" s="8" t="str">
-        <x:v>降低负载并等待恢复</x:v>
-      </x:c>
-      <x:c r="M159" s="8" t="str">
+      <x:c r="U159" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -16060,21 +19884,45 @@
         <x:v>DIRTY_RECORD_THRESHOLD_EXCEEDED</x:v>
       </x:c>
       <x:c r="H160" s="8" t="str">
-        <x:v>脏数据超过任务阈值；核对 规则结果、坏行引用与阈值</x:v>
+        <x:v>任务处理一部分数据后停止，页面显示脏数据数量和规则摘要</x:v>
       </x:c>
       <x:c r="I160" s="8" t="str">
+        <x:v>脏数据超过允许阈值，请检查数据质量规则和失败样本摘要</x:v>
+      </x:c>
+      <x:c r="J160" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0239 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0239/executions/EXEC-tenant-10-project-102-0239/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K160" s="8" t="str">
+        <x:v>2026-08-10T21:04:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0239 taskId=TASK-tenant-10-project-102-0239 executionId=EXEC-tenant-10-project-102-0239 objectId=object-15 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED message="dirty record ratio exceeds governed threshold; raw record content omitted" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L160" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0239、taskId=TASK-tenant-10-project-102-0239 和 executionId=EXEC-tenant-10-project-102-0239。 2. 调用执行日志接口，找到最早出现的 errorCode=DIRTY_RECORD_THRESHOLD_EXCEEDED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0239/executions/EXEC-tenant-10-project-102-0239/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 data-quality、对象台账。 5. 围绕“按规则码统计失败数量、比例、字段和时间分布，读取脱敏样本引用，不查看完整敏感行”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v337 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止。</x:v>
+      </x:c>
+      <x:c r="M160" s="8" t="str">
+        <x:v>本批数据中不符合规则的记录太多，超过任务允许范围</x:v>
+      </x:c>
+      <x:c r="N160" s="8" t="str">
+        <x:v>dirtyRecords/processedRecords 超过发布配置阈值，worker 按治理策略停止</x:v>
+      </x:c>
+      <x:c r="O160" s="8" t="str">
+        <x:v>确认阈值使用实际处理行数作分母，并检查同一失败记录是否被重复计数</x:v>
+      </x:c>
+      <x:c r="P160" s="8" t="str">
+        <x:v>定位主要规则；修复上游数据或清洗映射；必要时隔离明确坏行；不得无审批提高阈值掩盖质量问题</x:v>
+      </x:c>
+      <x:c r="Q160" s="8" t="str">
+        <x:v>修改清洗/映射配置或上游数据；若统计重复，修复计数幂等并增加重试测试</x:v>
+      </x:c>
+      <x:c r="R160" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0239</x:v>
       </x:c>
-      <x:c r="J160" s="19" t="str">
+      <x:c r="S160" s="19" t="str">
         <x:v>UTC 2026-08-10 21:04:00.000</x:v>
       </x:c>
-      <x:c r="K160" s="20" t="n">
+      <x:c r="T160" s="20" t="n">
         <x:v>0.98</x:v>
       </x:c>
-      <x:c r="L160" s="8" t="str">
-        <x:v>隔离坏行，超过停止阈值时退出</x:v>
-      </x:c>
-      <x:c r="M160" s="8" t="str">
+      <x:c r="U160" s="8" t="str">
         <x:v>RECOVERED</x:v>
       </x:c>
     </x:row>
@@ -16101,21 +19949,45 @@
         <x:v>DDL_REQUIRED</x:v>
       </x:c>
       <x:c r="H161" s="8" t="str">
-        <x:v>需要修改目标结构；核对 元数据差异与目标约束</x:v>
+        <x:v>系统解释了结构差异，但不会自动修改目标表，任务停在需要审批状态</x:v>
       </x:c>
       <x:c r="I161" s="8" t="str">
+        <x:v>修复需要修改目标数据库结构，请由数据库管理员评估并审批</x:v>
+      </x:c>
+      <x:c r="J161" s="8" t="str">
+        <x:v>平台入口：数据同步 &gt; 执行详情 &gt; 运行日志，按 traceId=trace-tenant-10-project-102-0240 过滤；API：GET /api/sync/sync-tasks/TASK-tenant-10-project-102-0240/executions/EXEC-tenant-10-project-102-0240/logs；服务日志：docker compose logs data-sync，再按同一 traceId 检索。</x:v>
+      </x:c>
+      <x:c r="K161" s="8" t="str">
+        <x:v>2026-08-10T21:12:00.000Z level=ERROR service=data-sync traceId=trace-tenant-10-project-102-0240 taskId=TASK-tenant-10-project-102-0240 executionId=EXEC-tenant-10-project-102-0240 objectId=object-16 errorCode=DDL_REQUIRED message="required remediation classified as DDL; autonomous execution blocked; approvalRequired=true" sensitivePayloadOmitted=true</x:v>
+      </x:c>
+      <x:c r="L161" s="8" t="str">
+        <x:v>1. 先从页面复制 traceId=trace-tenant-10-project-102-0240、taskId=TASK-tenant-10-project-102-0240 和 executionId=EXEC-tenant-10-project-102-0240。 2. 调用执行日志接口，找到最早出现的 errorCode=DDL_REQUIRED，确认不是后续级联报错。 3. 查询 /api/sync/sync-tasks/TASK-tenant-10-project-102-0240/executions/EXEC-tenant-10-project-102-0240/lifecycle-graph，确认失败停在 Agent、Kafka、worker 还是 Recovery。 4. 进入 data-sync 日志，按 traceId 检索关键行；同时核对关联服务 datasource-management、目标 PostgreSQL、审批中心。 5. 围绕“读取元数据差异、目标约束、受影响数据量、锁表风险、回滚 SQL 和业务窗口”读取配置、元数据、SQLState、指标或依赖健康证据。 6. 与最近一次成功配置 cfg-v338 和成功 execution 对比，排除本次变更之外的噪声。 7. 只有日志、状态和配置证据一致时才确认：当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录。</x:v>
+      </x:c>
+      <x:c r="M161" s="8" t="str">
+        <x:v>要解决问题必须改变目标表结构，这可能锁表或影响其他任务，所以系统不会自行修改</x:v>
+      </x:c>
+      <x:c r="N161" s="8" t="str">
+        <x:v>当前 schema 无法满足数据合同，唯一修复涉及 DDL，超出首次授权盒低风险动作目录</x:v>
+      </x:c>
+      <x:c r="O161" s="8" t="str">
+        <x:v>确认系统没有把 ALTER TABLE 包装成低风险工具；DDL 建议必须保留目标对象、影响和验证但不能自动执行</x:v>
+      </x:c>
+      <x:c r="P161" s="8" t="str">
+        <x:v>生成变更建议；由 DBA 审核 SQL、锁和回滚；在窗口执行；刷新元数据；重新预检和失败对象重放</x:v>
+      </x:c>
+      <x:c r="Q161" s="8" t="str">
+        <x:v>经审批执行明确 DDL；若系统错误分类为 DDL，修复元数据差异判断并增加约束回归测试</x:v>
+      </x:c>
+      <x:c r="R161" s="8" t="str">
         <x:v>synthetic://datasmart-govern/correlated/tenant-10-project-102/execution/EXEC-tenant-10-project-102-0240</x:v>
       </x:c>
-      <x:c r="J161" s="19" t="str">
+      <x:c r="S161" s="19" t="str">
         <x:v>UTC 2026-08-10 21:12:00.000</x:v>
       </x:c>
-      <x:c r="K161" s="20" t="n">
+      <x:c r="T161" s="20" t="n">
         <x:v>0.99</x:v>
       </x:c>
-      <x:c r="L161" s="8" t="str">
-        <x:v>高风险动作，转人工执行与验证</x:v>
-      </x:c>
-      <x:c r="M161" s="8" t="str">
+      <x:c r="U161" s="8" t="str">
         <x:v>ATTENTION_REQUIRED</x:v>
       </x:c>
     </x:row>
@@ -22219,16 +26091,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B27" s="8" t="str">
-        <x:v>第 1 列</x:v>
+        <x:v>第 14 列</x:v>
       </x:c>
       <x:c r="C27" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D27" s="8" t="str">
-        <x:v>解释 任务参数 的第 1 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 14 个字段</x:v>
       </x:c>
       <x:c r="E27" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22239,16 +26111,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B28" s="8" t="str">
-        <x:v>第 2 列</x:v>
+        <x:v>第 15 列</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D28" s="8" t="str">
-        <x:v>解释 任务参数 的第 2 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 15 个字段</x:v>
       </x:c>
       <x:c r="E28" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22259,16 +26131,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B29" s="8" t="str">
-        <x:v>第 3 列</x:v>
+        <x:v>第 16 列</x:v>
       </x:c>
       <x:c r="C29" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D29" s="8" t="str">
-        <x:v>解释 任务参数 的第 3 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 16 个字段</x:v>
       </x:c>
       <x:c r="E29" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22279,16 +26151,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B30" s="8" t="str">
-        <x:v>第 4 列</x:v>
+        <x:v>第 17 列</x:v>
       </x:c>
       <x:c r="C30" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D30" s="8" t="str">
-        <x:v>解释 任务参数 的第 4 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 17 个字段</x:v>
       </x:c>
       <x:c r="E30" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22299,16 +26171,16 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B31" s="8" t="str">
-        <x:v>第 5 列</x:v>
+        <x:v>第 18 列</x:v>
       </x:c>
       <x:c r="C31" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D31" s="8" t="str">
-        <x:v>解释 任务参数 的第 5 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 18 个字段</x:v>
       </x:c>
       <x:c r="E31" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22319,16 +26191,16 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B32" s="8" t="str">
-        <x:v>第 6 列</x:v>
+        <x:v>第 19 列</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D32" s="8" t="str">
-        <x:v>解释 任务参数 的第 6 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 19 个字段</x:v>
       </x:c>
       <x:c r="E32" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
@@ -22339,21 +26211,181 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="8" t="str">
-        <x:v>任务参数</x:v>
+        <x:v>失败任务明细</x:v>
       </x:c>
       <x:c r="B33" s="8" t="str">
-        <x:v>第 7 列</x:v>
+        <x:v>第 20 列</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
         <x:v>string/number</x:v>
       </x:c>
       <x:c r="D33" s="8" t="str">
-        <x:v>解释 任务参数 的第 7 个字段</x:v>
+        <x:v>解释 失败任务明细 的第 20 个字段</x:v>
       </x:c>
       <x:c r="E33" s="8" t="str">
         <x:v>按该表业务合同校验</x:v>
       </x:c>
       <x:c r="F33" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="8" t="str">
+        <x:v>失败任务明细</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="str">
+        <x:v>第 21 列</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="str">
+        <x:v>解释 失败任务明细 的第 21 个字段</x:v>
+      </x:c>
+      <x:c r="E34" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F34" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="str">
+        <x:v>第 1 列</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D35" s="8" t="str">
+        <x:v>解释 任务参数 的第 1 个字段</x:v>
+      </x:c>
+      <x:c r="E35" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="str">
+        <x:v>第 2 列</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D36" s="8" t="str">
+        <x:v>解释 任务参数 的第 2 个字段</x:v>
+      </x:c>
+      <x:c r="E36" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F36" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>第 3 列</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D37" s="8" t="str">
+        <x:v>解释 任务参数 的第 3 个字段</x:v>
+      </x:c>
+      <x:c r="E37" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F37" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>第 4 列</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D38" s="8" t="str">
+        <x:v>解释 任务参数 的第 4 个字段</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F38" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>第 5 列</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="str">
+        <x:v>解释 任务参数 的第 5 个字段</x:v>
+      </x:c>
+      <x:c r="E39" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>第 6 列</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="str">
+        <x:v>解释 任务参数 的第 6 个字段</x:v>
+      </x:c>
+      <x:c r="E40" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F40" s="8" t="str">
+        <x:v>internal/synthetic</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="8" t="str">
+        <x:v>任务参数</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>第 7 列</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>string/number</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="str">
+        <x:v>解释 任务参数 的第 7 个字段</x:v>
+      </x:c>
+      <x:c r="E41" s="8" t="str">
+        <x:v>按该表业务合同校验</x:v>
+      </x:c>
+      <x:c r="F41" s="8" t="str">
         <x:v>internal/synthetic</x:v>
       </x:c>
     </x:row>
